--- a/data/planif.xlsx
+++ b/data/planif.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/38dbb4d9e693c1ee/Desktop/Nouveau dossier/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1049" documentId="13_ncr:1_{CEC3A4F4-E090-400C-9B5F-3B734A132120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2F1B8C9-B217-412D-BA2F-90820A755FC0}"/>
+  <xr:revisionPtr revIDLastSave="1231" documentId="13_ncr:1_{CEC3A4F4-E090-400C-9B5F-3B734A132120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{990850C3-4F0A-4B4D-8F54-2B2D2626523B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="195">
   <si>
     <t>Décembre</t>
   </si>
@@ -831,6 +831,18 @@
   </si>
   <si>
     <t>Novembre</t>
+  </si>
+  <si>
+    <t>75 km marche</t>
+  </si>
+  <si>
+    <t>Affutage et compétition</t>
+  </si>
+  <si>
+    <t>Période de récupération</t>
+  </si>
+  <si>
+    <t>Consolidations spécifiques</t>
   </si>
 </sst>
 </file>
@@ -886,7 +898,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="23">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1019,8 +1031,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="49">
+  <borders count="56">
     <border>
       <left/>
       <right/>
@@ -1364,21 +1388,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color rgb="FF000000"/>
@@ -1598,12 +1607,96 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="189">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1665,6 +1758,54 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1743,6 +1884,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1810,6 +1954,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1827,7 +1977,7 @@
     <xf numFmtId="0" fontId="1" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1857,6 +2007,9 @@
     <xf numFmtId="0" fontId="1" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1869,9 +2022,15 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="8" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="20" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1881,85 +2040,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1968,10 +2061,205 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1979,7 +2267,86 @@
     <cellStyle name="Milliers" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="29">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD8FAF6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2328,25 +2695,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2A9EC4A6-FF98-4AEC-A1D1-83C2EDE4928D}" name="Tableau2" displayName="Tableau2" ref="B1:O90" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2A9EC4A6-FF98-4AEC-A1D1-83C2EDE4928D}" name="Tableau2" displayName="Tableau2" ref="B1:O90" totalsRowShown="0" headerRowDxfId="28" dataDxfId="27">
   <autoFilter ref="B1:O90" xr:uid="{2A9EC4A6-FF98-4AEC-A1D1-83C2EDE4928D}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{A64B88FD-547B-4818-BD4D-686DCEE58AE5}" name="Semaine" dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{AA918300-3D81-4B96-8EDC-8F0CC605284A}" name="Jour" dataDxfId="20"/>
-    <tableColumn id="10" xr3:uid="{9663290F-807D-45A9-9E94-703DB8BB0F1A}" name="Type de séance" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{91C0990C-861A-48E3-84FA-F1B3C2F3F69F}" name="Filière / Qualité " dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{66BE0558-672A-484D-B4AB-82C5AF0FA1EB}" name="Objectif physiologique" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{8DAB5F23-4B82-4EF0-9892-43BFE914BB86}" name="Séance détaillée" dataDxfId="16"/>
-    <tableColumn id="9" xr3:uid="{45E8FED0-21DF-4363-8994-09AC633A1825}" name="Distance totale (km)" dataDxfId="15"/>
-    <tableColumn id="6" xr3:uid="{CE732D0B-3806-4065-BFB3-1068CB2684F1}" name="Durée totale" dataDxfId="14"/>
-    <tableColumn id="11" xr3:uid="{D473D6F1-1F69-429F-85E1-9CA7766EE687}" name="temps moyen / km" dataDxfId="13" dataCellStyle="Milliers">
+    <tableColumn id="1" xr3:uid="{A64B88FD-547B-4818-BD4D-686DCEE58AE5}" name="Semaine" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{AA918300-3D81-4B96-8EDC-8F0CC605284A}" name="Jour" dataDxfId="25"/>
+    <tableColumn id="10" xr3:uid="{9663290F-807D-45A9-9E94-703DB8BB0F1A}" name="Type de séance" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{91C0990C-861A-48E3-84FA-F1B3C2F3F69F}" name="Filière / Qualité " dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{66BE0558-672A-484D-B4AB-82C5AF0FA1EB}" name="Objectif physiologique" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{8DAB5F23-4B82-4EF0-9892-43BFE914BB86}" name="Séance détaillée" dataDxfId="21"/>
+    <tableColumn id="9" xr3:uid="{45E8FED0-21DF-4363-8994-09AC633A1825}" name="Distance totale (km)" dataDxfId="20"/>
+    <tableColumn id="6" xr3:uid="{CE732D0B-3806-4065-BFB3-1068CB2684F1}" name="Durée totale" dataDxfId="19"/>
+    <tableColumn id="11" xr3:uid="{D473D6F1-1F69-429F-85E1-9CA7766EE687}" name="temps moyen / km" dataDxfId="18" dataCellStyle="Milliers">
       <calculatedColumnFormula>Tableau2[[#This Row],[Durée totale]]/Tableau2[[#This Row],[Distance totale (km)]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{13F8A0B1-733F-4A08-B2D4-5461B9FC3BF7}" name="Vitesse moyenne (km/h)" dataDxfId="12"/>
-    <tableColumn id="13" xr3:uid="{63EF3AB0-732A-4168-B397-AC25A367B464}" name="FC moyenne" dataDxfId="11"/>
-    <tableColumn id="14" xr3:uid="{39CA7289-A82E-4DD4-8D9A-F0B78153768D}" name="FC MAX" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{2BCC395B-5550-4D33-98B2-63DA20A6DAE6}" name="RPE" dataDxfId="9"/>
-    <tableColumn id="8" xr3:uid="{395CA70D-8616-428D-81C0-5D996801AD4B}" name="Charge de travail" dataDxfId="8">
+    <tableColumn id="12" xr3:uid="{13F8A0B1-733F-4A08-B2D4-5461B9FC3BF7}" name="Vitesse moyenne (km/h)" dataDxfId="17"/>
+    <tableColumn id="13" xr3:uid="{63EF3AB0-732A-4168-B397-AC25A367B464}" name="FC moyenne" dataDxfId="16"/>
+    <tableColumn id="14" xr3:uid="{39CA7289-A82E-4DD4-8D9A-F0B78153768D}" name="FC MAX" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{2BCC395B-5550-4D33-98B2-63DA20A6DAE6}" name="RPE" dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{395CA70D-8616-428D-81C0-5D996801AD4B}" name="Charge de travail" dataDxfId="13">
       <calculatedColumnFormula>Tableau2[[#This Row],[Durée totale]]*Tableau2[[#This Row],[RPE]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2355,10 +2722,10 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{BCD5C2E9-2545-4C3A-B0BC-17DE95C14C83}" name="Tableau3" displayName="Tableau3" ref="B1:B8" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{BCD5C2E9-2545-4C3A-B0BC-17DE95C14C83}" name="Tableau3" displayName="Tableau3" ref="B1:B8" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
   <autoFilter ref="B1:B8" xr:uid="{BCD5C2E9-2545-4C3A-B0BC-17DE95C14C83}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{8D9897F5-8072-4DCD-83CF-8633BA7CB26D}" name="Filière énergétique / Qualité" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{8D9897F5-8072-4DCD-83CF-8633BA7CB26D}" name="Filière énergétique / Qualité" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium22" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2668,130 +3035,130 @@
     <col min="28" max="28" width="17.44140625" style="3" bestFit="1" customWidth="1"/>
     <col min="29" max="30" width="14.33203125" style="3" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="13.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="32" max="34" width="14.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="36" max="38" width="14.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.33203125" style="3" customWidth="1"/>
+    <col min="33" max="36" width="19.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.33203125" style="3" bestFit="1" customWidth="1"/>
     <col min="39" max="39" width="13.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="40" max="46" width="14.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="13.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="13.44140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="49" max="50" width="13.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="51" max="54" width="13.44140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="55" max="60" width="13.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="13.44140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="62" max="63" width="13.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="64" max="65" width="14.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="13.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="67" max="69" width="14.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="13.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="71" max="72" width="14.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="40" max="43" width="19.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="44" max="46" width="14.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="47" max="50" width="19.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="51" max="53" width="13.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="54" max="57" width="19.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="58" max="60" width="13.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="61" max="63" width="19.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="14.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="65" max="68" width="19.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="14.33203125" style="3" customWidth="1"/>
+    <col min="70" max="70" width="16.5546875" style="3" customWidth="1"/>
+    <col min="71" max="71" width="17.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="14.33203125" style="3" bestFit="1" customWidth="1"/>
     <col min="73" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:72" x14ac:dyDescent="0.3">
       <c r="B1" s="2"/>
-      <c r="C1" s="95" t="s">
+      <c r="C1" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="100"/>
-      <c r="E1" s="100"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="95" t="s">
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="100"/>
-      <c r="I1" s="100"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="95" t="s">
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="100"/>
-      <c r="M1" s="100"/>
-      <c r="N1" s="45"/>
-      <c r="O1" s="95" t="s">
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="61"/>
+      <c r="O1" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="100"/>
-      <c r="Q1" s="100"/>
-      <c r="R1" s="45"/>
-      <c r="S1" s="95" t="s">
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="61"/>
+      <c r="S1" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="T1" s="100"/>
-      <c r="U1" s="100"/>
-      <c r="V1" s="45"/>
-      <c r="W1" s="28" t="s">
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
+      <c r="V1" s="61"/>
+      <c r="W1" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="X1" s="29"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="29"/>
-      <c r="AA1" s="29"/>
-      <c r="AB1" s="101"/>
-      <c r="AC1" s="102" t="s">
+      <c r="X1" s="45"/>
+      <c r="Y1" s="45"/>
+      <c r="Z1" s="45"/>
+      <c r="AA1" s="45"/>
+      <c r="AB1" s="111"/>
+      <c r="AC1" s="115" t="s">
         <v>185</v>
       </c>
-      <c r="AD1" s="103"/>
-      <c r="AE1" s="103"/>
-      <c r="AF1" s="103"/>
-      <c r="AG1" s="104"/>
-      <c r="AH1" s="102" t="s">
+      <c r="AD1" s="116"/>
+      <c r="AE1" s="116"/>
+      <c r="AF1" s="116"/>
+      <c r="AG1" s="117"/>
+      <c r="AH1" s="115" t="s">
         <v>186</v>
       </c>
-      <c r="AI1" s="103"/>
-      <c r="AJ1" s="103"/>
-      <c r="AK1" s="104"/>
-      <c r="AL1" s="102" t="s">
+      <c r="AI1" s="116"/>
+      <c r="AJ1" s="116"/>
+      <c r="AK1" s="117"/>
+      <c r="AL1" s="115" t="s">
         <v>187</v>
       </c>
-      <c r="AM1" s="103"/>
-      <c r="AN1" s="103"/>
-      <c r="AO1" s="103"/>
-      <c r="AP1" s="104"/>
-      <c r="AQ1" s="102" t="s">
+      <c r="AM1" s="116"/>
+      <c r="AN1" s="116"/>
+      <c r="AO1" s="116"/>
+      <c r="AP1" s="117"/>
+      <c r="AQ1" s="115" t="s">
         <v>188</v>
       </c>
-      <c r="AR1" s="103"/>
-      <c r="AS1" s="103"/>
-      <c r="AT1" s="104"/>
-      <c r="AU1" s="102" t="s">
+      <c r="AR1" s="116"/>
+      <c r="AS1" s="116"/>
+      <c r="AT1" s="117"/>
+      <c r="AU1" s="115" t="s">
         <v>189</v>
       </c>
-      <c r="AV1" s="103"/>
-      <c r="AW1" s="103"/>
-      <c r="AX1" s="104"/>
-      <c r="AY1" s="102" t="s">
+      <c r="AV1" s="116"/>
+      <c r="AW1" s="116"/>
+      <c r="AX1" s="117"/>
+      <c r="AY1" s="115" t="s">
         <v>190</v>
       </c>
-      <c r="AZ1" s="103"/>
-      <c r="BA1" s="103"/>
-      <c r="BB1" s="103"/>
-      <c r="BC1" s="104"/>
-      <c r="BD1" s="102" t="s">
+      <c r="AZ1" s="116"/>
+      <c r="BA1" s="116"/>
+      <c r="BB1" s="116"/>
+      <c r="BC1" s="117"/>
+      <c r="BD1" s="115" t="s">
         <v>0</v>
       </c>
-      <c r="BE1" s="103"/>
-      <c r="BF1" s="103"/>
-      <c r="BG1" s="104"/>
-      <c r="BH1" s="102" t="s">
+      <c r="BE1" s="116"/>
+      <c r="BF1" s="116"/>
+      <c r="BG1" s="117"/>
+      <c r="BH1" s="115" t="s">
         <v>1</v>
       </c>
-      <c r="BI1" s="103"/>
-      <c r="BJ1" s="103"/>
-      <c r="BK1" s="104"/>
-      <c r="BL1" s="102" t="s">
+      <c r="BI1" s="116"/>
+      <c r="BJ1" s="116"/>
+      <c r="BK1" s="117"/>
+      <c r="BL1" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="BM1" s="103"/>
-      <c r="BN1" s="103"/>
-      <c r="BO1" s="104"/>
-      <c r="BP1" s="102" t="s">
+      <c r="BM1" s="116"/>
+      <c r="BN1" s="116"/>
+      <c r="BO1" s="117"/>
+      <c r="BP1" s="115" t="s">
         <v>3</v>
       </c>
-      <c r="BQ1" s="103"/>
-      <c r="BR1" s="103"/>
-      <c r="BS1" s="103"/>
-      <c r="BT1" s="104"/>
+      <c r="BQ1" s="116"/>
+      <c r="BR1" s="116"/>
+      <c r="BS1" s="116"/>
+      <c r="BT1" s="117"/>
     </row>
     <row r="2" spans="1:72" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
@@ -2872,2083 +3239,2211 @@
       <c r="AA2" s="1">
         <v>25</v>
       </c>
-      <c r="AB2" s="93">
+      <c r="AB2" s="21">
         <v>26</v>
       </c>
-      <c r="AC2" s="94">
+      <c r="AC2" s="22">
         <v>27</v>
       </c>
-      <c r="AD2" s="94">
+      <c r="AD2" s="22">
         <v>28</v>
       </c>
-      <c r="AE2" s="94">
+      <c r="AE2" s="22">
         <v>29</v>
       </c>
-      <c r="AF2" s="94">
+      <c r="AF2" s="22">
         <v>30</v>
       </c>
-      <c r="AG2" s="94">
+      <c r="AG2" s="22">
         <v>31</v>
       </c>
-      <c r="AH2" s="94">
+      <c r="AH2" s="22">
         <v>32</v>
       </c>
-      <c r="AI2" s="94">
+      <c r="AI2" s="22">
         <v>33</v>
       </c>
-      <c r="AJ2" s="94">
+      <c r="AJ2" s="22">
         <v>34</v>
       </c>
-      <c r="AK2" s="94">
+      <c r="AK2" s="22">
         <v>35</v>
       </c>
-      <c r="AL2" s="94">
+      <c r="AL2" s="22">
         <v>36</v>
       </c>
-      <c r="AM2" s="94">
+      <c r="AM2" s="22">
         <v>37</v>
       </c>
-      <c r="AN2" s="94">
+      <c r="AN2" s="22">
         <v>38</v>
       </c>
-      <c r="AO2" s="94">
+      <c r="AO2" s="22">
         <v>39</v>
       </c>
-      <c r="AP2" s="94">
+      <c r="AP2" s="22">
         <v>40</v>
       </c>
-      <c r="AQ2" s="94">
+      <c r="AQ2" s="22">
         <v>41</v>
       </c>
-      <c r="AR2" s="94">
+      <c r="AR2" s="22">
         <v>42</v>
       </c>
-      <c r="AS2" s="94">
+      <c r="AS2" s="22">
         <v>43</v>
       </c>
-      <c r="AT2" s="94">
+      <c r="AT2" s="22">
         <v>44</v>
       </c>
-      <c r="AU2" s="94">
+      <c r="AU2" s="22">
         <v>45</v>
       </c>
-      <c r="AV2" s="94">
+      <c r="AV2" s="22">
         <v>46</v>
       </c>
-      <c r="AW2" s="94">
+      <c r="AW2" s="22">
         <v>47</v>
       </c>
-      <c r="AX2" s="94">
+      <c r="AX2" s="22">
         <v>48</v>
       </c>
-      <c r="AY2" s="94">
+      <c r="AY2" s="22">
         <v>49</v>
       </c>
-      <c r="AZ2" s="94">
+      <c r="AZ2" s="22">
         <v>50</v>
       </c>
-      <c r="BA2" s="94">
+      <c r="BA2" s="22">
         <v>51</v>
       </c>
-      <c r="BB2" s="94">
+      <c r="BB2" s="22">
         <v>52</v>
       </c>
-      <c r="BC2" s="94">
+      <c r="BC2" s="22">
         <v>53</v>
       </c>
-      <c r="BD2" s="94">
+      <c r="BD2" s="22">
         <v>54</v>
       </c>
-      <c r="BE2" s="94">
+      <c r="BE2" s="22">
         <v>55</v>
       </c>
-      <c r="BF2" s="94">
+      <c r="BF2" s="22">
         <v>56</v>
       </c>
-      <c r="BG2" s="94">
+      <c r="BG2" s="22">
         <v>57</v>
       </c>
-      <c r="BH2" s="94">
+      <c r="BH2" s="22">
         <v>58</v>
       </c>
-      <c r="BI2" s="94">
+      <c r="BI2" s="22">
         <v>59</v>
       </c>
-      <c r="BJ2" s="94">
+      <c r="BJ2" s="22">
         <v>60</v>
       </c>
-      <c r="BK2" s="94">
+      <c r="BK2" s="22">
         <v>61</v>
       </c>
-      <c r="BL2" s="94">
+      <c r="BL2" s="22">
         <v>62</v>
       </c>
-      <c r="BM2" s="94">
+      <c r="BM2" s="22">
         <v>63</v>
       </c>
-      <c r="BN2" s="94">
+      <c r="BN2" s="22">
         <v>64</v>
       </c>
-      <c r="BO2" s="94">
+      <c r="BO2" s="22">
         <v>65</v>
       </c>
-      <c r="BP2" s="94">
+      <c r="BP2" s="22">
         <v>66</v>
       </c>
-      <c r="BQ2" s="94">
+      <c r="BQ2" s="22">
         <v>67</v>
       </c>
-      <c r="BR2" s="94">
+      <c r="BR2" s="22">
         <v>68</v>
       </c>
-      <c r="BS2" s="94">
+      <c r="BS2" s="22">
         <v>69</v>
       </c>
-      <c r="BT2" s="94">
+      <c r="BT2" s="22">
         <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:72" x14ac:dyDescent="0.3">
-      <c r="A3" s="73" t="s">
+      <c r="A3" s="92" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="89" t="s">
+      <c r="B3" s="110" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="77" t="s">
+      <c r="C3" s="96" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="78"/>
-      <c r="E3" s="78"/>
-      <c r="F3" s="78"/>
-      <c r="G3" s="78"/>
-      <c r="H3" s="78"/>
-      <c r="I3" s="78"/>
-      <c r="J3" s="78"/>
-      <c r="K3" s="81" t="s">
+      <c r="D3" s="97"/>
+      <c r="E3" s="97"/>
+      <c r="F3" s="97"/>
+      <c r="G3" s="97"/>
+      <c r="H3" s="97"/>
+      <c r="I3" s="97"/>
+      <c r="J3" s="97"/>
+      <c r="K3" s="100" t="s">
         <v>10</v>
       </c>
-      <c r="L3" s="81"/>
-      <c r="M3" s="81"/>
-      <c r="N3" s="81"/>
-      <c r="O3" s="81"/>
-      <c r="P3" s="81"/>
-      <c r="Q3" s="81"/>
-      <c r="R3" s="81"/>
-      <c r="S3" s="81"/>
-      <c r="T3" s="81"/>
-      <c r="U3" s="34" t="s">
+      <c r="L3" s="100"/>
+      <c r="M3" s="100"/>
+      <c r="N3" s="100"/>
+      <c r="O3" s="100"/>
+      <c r="P3" s="100"/>
+      <c r="Q3" s="100"/>
+      <c r="R3" s="100"/>
+      <c r="S3" s="100"/>
+      <c r="T3" s="100"/>
+      <c r="U3" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="V3" s="34"/>
-      <c r="W3" s="34"/>
-      <c r="X3" s="34"/>
-      <c r="Y3" s="34"/>
-      <c r="Z3" s="34"/>
-      <c r="AA3" s="34"/>
-      <c r="AB3" s="34"/>
-      <c r="AC3" s="120"/>
-      <c r="AD3" s="120"/>
-      <c r="AE3" s="120"/>
-      <c r="AF3" s="120"/>
-      <c r="AG3" s="120"/>
-      <c r="AH3" s="120"/>
-      <c r="AI3" s="120"/>
-      <c r="AJ3" s="120"/>
-      <c r="AK3" s="120"/>
-      <c r="AL3" s="120"/>
-      <c r="AM3" s="120"/>
-      <c r="AN3" s="120"/>
-      <c r="AO3" s="120"/>
-      <c r="AP3" s="120"/>
-      <c r="AQ3" s="120"/>
-      <c r="AR3" s="120"/>
-      <c r="AS3" s="120"/>
-      <c r="AT3" s="120"/>
-      <c r="AU3" s="120"/>
-      <c r="AV3" s="120"/>
-      <c r="AW3" s="120"/>
-      <c r="AX3" s="120"/>
-      <c r="AY3" s="120"/>
-      <c r="AZ3" s="120"/>
-      <c r="BA3" s="120"/>
-      <c r="BB3" s="120"/>
-      <c r="BC3" s="120"/>
-      <c r="BD3" s="120"/>
-      <c r="BE3" s="120"/>
-      <c r="BF3" s="120"/>
-      <c r="BG3" s="120"/>
-      <c r="BH3" s="120"/>
-      <c r="BI3" s="120"/>
-      <c r="BJ3" s="120"/>
-      <c r="BK3" s="120"/>
-      <c r="BL3" s="120"/>
-      <c r="BM3" s="120"/>
-      <c r="BN3" s="120"/>
-      <c r="BO3" s="120"/>
-      <c r="BP3" s="120"/>
-      <c r="BQ3" s="120"/>
-      <c r="BR3" s="120"/>
-      <c r="BS3" s="120"/>
-      <c r="BT3" s="120"/>
+      <c r="V3" s="50"/>
+      <c r="W3" s="50"/>
+      <c r="X3" s="50"/>
+      <c r="Y3" s="50"/>
+      <c r="Z3" s="50"/>
+      <c r="AA3" s="50"/>
+      <c r="AB3" s="50"/>
+      <c r="AC3" s="159" t="s">
+        <v>193</v>
+      </c>
+      <c r="AD3" s="160"/>
+      <c r="AE3" s="153" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF3" s="154"/>
+      <c r="AG3" s="154"/>
+      <c r="AH3" s="154"/>
+      <c r="AI3" s="154"/>
+      <c r="AJ3" s="154"/>
+      <c r="AK3" s="154"/>
+      <c r="AL3" s="154"/>
+      <c r="AM3" s="154"/>
+      <c r="AN3" s="154"/>
+      <c r="AO3" s="154"/>
+      <c r="AP3" s="154"/>
+      <c r="AQ3" s="154"/>
+      <c r="AR3" s="154"/>
+      <c r="AS3" s="154"/>
+      <c r="AT3" s="154"/>
+      <c r="AU3" s="154"/>
+      <c r="AV3" s="154"/>
+      <c r="AW3" s="154"/>
+      <c r="AX3" s="154"/>
+      <c r="AY3" s="154"/>
+      <c r="AZ3" s="154"/>
+      <c r="BA3" s="154"/>
+      <c r="BB3" s="154"/>
+      <c r="BC3" s="155"/>
+      <c r="BD3" s="147" t="s">
+        <v>10</v>
+      </c>
+      <c r="BE3" s="148"/>
+      <c r="BF3" s="148"/>
+      <c r="BG3" s="148"/>
+      <c r="BH3" s="148"/>
+      <c r="BI3" s="148"/>
+      <c r="BJ3" s="148"/>
+      <c r="BK3" s="148"/>
+      <c r="BL3" s="148"/>
+      <c r="BM3" s="149"/>
+      <c r="BN3" s="141" t="s">
+        <v>192</v>
+      </c>
+      <c r="BO3" s="142"/>
+      <c r="BP3" s="142"/>
+      <c r="BQ3" s="142"/>
+      <c r="BR3" s="142"/>
+      <c r="BS3" s="143"/>
+      <c r="BT3" s="118"/>
     </row>
     <row r="4" spans="1:72" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="73"/>
-      <c r="B4" s="89"/>
-      <c r="C4" s="79"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="80"/>
-      <c r="I4" s="80"/>
-      <c r="J4" s="80"/>
-      <c r="K4" s="82"/>
-      <c r="L4" s="82"/>
-      <c r="M4" s="82"/>
-      <c r="N4" s="82"/>
-      <c r="O4" s="82"/>
-      <c r="P4" s="82"/>
-      <c r="Q4" s="82"/>
-      <c r="R4" s="82"/>
-      <c r="S4" s="82"/>
-      <c r="T4" s="82"/>
-      <c r="U4" s="35"/>
-      <c r="V4" s="35"/>
-      <c r="W4" s="35"/>
-      <c r="X4" s="35"/>
-      <c r="Y4" s="35"/>
-      <c r="Z4" s="35"/>
-      <c r="AA4" s="35"/>
-      <c r="AB4" s="35"/>
-      <c r="AC4" s="121"/>
-      <c r="AD4" s="121"/>
-      <c r="AE4" s="121"/>
-      <c r="AF4" s="121"/>
-      <c r="AG4" s="121"/>
-      <c r="AH4" s="121"/>
-      <c r="AI4" s="121"/>
-      <c r="AJ4" s="121"/>
-      <c r="AK4" s="121"/>
-      <c r="AL4" s="121"/>
-      <c r="AM4" s="121"/>
-      <c r="AN4" s="121"/>
-      <c r="AO4" s="121"/>
-      <c r="AP4" s="121"/>
-      <c r="AQ4" s="121"/>
-      <c r="AR4" s="121"/>
-      <c r="AS4" s="121"/>
-      <c r="AT4" s="121"/>
-      <c r="AU4" s="121"/>
-      <c r="AV4" s="121"/>
-      <c r="AW4" s="121"/>
-      <c r="AX4" s="121"/>
-      <c r="AY4" s="121"/>
-      <c r="AZ4" s="121"/>
-      <c r="BA4" s="121"/>
-      <c r="BB4" s="121"/>
-      <c r="BC4" s="121"/>
-      <c r="BD4" s="121"/>
-      <c r="BE4" s="121"/>
-      <c r="BF4" s="121"/>
-      <c r="BG4" s="121"/>
-      <c r="BH4" s="121"/>
-      <c r="BI4" s="121"/>
-      <c r="BJ4" s="121"/>
-      <c r="BK4" s="121"/>
-      <c r="BL4" s="121"/>
-      <c r="BM4" s="121"/>
-      <c r="BN4" s="121"/>
-      <c r="BO4" s="121"/>
-      <c r="BP4" s="121"/>
-      <c r="BQ4" s="121"/>
-      <c r="BR4" s="121"/>
-      <c r="BS4" s="121"/>
-      <c r="BT4" s="121"/>
+      <c r="A4" s="92"/>
+      <c r="B4" s="110"/>
+      <c r="C4" s="98"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="99"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="99"/>
+      <c r="H4" s="99"/>
+      <c r="I4" s="99"/>
+      <c r="J4" s="99"/>
+      <c r="K4" s="101"/>
+      <c r="L4" s="101"/>
+      <c r="M4" s="101"/>
+      <c r="N4" s="101"/>
+      <c r="O4" s="101"/>
+      <c r="P4" s="101"/>
+      <c r="Q4" s="101"/>
+      <c r="R4" s="101"/>
+      <c r="S4" s="101"/>
+      <c r="T4" s="101"/>
+      <c r="U4" s="51"/>
+      <c r="V4" s="51"/>
+      <c r="W4" s="51"/>
+      <c r="X4" s="51"/>
+      <c r="Y4" s="51"/>
+      <c r="Z4" s="51"/>
+      <c r="AA4" s="51"/>
+      <c r="AB4" s="51"/>
+      <c r="AC4" s="161"/>
+      <c r="AD4" s="162"/>
+      <c r="AE4" s="156"/>
+      <c r="AF4" s="157"/>
+      <c r="AG4" s="157"/>
+      <c r="AH4" s="157"/>
+      <c r="AI4" s="157"/>
+      <c r="AJ4" s="157"/>
+      <c r="AK4" s="157"/>
+      <c r="AL4" s="157"/>
+      <c r="AM4" s="157"/>
+      <c r="AN4" s="157"/>
+      <c r="AO4" s="157"/>
+      <c r="AP4" s="157"/>
+      <c r="AQ4" s="157"/>
+      <c r="AR4" s="157"/>
+      <c r="AS4" s="157"/>
+      <c r="AT4" s="157"/>
+      <c r="AU4" s="157"/>
+      <c r="AV4" s="157"/>
+      <c r="AW4" s="157"/>
+      <c r="AX4" s="157"/>
+      <c r="AY4" s="157"/>
+      <c r="AZ4" s="157"/>
+      <c r="BA4" s="157"/>
+      <c r="BB4" s="157"/>
+      <c r="BC4" s="158"/>
+      <c r="BD4" s="150"/>
+      <c r="BE4" s="151"/>
+      <c r="BF4" s="151"/>
+      <c r="BG4" s="151"/>
+      <c r="BH4" s="151"/>
+      <c r="BI4" s="151"/>
+      <c r="BJ4" s="151"/>
+      <c r="BK4" s="151"/>
+      <c r="BL4" s="151"/>
+      <c r="BM4" s="152"/>
+      <c r="BN4" s="144"/>
+      <c r="BO4" s="145"/>
+      <c r="BP4" s="145"/>
+      <c r="BQ4" s="145"/>
+      <c r="BR4" s="145"/>
+      <c r="BS4" s="146"/>
+      <c r="BT4" s="119"/>
     </row>
     <row r="5" spans="1:72" x14ac:dyDescent="0.3">
-      <c r="A5" s="73"/>
-      <c r="B5" s="46" t="s">
+      <c r="A5" s="92"/>
+      <c r="B5" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="88" t="s">
+      <c r="C5" s="108" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="88"/>
-      <c r="E5" s="88"/>
-      <c r="F5" s="88"/>
-      <c r="G5" s="88"/>
-      <c r="H5" s="88"/>
-      <c r="I5" s="88" t="s">
+      <c r="D5" s="108"/>
+      <c r="E5" s="108"/>
+      <c r="F5" s="108"/>
+      <c r="G5" s="108"/>
+      <c r="H5" s="108"/>
+      <c r="I5" s="108" t="s">
         <v>11</v>
       </c>
-      <c r="J5" s="88"/>
-      <c r="K5" s="88"/>
-      <c r="L5" s="88"/>
-      <c r="M5" s="88"/>
-      <c r="N5" s="88"/>
-      <c r="O5" s="50" t="s">
+      <c r="J5" s="108"/>
+      <c r="K5" s="108"/>
+      <c r="L5" s="108"/>
+      <c r="M5" s="108"/>
+      <c r="N5" s="108"/>
+      <c r="O5" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="P5" s="51"/>
-      <c r="Q5" s="51"/>
-      <c r="R5" s="51"/>
-      <c r="S5" s="51"/>
-      <c r="T5" s="51"/>
-      <c r="U5" s="51"/>
-      <c r="V5" s="52"/>
-      <c r="W5" s="47" t="s">
+      <c r="P5" s="68"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="68"/>
+      <c r="S5" s="68"/>
+      <c r="T5" s="68"/>
+      <c r="U5" s="68"/>
+      <c r="V5" s="69"/>
+      <c r="W5" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="X5" s="48"/>
-      <c r="Y5" s="49"/>
-      <c r="Z5" s="87" t="s">
+      <c r="X5" s="65"/>
+      <c r="Y5" s="66"/>
+      <c r="Z5" s="107" t="s">
         <v>14</v>
       </c>
-      <c r="AA5" s="87"/>
-      <c r="AB5" s="117" t="s">
+      <c r="AA5" s="107"/>
+      <c r="AB5" s="94" t="s">
         <v>15</v>
       </c>
-      <c r="AC5" s="120"/>
-      <c r="AD5" s="120"/>
-      <c r="AE5" s="120"/>
-      <c r="AF5" s="120"/>
-      <c r="AG5" s="120"/>
-      <c r="AH5" s="120"/>
-      <c r="AI5" s="120"/>
-      <c r="AJ5" s="120"/>
-      <c r="AK5" s="120"/>
-      <c r="AL5" s="120"/>
-      <c r="AM5" s="120"/>
-      <c r="AN5" s="120"/>
-      <c r="AO5" s="120"/>
-      <c r="AP5" s="120"/>
-      <c r="AQ5" s="120"/>
-      <c r="AR5" s="120"/>
-      <c r="AS5" s="120"/>
-      <c r="AT5" s="120"/>
-      <c r="AU5" s="120"/>
-      <c r="AV5" s="120"/>
-      <c r="AW5" s="120"/>
-      <c r="AX5" s="120"/>
-      <c r="AY5" s="120"/>
-      <c r="AZ5" s="120"/>
-      <c r="BA5" s="120"/>
-      <c r="BB5" s="120"/>
-      <c r="BC5" s="120"/>
-      <c r="BD5" s="120"/>
-      <c r="BE5" s="120"/>
-      <c r="BF5" s="120"/>
-      <c r="BG5" s="120"/>
-      <c r="BH5" s="120"/>
-      <c r="BI5" s="120"/>
-      <c r="BJ5" s="120"/>
-      <c r="BK5" s="120"/>
-      <c r="BL5" s="120"/>
-      <c r="BM5" s="120"/>
-      <c r="BN5" s="120"/>
-      <c r="BO5" s="120"/>
-      <c r="BP5" s="120"/>
-      <c r="BQ5" s="120"/>
-      <c r="BR5" s="120"/>
-      <c r="BS5" s="120"/>
-      <c r="BT5" s="120"/>
+      <c r="AC5" s="159" t="s">
+        <v>193</v>
+      </c>
+      <c r="AD5" s="160"/>
+      <c r="AE5" s="171" t="s">
+        <v>11</v>
+      </c>
+      <c r="AF5" s="172"/>
+      <c r="AG5" s="172"/>
+      <c r="AH5" s="172"/>
+      <c r="AI5" s="172"/>
+      <c r="AJ5" s="173"/>
+      <c r="AK5" s="171" t="s">
+        <v>11</v>
+      </c>
+      <c r="AL5" s="172"/>
+      <c r="AM5" s="172"/>
+      <c r="AN5" s="172"/>
+      <c r="AO5" s="172"/>
+      <c r="AP5" s="173"/>
+      <c r="AQ5" s="171" t="s">
+        <v>11</v>
+      </c>
+      <c r="AR5" s="172"/>
+      <c r="AS5" s="172"/>
+      <c r="AT5" s="172"/>
+      <c r="AU5" s="172"/>
+      <c r="AV5" s="173"/>
+      <c r="AW5" s="171" t="s">
+        <v>11</v>
+      </c>
+      <c r="AX5" s="172"/>
+      <c r="AY5" s="172"/>
+      <c r="AZ5" s="172"/>
+      <c r="BA5" s="172"/>
+      <c r="BB5" s="172"/>
+      <c r="BC5" s="173"/>
+      <c r="BD5" s="177" t="s">
+        <v>12</v>
+      </c>
+      <c r="BE5" s="178"/>
+      <c r="BF5" s="178"/>
+      <c r="BG5" s="178"/>
+      <c r="BH5" s="178"/>
+      <c r="BI5" s="178"/>
+      <c r="BJ5" s="178"/>
+      <c r="BK5" s="178"/>
+      <c r="BL5" s="178"/>
+      <c r="BM5" s="179"/>
+      <c r="BN5" s="135" t="s">
+        <v>13</v>
+      </c>
+      <c r="BO5" s="136"/>
+      <c r="BP5" s="137"/>
+      <c r="BQ5" s="129" t="s">
+        <v>14</v>
+      </c>
+      <c r="BR5" s="130"/>
+      <c r="BS5" s="127" t="s">
+        <v>18</v>
+      </c>
+      <c r="BT5" s="118"/>
     </row>
     <row r="6" spans="1:72" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="73"/>
-      <c r="B6" s="46"/>
-      <c r="C6" s="88"/>
-      <c r="D6" s="88"/>
-      <c r="E6" s="88"/>
-      <c r="F6" s="88"/>
-      <c r="G6" s="88"/>
-      <c r="H6" s="88"/>
-      <c r="I6" s="88"/>
-      <c r="J6" s="88"/>
-      <c r="K6" s="88"/>
-      <c r="L6" s="88"/>
-      <c r="M6" s="88"/>
-      <c r="N6" s="88"/>
-      <c r="O6" s="53"/>
-      <c r="P6" s="54"/>
-      <c r="Q6" s="54"/>
-      <c r="R6" s="54"/>
-      <c r="S6" s="54"/>
-      <c r="T6" s="54"/>
-      <c r="U6" s="54"/>
-      <c r="V6" s="55"/>
-      <c r="W6" s="47"/>
-      <c r="X6" s="48"/>
-      <c r="Y6" s="49"/>
-      <c r="Z6" s="87"/>
-      <c r="AA6" s="87"/>
-      <c r="AB6" s="117"/>
-      <c r="AC6" s="121"/>
-      <c r="AD6" s="121"/>
-      <c r="AE6" s="121"/>
-      <c r="AF6" s="121"/>
-      <c r="AG6" s="121"/>
-      <c r="AH6" s="121"/>
-      <c r="AI6" s="121"/>
-      <c r="AJ6" s="121"/>
-      <c r="AK6" s="121"/>
-      <c r="AL6" s="121"/>
-      <c r="AM6" s="121"/>
-      <c r="AN6" s="121"/>
-      <c r="AO6" s="121"/>
-      <c r="AP6" s="121"/>
-      <c r="AQ6" s="121"/>
-      <c r="AR6" s="121"/>
-      <c r="AS6" s="121"/>
-      <c r="AT6" s="121"/>
-      <c r="AU6" s="121"/>
-      <c r="AV6" s="121"/>
-      <c r="AW6" s="121"/>
-      <c r="AX6" s="121"/>
-      <c r="AY6" s="121"/>
-      <c r="AZ6" s="121"/>
-      <c r="BA6" s="121"/>
-      <c r="BB6" s="121"/>
-      <c r="BC6" s="121"/>
-      <c r="BD6" s="121"/>
-      <c r="BE6" s="121"/>
-      <c r="BF6" s="121"/>
-      <c r="BG6" s="121"/>
-      <c r="BH6" s="121"/>
-      <c r="BI6" s="121"/>
-      <c r="BJ6" s="121"/>
-      <c r="BK6" s="121"/>
-      <c r="BL6" s="121"/>
-      <c r="BM6" s="121"/>
-      <c r="BN6" s="121"/>
-      <c r="BO6" s="121"/>
-      <c r="BP6" s="121"/>
-      <c r="BQ6" s="121"/>
-      <c r="BR6" s="121"/>
-      <c r="BS6" s="121"/>
-      <c r="BT6" s="121"/>
+      <c r="A6" s="92"/>
+      <c r="B6" s="62"/>
+      <c r="C6" s="108"/>
+      <c r="D6" s="108"/>
+      <c r="E6" s="108"/>
+      <c r="F6" s="108"/>
+      <c r="G6" s="108"/>
+      <c r="H6" s="108"/>
+      <c r="I6" s="108"/>
+      <c r="J6" s="108"/>
+      <c r="K6" s="108"/>
+      <c r="L6" s="108"/>
+      <c r="M6" s="108"/>
+      <c r="N6" s="108"/>
+      <c r="O6" s="70"/>
+      <c r="P6" s="71"/>
+      <c r="Q6" s="71"/>
+      <c r="R6" s="71"/>
+      <c r="S6" s="71"/>
+      <c r="T6" s="71"/>
+      <c r="U6" s="71"/>
+      <c r="V6" s="72"/>
+      <c r="W6" s="64"/>
+      <c r="X6" s="65"/>
+      <c r="Y6" s="66"/>
+      <c r="Z6" s="107"/>
+      <c r="AA6" s="107"/>
+      <c r="AB6" s="94"/>
+      <c r="AC6" s="161"/>
+      <c r="AD6" s="162"/>
+      <c r="AE6" s="174"/>
+      <c r="AF6" s="175"/>
+      <c r="AG6" s="175"/>
+      <c r="AH6" s="175"/>
+      <c r="AI6" s="175"/>
+      <c r="AJ6" s="176"/>
+      <c r="AK6" s="174"/>
+      <c r="AL6" s="175"/>
+      <c r="AM6" s="175"/>
+      <c r="AN6" s="175"/>
+      <c r="AO6" s="175"/>
+      <c r="AP6" s="176"/>
+      <c r="AQ6" s="174"/>
+      <c r="AR6" s="175"/>
+      <c r="AS6" s="175"/>
+      <c r="AT6" s="175"/>
+      <c r="AU6" s="175"/>
+      <c r="AV6" s="176"/>
+      <c r="AW6" s="174"/>
+      <c r="AX6" s="175"/>
+      <c r="AY6" s="175"/>
+      <c r="AZ6" s="175"/>
+      <c r="BA6" s="175"/>
+      <c r="BB6" s="175"/>
+      <c r="BC6" s="176"/>
+      <c r="BD6" s="180"/>
+      <c r="BE6" s="181"/>
+      <c r="BF6" s="181"/>
+      <c r="BG6" s="181"/>
+      <c r="BH6" s="181"/>
+      <c r="BI6" s="181"/>
+      <c r="BJ6" s="181"/>
+      <c r="BK6" s="181"/>
+      <c r="BL6" s="181"/>
+      <c r="BM6" s="182"/>
+      <c r="BN6" s="138"/>
+      <c r="BO6" s="139"/>
+      <c r="BP6" s="140"/>
+      <c r="BQ6" s="131"/>
+      <c r="BR6" s="132"/>
+      <c r="BS6" s="128"/>
+      <c r="BT6" s="119"/>
     </row>
     <row r="7" spans="1:72" x14ac:dyDescent="0.3">
-      <c r="A7" s="73"/>
-      <c r="B7" s="46" t="s">
+      <c r="A7" s="92"/>
+      <c r="B7" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="86" t="s">
+      <c r="C7" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="86" t="s">
+      <c r="D7" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="85" t="s">
+      <c r="E7" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="85" t="s">
+      <c r="F7" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="85" t="s">
+      <c r="G7" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="H7" s="85" t="s">
+      <c r="H7" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="I7" s="83" t="s">
+      <c r="I7" s="102" t="s">
         <v>22</v>
       </c>
-      <c r="J7" s="85" t="s">
+      <c r="J7" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="K7" s="85" t="s">
+      <c r="K7" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="L7" s="85" t="s">
+      <c r="L7" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="M7" s="85" t="s">
+      <c r="M7" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="N7" s="84" t="s">
+      <c r="N7" s="103" t="s">
         <v>19</v>
       </c>
-      <c r="O7" s="75" t="s">
+      <c r="O7" s="104" t="s">
         <v>21</v>
       </c>
-      <c r="P7" s="83" t="s">
+      <c r="P7" s="102" t="s">
         <v>22</v>
       </c>
-      <c r="Q7" s="56" t="s">
+      <c r="Q7" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="R7" s="56" t="s">
+      <c r="R7" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="S7" s="56" t="s">
+      <c r="S7" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="T7" s="56" t="s">
+      <c r="T7" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="U7" s="83" t="s">
+      <c r="U7" s="102" t="s">
         <v>22</v>
       </c>
-      <c r="V7" s="56" t="s">
+      <c r="V7" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="W7" s="56" t="s">
+      <c r="W7" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="X7" s="56" t="s">
+      <c r="X7" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="Y7" s="56" t="s">
+      <c r="Y7" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="Z7" s="84" t="s">
+      <c r="Z7" s="103" t="s">
         <v>19</v>
       </c>
-      <c r="AA7" s="84" t="s">
+      <c r="AA7" s="103" t="s">
         <v>19</v>
       </c>
-      <c r="AB7" s="117" t="s">
+      <c r="AB7" s="94" t="s">
         <v>18</v>
       </c>
-      <c r="AC7" s="120"/>
-      <c r="AD7" s="120"/>
-      <c r="AE7" s="120"/>
-      <c r="AF7" s="120"/>
-      <c r="AG7" s="120"/>
-      <c r="AH7" s="120"/>
-      <c r="AI7" s="120"/>
-      <c r="AJ7" s="120"/>
-      <c r="AK7" s="120"/>
-      <c r="AL7" s="120"/>
-      <c r="AM7" s="120"/>
-      <c r="AN7" s="120"/>
-      <c r="AO7" s="120"/>
-      <c r="AP7" s="120"/>
-      <c r="AQ7" s="120"/>
-      <c r="AR7" s="120"/>
-      <c r="AS7" s="120"/>
-      <c r="AT7" s="120"/>
-      <c r="AU7" s="120"/>
-      <c r="AV7" s="120"/>
-      <c r="AW7" s="120"/>
-      <c r="AX7" s="120"/>
-      <c r="AY7" s="120"/>
-      <c r="AZ7" s="120"/>
-      <c r="BA7" s="120"/>
-      <c r="BB7" s="120"/>
-      <c r="BC7" s="120"/>
-      <c r="BD7" s="120"/>
-      <c r="BE7" s="120"/>
-      <c r="BF7" s="120"/>
-      <c r="BG7" s="120"/>
-      <c r="BH7" s="120"/>
-      <c r="BI7" s="120"/>
-      <c r="BJ7" s="120"/>
-      <c r="BK7" s="120"/>
-      <c r="BL7" s="120"/>
-      <c r="BM7" s="120"/>
-      <c r="BN7" s="120"/>
-      <c r="BO7" s="120"/>
-      <c r="BP7" s="120"/>
-      <c r="BQ7" s="120"/>
-      <c r="BR7" s="120"/>
-      <c r="BS7" s="120"/>
-      <c r="BT7" s="120"/>
+      <c r="AC7" s="159" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD7" s="160"/>
+      <c r="AE7" s="165" t="s">
+        <v>17</v>
+      </c>
+      <c r="AF7" s="165" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG7" s="183" t="s">
+        <v>20</v>
+      </c>
+      <c r="AH7" s="183" t="s">
+        <v>20</v>
+      </c>
+      <c r="AI7" s="183" t="s">
+        <v>20</v>
+      </c>
+      <c r="AJ7" s="183" t="s">
+        <v>20</v>
+      </c>
+      <c r="AK7" s="167" t="s">
+        <v>19</v>
+      </c>
+      <c r="AL7" s="127" t="s">
+        <v>21</v>
+      </c>
+      <c r="AM7" s="163" t="s">
+        <v>22</v>
+      </c>
+      <c r="AN7" s="183" t="s">
+        <v>20</v>
+      </c>
+      <c r="AO7" s="183" t="s">
+        <v>20</v>
+      </c>
+      <c r="AP7" s="183" t="s">
+        <v>20</v>
+      </c>
+      <c r="AQ7" s="183" t="s">
+        <v>20</v>
+      </c>
+      <c r="AR7" s="167" t="s">
+        <v>19</v>
+      </c>
+      <c r="AS7" s="127" t="s">
+        <v>21</v>
+      </c>
+      <c r="AT7" s="163" t="s">
+        <v>22</v>
+      </c>
+      <c r="AU7" s="183" t="s">
+        <v>20</v>
+      </c>
+      <c r="AV7" s="183" t="s">
+        <v>20</v>
+      </c>
+      <c r="AW7" s="183" t="s">
+        <v>20</v>
+      </c>
+      <c r="AX7" s="183" t="s">
+        <v>20</v>
+      </c>
+      <c r="AY7" s="167" t="s">
+        <v>19</v>
+      </c>
+      <c r="AZ7" s="127" t="s">
+        <v>21</v>
+      </c>
+      <c r="BA7" s="163" t="s">
+        <v>22</v>
+      </c>
+      <c r="BB7" s="183" t="s">
+        <v>20</v>
+      </c>
+      <c r="BC7" s="183" t="s">
+        <v>20</v>
+      </c>
+      <c r="BD7" s="183" t="s">
+        <v>20</v>
+      </c>
+      <c r="BE7" s="183" t="s">
+        <v>20</v>
+      </c>
+      <c r="BF7" s="167" t="s">
+        <v>19</v>
+      </c>
+      <c r="BG7" s="127" t="s">
+        <v>21</v>
+      </c>
+      <c r="BH7" s="163" t="s">
+        <v>22</v>
+      </c>
+      <c r="BI7" s="183" t="s">
+        <v>20</v>
+      </c>
+      <c r="BJ7" s="183" t="s">
+        <v>20</v>
+      </c>
+      <c r="BK7" s="183" t="s">
+        <v>20</v>
+      </c>
+      <c r="BL7" s="163" t="s">
+        <v>22</v>
+      </c>
+      <c r="BM7" s="183" t="s">
+        <v>20</v>
+      </c>
+      <c r="BN7" s="183" t="s">
+        <v>20</v>
+      </c>
+      <c r="BO7" s="183" t="s">
+        <v>20</v>
+      </c>
+      <c r="BP7" s="183" t="s">
+        <v>20</v>
+      </c>
+      <c r="BQ7" s="167" t="s">
+        <v>19</v>
+      </c>
+      <c r="BR7" s="167" t="s">
+        <v>19</v>
+      </c>
+      <c r="BS7" s="127" t="s">
+        <v>18</v>
+      </c>
+      <c r="BT7" s="118"/>
     </row>
     <row r="8" spans="1:72" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="73"/>
-      <c r="B8" s="46"/>
-      <c r="C8" s="86"/>
-      <c r="D8" s="86"/>
-      <c r="E8" s="85"/>
-      <c r="F8" s="85"/>
-      <c r="G8" s="85"/>
-      <c r="H8" s="85"/>
-      <c r="I8" s="83"/>
-      <c r="J8" s="85"/>
-      <c r="K8" s="85"/>
-      <c r="L8" s="85"/>
-      <c r="M8" s="85"/>
-      <c r="N8" s="84"/>
-      <c r="O8" s="75"/>
-      <c r="P8" s="83"/>
-      <c r="Q8" s="56"/>
-      <c r="R8" s="56"/>
-      <c r="S8" s="56"/>
-      <c r="T8" s="56"/>
-      <c r="U8" s="83"/>
-      <c r="V8" s="56"/>
-      <c r="W8" s="56"/>
-      <c r="X8" s="56"/>
-      <c r="Y8" s="56"/>
-      <c r="Z8" s="84"/>
-      <c r="AA8" s="84"/>
-      <c r="AB8" s="117"/>
-      <c r="AC8" s="121"/>
-      <c r="AD8" s="121"/>
-      <c r="AE8" s="121"/>
-      <c r="AF8" s="121"/>
-      <c r="AG8" s="121"/>
-      <c r="AH8" s="121"/>
-      <c r="AI8" s="121"/>
-      <c r="AJ8" s="121"/>
-      <c r="AK8" s="121"/>
-      <c r="AL8" s="121"/>
-      <c r="AM8" s="121"/>
-      <c r="AN8" s="121"/>
-      <c r="AO8" s="121"/>
-      <c r="AP8" s="121"/>
-      <c r="AQ8" s="121"/>
-      <c r="AR8" s="121"/>
-      <c r="AS8" s="121"/>
-      <c r="AT8" s="121"/>
-      <c r="AU8" s="121"/>
-      <c r="AV8" s="121"/>
-      <c r="AW8" s="121"/>
-      <c r="AX8" s="121"/>
-      <c r="AY8" s="121"/>
-      <c r="AZ8" s="121"/>
-      <c r="BA8" s="121"/>
-      <c r="BB8" s="121"/>
-      <c r="BC8" s="121"/>
-      <c r="BD8" s="121"/>
-      <c r="BE8" s="121"/>
-      <c r="BF8" s="121"/>
-      <c r="BG8" s="121"/>
-      <c r="BH8" s="121"/>
-      <c r="BI8" s="121"/>
-      <c r="BJ8" s="121"/>
-      <c r="BK8" s="121"/>
-      <c r="BL8" s="121"/>
-      <c r="BM8" s="121"/>
-      <c r="BN8" s="121"/>
-      <c r="BO8" s="121"/>
-      <c r="BP8" s="121"/>
-      <c r="BQ8" s="121"/>
-      <c r="BR8" s="121"/>
-      <c r="BS8" s="121"/>
-      <c r="BT8" s="121"/>
+      <c r="A8" s="92"/>
+      <c r="B8" s="62"/>
+      <c r="C8" s="106"/>
+      <c r="D8" s="106"/>
+      <c r="E8" s="105"/>
+      <c r="F8" s="105"/>
+      <c r="G8" s="105"/>
+      <c r="H8" s="105"/>
+      <c r="I8" s="102"/>
+      <c r="J8" s="105"/>
+      <c r="K8" s="105"/>
+      <c r="L8" s="105"/>
+      <c r="M8" s="105"/>
+      <c r="N8" s="103"/>
+      <c r="O8" s="104"/>
+      <c r="P8" s="102"/>
+      <c r="Q8" s="73"/>
+      <c r="R8" s="73"/>
+      <c r="S8" s="73"/>
+      <c r="T8" s="73"/>
+      <c r="U8" s="102"/>
+      <c r="V8" s="73"/>
+      <c r="W8" s="73"/>
+      <c r="X8" s="73"/>
+      <c r="Y8" s="73"/>
+      <c r="Z8" s="103"/>
+      <c r="AA8" s="103"/>
+      <c r="AB8" s="94"/>
+      <c r="AC8" s="161"/>
+      <c r="AD8" s="162"/>
+      <c r="AE8" s="166"/>
+      <c r="AF8" s="166"/>
+      <c r="AG8" s="184"/>
+      <c r="AH8" s="184"/>
+      <c r="AI8" s="184"/>
+      <c r="AJ8" s="184"/>
+      <c r="AK8" s="168"/>
+      <c r="AL8" s="128"/>
+      <c r="AM8" s="164"/>
+      <c r="AN8" s="184"/>
+      <c r="AO8" s="184"/>
+      <c r="AP8" s="184"/>
+      <c r="AQ8" s="184"/>
+      <c r="AR8" s="168"/>
+      <c r="AS8" s="128"/>
+      <c r="AT8" s="164"/>
+      <c r="AU8" s="184"/>
+      <c r="AV8" s="184"/>
+      <c r="AW8" s="184"/>
+      <c r="AX8" s="184"/>
+      <c r="AY8" s="168"/>
+      <c r="AZ8" s="128"/>
+      <c r="BA8" s="164"/>
+      <c r="BB8" s="184"/>
+      <c r="BC8" s="184"/>
+      <c r="BD8" s="184"/>
+      <c r="BE8" s="184"/>
+      <c r="BF8" s="168"/>
+      <c r="BG8" s="128"/>
+      <c r="BH8" s="164"/>
+      <c r="BI8" s="184"/>
+      <c r="BJ8" s="184"/>
+      <c r="BK8" s="184"/>
+      <c r="BL8" s="164"/>
+      <c r="BM8" s="184"/>
+      <c r="BN8" s="184"/>
+      <c r="BO8" s="184"/>
+      <c r="BP8" s="184"/>
+      <c r="BQ8" s="168"/>
+      <c r="BR8" s="168"/>
+      <c r="BS8" s="128"/>
+      <c r="BT8" s="119"/>
     </row>
     <row r="9" spans="1:72" x14ac:dyDescent="0.3">
-      <c r="A9" s="73"/>
-      <c r="B9" s="76" t="s">
+      <c r="A9" s="92"/>
+      <c r="B9" s="95" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="46" t="s">
+      <c r="C9" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="46" t="s">
+      <c r="D9" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="46" t="s">
+      <c r="E9" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="F9" s="46" t="s">
+      <c r="F9" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="46" t="s">
+      <c r="G9" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="H9" s="46" t="s">
+      <c r="H9" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="I9" s="46" t="s">
+      <c r="I9" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="J9" s="46" t="s">
+      <c r="J9" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="K9" s="46" t="s">
+      <c r="K9" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="L9" s="46" t="s">
+      <c r="L9" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="M9" s="46" t="s">
+      <c r="M9" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="N9" s="46" t="s">
+      <c r="N9" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="O9" s="46" t="str">
+      <c r="O9" s="62" t="str">
         <f>N9</f>
         <v>Lundi</v>
       </c>
-      <c r="P9" s="46" t="str">
+      <c r="P9" s="62" t="str">
         <f>O9</f>
         <v>Lundi</v>
       </c>
-      <c r="Q9" s="46" t="str">
+      <c r="Q9" s="62" t="str">
         <f t="shared" ref="Q9:Z9" si="0">P9</f>
         <v>Lundi</v>
       </c>
-      <c r="R9" s="46" t="str">
+      <c r="R9" s="62" t="str">
         <f t="shared" si="0"/>
         <v>Lundi</v>
       </c>
-      <c r="S9" s="46" t="str">
+      <c r="S9" s="62" t="str">
         <f t="shared" si="0"/>
         <v>Lundi</v>
       </c>
-      <c r="T9" s="46" t="str">
+      <c r="T9" s="62" t="str">
         <f t="shared" si="0"/>
         <v>Lundi</v>
       </c>
-      <c r="U9" s="46" t="str">
+      <c r="U9" s="62" t="str">
         <f t="shared" si="0"/>
         <v>Lundi</v>
       </c>
-      <c r="V9" s="46" t="str">
+      <c r="V9" s="62" t="str">
         <f t="shared" si="0"/>
         <v>Lundi</v>
       </c>
-      <c r="W9" s="46" t="str">
+      <c r="W9" s="62" t="str">
         <f t="shared" si="0"/>
         <v>Lundi</v>
       </c>
-      <c r="X9" s="46" t="str">
+      <c r="X9" s="62" t="str">
         <f t="shared" si="0"/>
         <v>Lundi</v>
       </c>
-      <c r="Y9" s="46" t="str">
+      <c r="Y9" s="62" t="str">
         <f t="shared" si="0"/>
         <v>Lundi</v>
       </c>
-      <c r="Z9" s="46" t="str">
+      <c r="Z9" s="62" t="str">
         <f t="shared" si="0"/>
         <v>Lundi</v>
       </c>
-      <c r="AA9" s="46" t="str">
+      <c r="AA9" s="62" t="str">
         <f t="shared" ref="AA9" si="1">Z9</f>
         <v>Lundi</v>
       </c>
-      <c r="AB9" s="95" t="str">
+      <c r="AB9" s="63" t="str">
         <f t="shared" ref="AB9" si="2">AA9</f>
         <v>Lundi</v>
       </c>
-      <c r="AC9" s="120" t="str">
+      <c r="AC9" s="118" t="str">
         <f>AB9</f>
         <v>Lundi</v>
       </c>
-      <c r="AD9" s="120" t="str">
+      <c r="AD9" s="118" t="str">
         <f t="shared" ref="AD9:BT9" si="3">AC9</f>
         <v>Lundi</v>
       </c>
-      <c r="AE9" s="120" t="str">
+      <c r="AE9" s="118" t="str">
         <f t="shared" si="3"/>
         <v>Lundi</v>
       </c>
-      <c r="AF9" s="120" t="str">
+      <c r="AF9" s="118" t="str">
         <f t="shared" si="3"/>
         <v>Lundi</v>
       </c>
-      <c r="AG9" s="120" t="str">
+      <c r="AG9" s="118" t="str">
         <f t="shared" si="3"/>
         <v>Lundi</v>
       </c>
-      <c r="AH9" s="120" t="str">
+      <c r="AH9" s="118" t="str">
         <f t="shared" si="3"/>
         <v>Lundi</v>
       </c>
-      <c r="AI9" s="120" t="str">
+      <c r="AI9" s="118" t="str">
         <f t="shared" si="3"/>
         <v>Lundi</v>
       </c>
-      <c r="AJ9" s="120" t="str">
+      <c r="AJ9" s="118" t="str">
         <f t="shared" si="3"/>
         <v>Lundi</v>
       </c>
-      <c r="AK9" s="120" t="str">
+      <c r="AK9" s="118" t="str">
         <f t="shared" si="3"/>
         <v>Lundi</v>
       </c>
-      <c r="AL9" s="120" t="str">
+      <c r="AL9" s="118" t="str">
         <f t="shared" si="3"/>
         <v>Lundi</v>
       </c>
-      <c r="AM9" s="120" t="str">
+      <c r="AM9" s="118" t="str">
         <f t="shared" si="3"/>
         <v>Lundi</v>
       </c>
-      <c r="AN9" s="120" t="str">
+      <c r="AN9" s="118" t="str">
         <f t="shared" si="3"/>
         <v>Lundi</v>
       </c>
-      <c r="AO9" s="120" t="str">
+      <c r="AO9" s="118" t="str">
         <f t="shared" si="3"/>
         <v>Lundi</v>
       </c>
-      <c r="AP9" s="120" t="str">
+      <c r="AP9" s="118" t="str">
         <f t="shared" si="3"/>
         <v>Lundi</v>
       </c>
-      <c r="AQ9" s="120" t="str">
+      <c r="AQ9" s="118" t="str">
         <f t="shared" si="3"/>
         <v>Lundi</v>
       </c>
-      <c r="AR9" s="120" t="str">
+      <c r="AR9" s="118" t="str">
         <f t="shared" si="3"/>
         <v>Lundi</v>
       </c>
-      <c r="AS9" s="120" t="str">
+      <c r="AS9" s="118" t="str">
         <f t="shared" si="3"/>
         <v>Lundi</v>
       </c>
-      <c r="AT9" s="120" t="str">
+      <c r="AT9" s="118" t="str">
         <f t="shared" si="3"/>
         <v>Lundi</v>
       </c>
-      <c r="AU9" s="120" t="str">
+      <c r="AU9" s="118" t="str">
         <f t="shared" si="3"/>
         <v>Lundi</v>
       </c>
-      <c r="AV9" s="120" t="str">
+      <c r="AV9" s="118" t="str">
         <f t="shared" si="3"/>
         <v>Lundi</v>
       </c>
-      <c r="AW9" s="120" t="str">
+      <c r="AW9" s="118" t="str">
         <f t="shared" si="3"/>
         <v>Lundi</v>
       </c>
-      <c r="AX9" s="120" t="str">
+      <c r="AX9" s="118" t="str">
         <f t="shared" si="3"/>
         <v>Lundi</v>
       </c>
-      <c r="AY9" s="120" t="str">
+      <c r="AY9" s="118" t="str">
         <f t="shared" si="3"/>
         <v>Lundi</v>
       </c>
-      <c r="AZ9" s="120" t="str">
+      <c r="AZ9" s="118" t="str">
         <f t="shared" si="3"/>
         <v>Lundi</v>
       </c>
-      <c r="BA9" s="120" t="str">
+      <c r="BA9" s="118" t="str">
         <f t="shared" si="3"/>
         <v>Lundi</v>
       </c>
-      <c r="BB9" s="120" t="str">
+      <c r="BB9" s="118" t="str">
         <f t="shared" si="3"/>
         <v>Lundi</v>
       </c>
-      <c r="BC9" s="120" t="str">
+      <c r="BC9" s="118" t="str">
         <f t="shared" si="3"/>
         <v>Lundi</v>
       </c>
-      <c r="BD9" s="120" t="str">
+      <c r="BD9" s="118" t="str">
         <f t="shared" si="3"/>
         <v>Lundi</v>
       </c>
-      <c r="BE9" s="120" t="str">
+      <c r="BE9" s="118" t="str">
         <f t="shared" si="3"/>
         <v>Lundi</v>
       </c>
-      <c r="BF9" s="120" t="str">
+      <c r="BF9" s="118" t="str">
         <f t="shared" si="3"/>
         <v>Lundi</v>
       </c>
-      <c r="BG9" s="120" t="str">
+      <c r="BG9" s="118" t="str">
         <f t="shared" si="3"/>
         <v>Lundi</v>
       </c>
-      <c r="BH9" s="120" t="str">
+      <c r="BH9" s="118" t="str">
         <f t="shared" si="3"/>
         <v>Lundi</v>
       </c>
-      <c r="BI9" s="120" t="str">
+      <c r="BI9" s="118" t="str">
         <f t="shared" si="3"/>
         <v>Lundi</v>
       </c>
-      <c r="BJ9" s="120" t="str">
+      <c r="BJ9" s="169" t="str">
         <f t="shared" si="3"/>
         <v>Lundi</v>
       </c>
-      <c r="BK9" s="120" t="str">
+      <c r="BK9" s="118" t="str">
         <f t="shared" si="3"/>
         <v>Lundi</v>
       </c>
-      <c r="BL9" s="120" t="str">
+      <c r="BL9" s="118" t="str">
         <f t="shared" si="3"/>
         <v>Lundi</v>
       </c>
-      <c r="BM9" s="120" t="str">
+      <c r="BM9" s="118" t="str">
         <f t="shared" si="3"/>
         <v>Lundi</v>
       </c>
-      <c r="BN9" s="120" t="str">
+      <c r="BN9" s="118" t="str">
         <f t="shared" si="3"/>
         <v>Lundi</v>
       </c>
-      <c r="BO9" s="120" t="str">
+      <c r="BO9" s="118" t="str">
         <f t="shared" si="3"/>
         <v>Lundi</v>
       </c>
-      <c r="BP9" s="120" t="str">
+      <c r="BP9" s="118" t="str">
         <f t="shared" si="3"/>
         <v>Lundi</v>
       </c>
-      <c r="BQ9" s="120" t="str">
+      <c r="BQ9" s="118" t="str">
         <f t="shared" si="3"/>
         <v>Lundi</v>
       </c>
-      <c r="BR9" s="120" t="str">
+      <c r="BR9" s="118" t="str">
         <f t="shared" si="3"/>
         <v>Lundi</v>
       </c>
-      <c r="BS9" s="120" t="str">
+      <c r="BS9" s="118" t="str">
         <f t="shared" si="3"/>
         <v>Lundi</v>
       </c>
-      <c r="BT9" s="120" t="str">
+      <c r="BT9" s="118" t="str">
         <f t="shared" si="3"/>
         <v>Lundi</v>
       </c>
     </row>
     <row r="10" spans="1:72" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="73"/>
-      <c r="B10" s="76"/>
-      <c r="C10" s="46"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="46"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="46"/>
-      <c r="J10" s="46"/>
-      <c r="K10" s="46"/>
-      <c r="L10" s="46"/>
-      <c r="M10" s="46"/>
-      <c r="N10" s="46"/>
-      <c r="O10" s="46"/>
-      <c r="P10" s="46"/>
-      <c r="Q10" s="46"/>
-      <c r="R10" s="46"/>
-      <c r="S10" s="46"/>
-      <c r="T10" s="46"/>
-      <c r="U10" s="46"/>
-      <c r="V10" s="46"/>
-      <c r="W10" s="46"/>
-      <c r="X10" s="46"/>
-      <c r="Y10" s="46"/>
-      <c r="Z10" s="46"/>
-      <c r="AA10" s="46"/>
-      <c r="AB10" s="95"/>
-      <c r="AC10" s="121"/>
-      <c r="AD10" s="121"/>
-      <c r="AE10" s="121"/>
-      <c r="AF10" s="121"/>
-      <c r="AG10" s="121"/>
-      <c r="AH10" s="121"/>
-      <c r="AI10" s="121"/>
-      <c r="AJ10" s="121"/>
-      <c r="AK10" s="121"/>
-      <c r="AL10" s="121"/>
-      <c r="AM10" s="121"/>
-      <c r="AN10" s="121"/>
-      <c r="AO10" s="121"/>
-      <c r="AP10" s="121"/>
-      <c r="AQ10" s="121"/>
-      <c r="AR10" s="121"/>
-      <c r="AS10" s="121"/>
-      <c r="AT10" s="121"/>
-      <c r="AU10" s="121"/>
-      <c r="AV10" s="121"/>
-      <c r="AW10" s="121"/>
-      <c r="AX10" s="121"/>
-      <c r="AY10" s="121"/>
-      <c r="AZ10" s="121"/>
-      <c r="BA10" s="121"/>
-      <c r="BB10" s="121"/>
-      <c r="BC10" s="121"/>
-      <c r="BD10" s="121"/>
-      <c r="BE10" s="121"/>
-      <c r="BF10" s="121"/>
-      <c r="BG10" s="121"/>
-      <c r="BH10" s="121"/>
-      <c r="BI10" s="121"/>
-      <c r="BJ10" s="121"/>
-      <c r="BK10" s="121"/>
-      <c r="BL10" s="121"/>
-      <c r="BM10" s="121"/>
-      <c r="BN10" s="121"/>
-      <c r="BO10" s="121"/>
-      <c r="BP10" s="121"/>
-      <c r="BQ10" s="121"/>
-      <c r="BR10" s="121"/>
-      <c r="BS10" s="121"/>
-      <c r="BT10" s="121"/>
+      <c r="A10" s="92"/>
+      <c r="B10" s="95"/>
+      <c r="C10" s="62"/>
+      <c r="D10" s="62"/>
+      <c r="E10" s="62"/>
+      <c r="F10" s="62"/>
+      <c r="G10" s="62"/>
+      <c r="H10" s="62"/>
+      <c r="I10" s="62"/>
+      <c r="J10" s="62"/>
+      <c r="K10" s="62"/>
+      <c r="L10" s="62"/>
+      <c r="M10" s="62"/>
+      <c r="N10" s="62"/>
+      <c r="O10" s="62"/>
+      <c r="P10" s="62"/>
+      <c r="Q10" s="62"/>
+      <c r="R10" s="62"/>
+      <c r="S10" s="62"/>
+      <c r="T10" s="62"/>
+      <c r="U10" s="62"/>
+      <c r="V10" s="62"/>
+      <c r="W10" s="62"/>
+      <c r="X10" s="62"/>
+      <c r="Y10" s="62"/>
+      <c r="Z10" s="62"/>
+      <c r="AA10" s="62"/>
+      <c r="AB10" s="63"/>
+      <c r="AC10" s="119"/>
+      <c r="AD10" s="119"/>
+      <c r="AE10" s="119"/>
+      <c r="AF10" s="119"/>
+      <c r="AG10" s="119"/>
+      <c r="AH10" s="119"/>
+      <c r="AI10" s="119"/>
+      <c r="AJ10" s="119"/>
+      <c r="AK10" s="119"/>
+      <c r="AL10" s="119"/>
+      <c r="AM10" s="119"/>
+      <c r="AN10" s="119"/>
+      <c r="AO10" s="119"/>
+      <c r="AP10" s="119"/>
+      <c r="AQ10" s="119"/>
+      <c r="AR10" s="119"/>
+      <c r="AS10" s="119"/>
+      <c r="AT10" s="119"/>
+      <c r="AU10" s="119"/>
+      <c r="AV10" s="119"/>
+      <c r="AW10" s="119"/>
+      <c r="AX10" s="119"/>
+      <c r="AY10" s="119"/>
+      <c r="AZ10" s="119"/>
+      <c r="BA10" s="119"/>
+      <c r="BB10" s="119"/>
+      <c r="BC10" s="119"/>
+      <c r="BD10" s="119"/>
+      <c r="BE10" s="119"/>
+      <c r="BF10" s="119"/>
+      <c r="BG10" s="119"/>
+      <c r="BH10" s="119"/>
+      <c r="BI10" s="119"/>
+      <c r="BJ10" s="170"/>
+      <c r="BK10" s="119"/>
+      <c r="BL10" s="119"/>
+      <c r="BM10" s="119"/>
+      <c r="BN10" s="119"/>
+      <c r="BO10" s="119"/>
+      <c r="BP10" s="119"/>
+      <c r="BQ10" s="119"/>
+      <c r="BR10" s="119"/>
+      <c r="BS10" s="119"/>
+      <c r="BT10" s="119"/>
     </row>
     <row r="11" spans="1:72" x14ac:dyDescent="0.3">
-      <c r="A11" s="73"/>
-      <c r="B11" s="76" t="s">
+      <c r="A11" s="92"/>
+      <c r="B11" s="95" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="46" t="s">
+      <c r="C11" s="62" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="46"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="46"/>
-      <c r="H11" s="46"/>
-      <c r="I11" s="46"/>
-      <c r="J11" s="46"/>
-      <c r="K11" s="46" t="s">
+      <c r="D11" s="62"/>
+      <c r="E11" s="62"/>
+      <c r="F11" s="62"/>
+      <c r="G11" s="62"/>
+      <c r="H11" s="62"/>
+      <c r="I11" s="62"/>
+      <c r="J11" s="62"/>
+      <c r="K11" s="62" t="s">
         <v>28</v>
       </c>
-      <c r="L11" s="46"/>
-      <c r="M11" s="46"/>
-      <c r="N11" s="46" t="s">
+      <c r="L11" s="62"/>
+      <c r="M11" s="62"/>
+      <c r="N11" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="O11" s="46"/>
-      <c r="P11" s="46"/>
-      <c r="Q11" s="46"/>
-      <c r="R11" s="46"/>
-      <c r="S11" s="46"/>
-      <c r="T11" s="46"/>
-      <c r="U11" s="25" t="s">
+      <c r="O11" s="62"/>
+      <c r="P11" s="62"/>
+      <c r="Q11" s="62"/>
+      <c r="R11" s="62"/>
+      <c r="S11" s="62"/>
+      <c r="T11" s="62"/>
+      <c r="U11" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="V11" s="26"/>
-      <c r="W11" s="26"/>
-      <c r="X11" s="26"/>
-      <c r="Y11" s="27"/>
-      <c r="Z11" s="25" t="s">
+      <c r="V11" s="42"/>
+      <c r="W11" s="42"/>
+      <c r="X11" s="42"/>
+      <c r="Y11" s="43"/>
+      <c r="Z11" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="AA11" s="27"/>
-      <c r="AB11" s="117" t="s">
+      <c r="AA11" s="43"/>
+      <c r="AB11" s="94" t="s">
         <v>18</v>
       </c>
-      <c r="AC11" s="120"/>
-      <c r="AD11" s="120"/>
-      <c r="AE11" s="120"/>
-      <c r="AF11" s="120"/>
-      <c r="AG11" s="120"/>
-      <c r="AH11" s="120"/>
-      <c r="AI11" s="120"/>
-      <c r="AJ11" s="120"/>
-      <c r="AK11" s="120"/>
-      <c r="AL11" s="120"/>
-      <c r="AM11" s="120"/>
-      <c r="AN11" s="120"/>
-      <c r="AO11" s="120"/>
-      <c r="AP11" s="120"/>
-      <c r="AQ11" s="120"/>
-      <c r="AR11" s="120"/>
-      <c r="AS11" s="120"/>
-      <c r="AT11" s="120"/>
-      <c r="AU11" s="120"/>
-      <c r="AV11" s="120"/>
-      <c r="AW11" s="120"/>
-      <c r="AX11" s="120"/>
-      <c r="AY11" s="120"/>
-      <c r="AZ11" s="120"/>
-      <c r="BA11" s="120"/>
-      <c r="BB11" s="120"/>
-      <c r="BC11" s="120"/>
-      <c r="BD11" s="120"/>
-      <c r="BE11" s="120"/>
-      <c r="BF11" s="120"/>
-      <c r="BG11" s="120"/>
-      <c r="BH11" s="120"/>
-      <c r="BI11" s="120"/>
-      <c r="BJ11" s="120"/>
-      <c r="BK11" s="120"/>
-      <c r="BL11" s="120"/>
-      <c r="BM11" s="120"/>
-      <c r="BN11" s="120"/>
-      <c r="BO11" s="120"/>
-      <c r="BP11" s="120"/>
-      <c r="BQ11" s="120"/>
-      <c r="BR11" s="120"/>
-      <c r="BS11" s="120"/>
-      <c r="BT11" s="120"/>
+      <c r="AC11" s="159" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD11" s="160"/>
+      <c r="AE11" s="123" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF11" s="133"/>
+      <c r="AG11" s="133"/>
+      <c r="AH11" s="133"/>
+      <c r="AI11" s="133"/>
+      <c r="AJ11" s="133"/>
+      <c r="AK11" s="133"/>
+      <c r="AL11" s="133"/>
+      <c r="AM11" s="124"/>
+      <c r="AN11" s="123" t="s">
+        <v>28</v>
+      </c>
+      <c r="AO11" s="133"/>
+      <c r="AP11" s="133"/>
+      <c r="AQ11" s="133"/>
+      <c r="AR11" s="133"/>
+      <c r="AS11" s="124"/>
+      <c r="AT11" s="123" t="s">
+        <v>27</v>
+      </c>
+      <c r="AU11" s="133"/>
+      <c r="AV11" s="133"/>
+      <c r="AW11" s="133"/>
+      <c r="AX11" s="133"/>
+      <c r="AY11" s="133"/>
+      <c r="AZ11" s="124"/>
+      <c r="BA11" s="123" t="s">
+        <v>28</v>
+      </c>
+      <c r="BB11" s="133"/>
+      <c r="BC11" s="133"/>
+      <c r="BD11" s="133"/>
+      <c r="BE11" s="133"/>
+      <c r="BF11" s="133"/>
+      <c r="BG11" s="124"/>
+      <c r="BH11" s="123" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI11" s="133"/>
+      <c r="BJ11" s="133"/>
+      <c r="BK11" s="133"/>
+      <c r="BL11" s="133"/>
+      <c r="BM11" s="124"/>
+      <c r="BN11" s="123" t="s">
+        <v>194</v>
+      </c>
+      <c r="BO11" s="133"/>
+      <c r="BP11" s="124"/>
+      <c r="BQ11" s="123" t="s">
+        <v>31</v>
+      </c>
+      <c r="BR11" s="124"/>
+      <c r="BS11" s="127" t="s">
+        <v>18</v>
+      </c>
+      <c r="BT11" s="118"/>
     </row>
     <row r="12" spans="1:72" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="74"/>
-      <c r="B12" s="76"/>
-      <c r="C12" s="46"/>
-      <c r="D12" s="46"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="46"/>
-      <c r="G12" s="46"/>
-      <c r="H12" s="46"/>
-      <c r="I12" s="46"/>
-      <c r="J12" s="46"/>
-      <c r="K12" s="46"/>
-      <c r="L12" s="46"/>
-      <c r="M12" s="46"/>
-      <c r="N12" s="46"/>
-      <c r="O12" s="46"/>
-      <c r="P12" s="46"/>
-      <c r="Q12" s="46"/>
-      <c r="R12" s="46"/>
-      <c r="S12" s="46"/>
-      <c r="T12" s="46"/>
-      <c r="U12" s="28"/>
-      <c r="V12" s="29"/>
-      <c r="W12" s="29"/>
-      <c r="X12" s="29"/>
-      <c r="Y12" s="30"/>
-      <c r="Z12" s="28"/>
-      <c r="AA12" s="30"/>
-      <c r="AB12" s="117"/>
-      <c r="AC12" s="121"/>
-      <c r="AD12" s="121"/>
-      <c r="AE12" s="121"/>
-      <c r="AF12" s="121"/>
-      <c r="AG12" s="121"/>
-      <c r="AH12" s="121"/>
-      <c r="AI12" s="121"/>
-      <c r="AJ12" s="121"/>
-      <c r="AK12" s="121"/>
-      <c r="AL12" s="121"/>
-      <c r="AM12" s="121"/>
-      <c r="AN12" s="121"/>
-      <c r="AO12" s="121"/>
-      <c r="AP12" s="121"/>
-      <c r="AQ12" s="121"/>
-      <c r="AR12" s="121"/>
-      <c r="AS12" s="121"/>
-      <c r="AT12" s="121"/>
-      <c r="AU12" s="121"/>
-      <c r="AV12" s="121"/>
-      <c r="AW12" s="121"/>
-      <c r="AX12" s="121"/>
-      <c r="AY12" s="121"/>
-      <c r="AZ12" s="121"/>
-      <c r="BA12" s="121"/>
-      <c r="BB12" s="121"/>
-      <c r="BC12" s="121"/>
-      <c r="BD12" s="121"/>
-      <c r="BE12" s="121"/>
-      <c r="BF12" s="121"/>
-      <c r="BG12" s="121"/>
-      <c r="BH12" s="121"/>
-      <c r="BI12" s="121"/>
-      <c r="BJ12" s="121"/>
-      <c r="BK12" s="121"/>
-      <c r="BL12" s="121"/>
-      <c r="BM12" s="121"/>
-      <c r="BN12" s="121"/>
-      <c r="BO12" s="121"/>
-      <c r="BP12" s="121"/>
-      <c r="BQ12" s="121"/>
-      <c r="BR12" s="121"/>
-      <c r="BS12" s="121"/>
-      <c r="BT12" s="121"/>
+      <c r="A12" s="93"/>
+      <c r="B12" s="95"/>
+      <c r="C12" s="62"/>
+      <c r="D12" s="62"/>
+      <c r="E12" s="62"/>
+      <c r="F12" s="62"/>
+      <c r="G12" s="62"/>
+      <c r="H12" s="62"/>
+      <c r="I12" s="62"/>
+      <c r="J12" s="62"/>
+      <c r="K12" s="62"/>
+      <c r="L12" s="62"/>
+      <c r="M12" s="62"/>
+      <c r="N12" s="62"/>
+      <c r="O12" s="62"/>
+      <c r="P12" s="62"/>
+      <c r="Q12" s="62"/>
+      <c r="R12" s="62"/>
+      <c r="S12" s="62"/>
+      <c r="T12" s="62"/>
+      <c r="U12" s="44"/>
+      <c r="V12" s="45"/>
+      <c r="W12" s="45"/>
+      <c r="X12" s="45"/>
+      <c r="Y12" s="46"/>
+      <c r="Z12" s="44"/>
+      <c r="AA12" s="46"/>
+      <c r="AB12" s="94"/>
+      <c r="AC12" s="161"/>
+      <c r="AD12" s="162"/>
+      <c r="AE12" s="125"/>
+      <c r="AF12" s="134"/>
+      <c r="AG12" s="134"/>
+      <c r="AH12" s="134"/>
+      <c r="AI12" s="134"/>
+      <c r="AJ12" s="134"/>
+      <c r="AK12" s="134"/>
+      <c r="AL12" s="134"/>
+      <c r="AM12" s="126"/>
+      <c r="AN12" s="125"/>
+      <c r="AO12" s="134"/>
+      <c r="AP12" s="134"/>
+      <c r="AQ12" s="134"/>
+      <c r="AR12" s="134"/>
+      <c r="AS12" s="126"/>
+      <c r="AT12" s="125"/>
+      <c r="AU12" s="134"/>
+      <c r="AV12" s="134"/>
+      <c r="AW12" s="134"/>
+      <c r="AX12" s="134"/>
+      <c r="AY12" s="134"/>
+      <c r="AZ12" s="126"/>
+      <c r="BA12" s="125"/>
+      <c r="BB12" s="134"/>
+      <c r="BC12" s="134"/>
+      <c r="BD12" s="134"/>
+      <c r="BE12" s="134"/>
+      <c r="BF12" s="134"/>
+      <c r="BG12" s="126"/>
+      <c r="BH12" s="125"/>
+      <c r="BI12" s="134"/>
+      <c r="BJ12" s="134"/>
+      <c r="BK12" s="134"/>
+      <c r="BL12" s="134"/>
+      <c r="BM12" s="126"/>
+      <c r="BN12" s="125"/>
+      <c r="BO12" s="134"/>
+      <c r="BP12" s="126"/>
+      <c r="BQ12" s="125"/>
+      <c r="BR12" s="126"/>
+      <c r="BS12" s="128"/>
+      <c r="BT12" s="119"/>
     </row>
     <row r="13" spans="1:72" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="39" t="s">
+      <c r="A13" s="55" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="45" t="s">
+      <c r="B13" s="61" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="57" t="s">
+      <c r="C13" s="74" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="58"/>
-      <c r="E13" s="58"/>
-      <c r="F13" s="58"/>
-      <c r="G13" s="58"/>
-      <c r="H13" s="58"/>
-      <c r="I13" s="58"/>
-      <c r="J13" s="58"/>
-      <c r="K13" s="58"/>
-      <c r="L13" s="58"/>
-      <c r="M13" s="58"/>
-      <c r="N13" s="58"/>
-      <c r="O13" s="58"/>
-      <c r="P13" s="58"/>
-      <c r="Q13" s="58"/>
-      <c r="R13" s="58"/>
-      <c r="S13" s="58"/>
-      <c r="T13" s="58"/>
-      <c r="U13" s="58"/>
-      <c r="V13" s="58"/>
-      <c r="W13" s="58"/>
-      <c r="X13" s="58"/>
-      <c r="Y13" s="58"/>
-      <c r="Z13" s="58"/>
-      <c r="AA13" s="58"/>
-      <c r="AB13" s="58"/>
-      <c r="AC13" s="120"/>
-      <c r="AD13" s="120"/>
-      <c r="AE13" s="120"/>
-      <c r="AF13" s="120"/>
-      <c r="AG13" s="120"/>
-      <c r="AH13" s="120"/>
-      <c r="AI13" s="120"/>
-      <c r="AJ13" s="120"/>
-      <c r="AK13" s="120"/>
-      <c r="AL13" s="120"/>
-      <c r="AM13" s="120"/>
-      <c r="AN13" s="120"/>
-      <c r="AO13" s="120"/>
-      <c r="AP13" s="120"/>
-      <c r="AQ13" s="120"/>
-      <c r="AR13" s="120"/>
-      <c r="AS13" s="120"/>
-      <c r="AT13" s="120"/>
-      <c r="AU13" s="120"/>
-      <c r="AV13" s="120"/>
-      <c r="AW13" s="120"/>
-      <c r="AX13" s="120"/>
-      <c r="AY13" s="120"/>
-      <c r="AZ13" s="120"/>
-      <c r="BA13" s="120"/>
-      <c r="BB13" s="120"/>
-      <c r="BC13" s="120"/>
-      <c r="BD13" s="120"/>
-      <c r="BE13" s="120"/>
-      <c r="BF13" s="120"/>
-      <c r="BG13" s="120"/>
-      <c r="BH13" s="120"/>
-      <c r="BI13" s="120"/>
-      <c r="BJ13" s="120"/>
-      <c r="BK13" s="120"/>
-      <c r="BL13" s="120"/>
-      <c r="BM13" s="120"/>
-      <c r="BN13" s="120"/>
-      <c r="BO13" s="120"/>
-      <c r="BP13" s="120"/>
-      <c r="BQ13" s="120"/>
-      <c r="BR13" s="120"/>
-      <c r="BS13" s="120"/>
-      <c r="BT13" s="120"/>
+      <c r="D13" s="75"/>
+      <c r="E13" s="75"/>
+      <c r="F13" s="75"/>
+      <c r="G13" s="75"/>
+      <c r="H13" s="75"/>
+      <c r="I13" s="75"/>
+      <c r="J13" s="75"/>
+      <c r="K13" s="75"/>
+      <c r="L13" s="75"/>
+      <c r="M13" s="75"/>
+      <c r="N13" s="75"/>
+      <c r="O13" s="75"/>
+      <c r="P13" s="75"/>
+      <c r="Q13" s="75"/>
+      <c r="R13" s="75"/>
+      <c r="S13" s="75"/>
+      <c r="T13" s="75"/>
+      <c r="U13" s="75"/>
+      <c r="V13" s="75"/>
+      <c r="W13" s="75"/>
+      <c r="X13" s="75"/>
+      <c r="Y13" s="75"/>
+      <c r="Z13" s="75"/>
+      <c r="AA13" s="75"/>
+      <c r="AB13" s="75"/>
+      <c r="AC13" s="118"/>
+      <c r="AD13" s="118"/>
+      <c r="AE13" s="118"/>
+      <c r="AF13" s="118"/>
+      <c r="AG13" s="118"/>
+      <c r="AH13" s="118"/>
+      <c r="AI13" s="118"/>
+      <c r="AJ13" s="118"/>
+      <c r="AK13" s="118"/>
+      <c r="AL13" s="118"/>
+      <c r="AM13" s="118"/>
+      <c r="AN13" s="118"/>
+      <c r="AO13" s="118"/>
+      <c r="AP13" s="118"/>
+      <c r="AQ13" s="118"/>
+      <c r="AR13" s="118"/>
+      <c r="AS13" s="118"/>
+      <c r="AT13" s="118"/>
+      <c r="AU13" s="118"/>
+      <c r="AV13" s="118"/>
+      <c r="AW13" s="118"/>
+      <c r="AX13" s="118"/>
+      <c r="AY13" s="118"/>
+      <c r="AZ13" s="118"/>
+      <c r="BA13" s="118"/>
+      <c r="BB13" s="118"/>
+      <c r="BC13" s="118"/>
+      <c r="BD13" s="118"/>
+      <c r="BE13" s="118"/>
+      <c r="BF13" s="118"/>
+      <c r="BG13" s="118"/>
+      <c r="BH13" s="118"/>
+      <c r="BI13" s="118"/>
+      <c r="BJ13" s="118"/>
+      <c r="BK13" s="118"/>
+      <c r="BL13" s="118"/>
+      <c r="BM13" s="118"/>
+      <c r="BN13" s="118"/>
+      <c r="BO13" s="118"/>
+      <c r="BP13" s="118"/>
+      <c r="BQ13" s="118"/>
+      <c r="BR13" s="118"/>
+      <c r="BS13" s="118"/>
+      <c r="BT13" s="118"/>
     </row>
     <row r="14" spans="1:72" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="40"/>
-      <c r="B14" s="45"/>
-      <c r="C14" s="59"/>
-      <c r="D14" s="60"/>
-      <c r="E14" s="60"/>
-      <c r="F14" s="60"/>
-      <c r="G14" s="60"/>
-      <c r="H14" s="60"/>
-      <c r="I14" s="60"/>
-      <c r="J14" s="60"/>
-      <c r="K14" s="60"/>
-      <c r="L14" s="60"/>
-      <c r="M14" s="60"/>
-      <c r="N14" s="60"/>
-      <c r="O14" s="60"/>
-      <c r="P14" s="60"/>
-      <c r="Q14" s="60"/>
-      <c r="R14" s="60"/>
-      <c r="S14" s="60"/>
-      <c r="T14" s="60"/>
-      <c r="U14" s="60"/>
-      <c r="V14" s="60"/>
-      <c r="W14" s="60"/>
-      <c r="X14" s="60"/>
-      <c r="Y14" s="60"/>
-      <c r="Z14" s="60"/>
-      <c r="AA14" s="60"/>
-      <c r="AB14" s="60"/>
-      <c r="AC14" s="121"/>
-      <c r="AD14" s="121"/>
-      <c r="AE14" s="121"/>
-      <c r="AF14" s="121"/>
-      <c r="AG14" s="121"/>
-      <c r="AH14" s="121"/>
-      <c r="AI14" s="121"/>
-      <c r="AJ14" s="121"/>
-      <c r="AK14" s="121"/>
-      <c r="AL14" s="121"/>
-      <c r="AM14" s="121"/>
-      <c r="AN14" s="121"/>
-      <c r="AO14" s="121"/>
-      <c r="AP14" s="121"/>
-      <c r="AQ14" s="121"/>
-      <c r="AR14" s="121"/>
-      <c r="AS14" s="121"/>
-      <c r="AT14" s="121"/>
-      <c r="AU14" s="121"/>
-      <c r="AV14" s="121"/>
-      <c r="AW14" s="121"/>
-      <c r="AX14" s="121"/>
-      <c r="AY14" s="121"/>
-      <c r="AZ14" s="121"/>
-      <c r="BA14" s="121"/>
-      <c r="BB14" s="121"/>
-      <c r="BC14" s="121"/>
-      <c r="BD14" s="121"/>
-      <c r="BE14" s="121"/>
-      <c r="BF14" s="121"/>
-      <c r="BG14" s="121"/>
-      <c r="BH14" s="121"/>
-      <c r="BI14" s="121"/>
-      <c r="BJ14" s="121"/>
-      <c r="BK14" s="121"/>
-      <c r="BL14" s="121"/>
-      <c r="BM14" s="121"/>
-      <c r="BN14" s="121"/>
-      <c r="BO14" s="121"/>
-      <c r="BP14" s="121"/>
-      <c r="BQ14" s="121"/>
-      <c r="BR14" s="121"/>
-      <c r="BS14" s="121"/>
-      <c r="BT14" s="121"/>
+      <c r="A14" s="56"/>
+      <c r="B14" s="61"/>
+      <c r="C14" s="76"/>
+      <c r="D14" s="77"/>
+      <c r="E14" s="77"/>
+      <c r="F14" s="77"/>
+      <c r="G14" s="77"/>
+      <c r="H14" s="77"/>
+      <c r="I14" s="77"/>
+      <c r="J14" s="77"/>
+      <c r="K14" s="77"/>
+      <c r="L14" s="77"/>
+      <c r="M14" s="77"/>
+      <c r="N14" s="77"/>
+      <c r="O14" s="77"/>
+      <c r="P14" s="77"/>
+      <c r="Q14" s="77"/>
+      <c r="R14" s="77"/>
+      <c r="S14" s="77"/>
+      <c r="T14" s="77"/>
+      <c r="U14" s="77"/>
+      <c r="V14" s="77"/>
+      <c r="W14" s="77"/>
+      <c r="X14" s="77"/>
+      <c r="Y14" s="77"/>
+      <c r="Z14" s="77"/>
+      <c r="AA14" s="77"/>
+      <c r="AB14" s="77"/>
+      <c r="AC14" s="119"/>
+      <c r="AD14" s="119"/>
+      <c r="AE14" s="119"/>
+      <c r="AF14" s="119"/>
+      <c r="AG14" s="119"/>
+      <c r="AH14" s="119"/>
+      <c r="AI14" s="119"/>
+      <c r="AJ14" s="119"/>
+      <c r="AK14" s="119"/>
+      <c r="AL14" s="119"/>
+      <c r="AM14" s="119"/>
+      <c r="AN14" s="119"/>
+      <c r="AO14" s="119"/>
+      <c r="AP14" s="119"/>
+      <c r="AQ14" s="119"/>
+      <c r="AR14" s="119"/>
+      <c r="AS14" s="119"/>
+      <c r="AT14" s="119"/>
+      <c r="AU14" s="119"/>
+      <c r="AV14" s="119"/>
+      <c r="AW14" s="119"/>
+      <c r="AX14" s="119"/>
+      <c r="AY14" s="119"/>
+      <c r="AZ14" s="119"/>
+      <c r="BA14" s="119"/>
+      <c r="BB14" s="119"/>
+      <c r="BC14" s="119"/>
+      <c r="BD14" s="119"/>
+      <c r="BE14" s="119"/>
+      <c r="BF14" s="119"/>
+      <c r="BG14" s="119"/>
+      <c r="BH14" s="119"/>
+      <c r="BI14" s="119"/>
+      <c r="BJ14" s="119"/>
+      <c r="BK14" s="119"/>
+      <c r="BL14" s="119"/>
+      <c r="BM14" s="119"/>
+      <c r="BN14" s="119"/>
+      <c r="BO14" s="119"/>
+      <c r="BP14" s="119"/>
+      <c r="BQ14" s="119"/>
+      <c r="BR14" s="119"/>
+      <c r="BS14" s="119"/>
+      <c r="BT14" s="119"/>
     </row>
     <row r="15" spans="1:72" x14ac:dyDescent="0.3">
-      <c r="A15" s="40"/>
-      <c r="B15" s="45" t="s">
+      <c r="A15" s="56"/>
+      <c r="B15" s="61" t="s">
         <v>35</v>
       </c>
-      <c r="C15" s="41"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="41"/>
-      <c r="I15" s="41"/>
-      <c r="J15" s="41"/>
-      <c r="K15" s="46"/>
-      <c r="L15" s="46"/>
-      <c r="M15" s="46"/>
-      <c r="N15" s="46"/>
-      <c r="O15" s="46"/>
-      <c r="P15" s="63"/>
-      <c r="Q15" s="64"/>
-      <c r="R15" s="64"/>
-      <c r="S15" s="64"/>
-      <c r="T15" s="64"/>
-      <c r="U15" s="64"/>
-      <c r="V15" s="64"/>
-      <c r="W15" s="64"/>
-      <c r="X15" s="64"/>
-      <c r="Y15" s="65"/>
-      <c r="Z15" s="71"/>
-      <c r="AA15" s="72"/>
-      <c r="AB15" s="118"/>
-      <c r="AC15" s="120"/>
-      <c r="AD15" s="120"/>
-      <c r="AE15" s="120"/>
-      <c r="AF15" s="120"/>
-      <c r="AG15" s="120"/>
-      <c r="AH15" s="120"/>
-      <c r="AI15" s="120"/>
-      <c r="AJ15" s="120"/>
-      <c r="AK15" s="120"/>
-      <c r="AL15" s="120"/>
-      <c r="AM15" s="120"/>
-      <c r="AN15" s="120"/>
-      <c r="AO15" s="120"/>
-      <c r="AP15" s="120"/>
-      <c r="AQ15" s="120"/>
-      <c r="AR15" s="120"/>
-      <c r="AS15" s="120"/>
-      <c r="AT15" s="120"/>
-      <c r="AU15" s="120"/>
-      <c r="AV15" s="120"/>
-      <c r="AW15" s="120"/>
-      <c r="AX15" s="120"/>
-      <c r="AY15" s="120"/>
-      <c r="AZ15" s="120"/>
-      <c r="BA15" s="120"/>
-      <c r="BB15" s="120"/>
-      <c r="BC15" s="120"/>
-      <c r="BD15" s="120"/>
-      <c r="BE15" s="120"/>
-      <c r="BF15" s="120"/>
-      <c r="BG15" s="120"/>
-      <c r="BH15" s="120"/>
-      <c r="BI15" s="120"/>
-      <c r="BJ15" s="120"/>
-      <c r="BK15" s="120"/>
-      <c r="BL15" s="120"/>
-      <c r="BM15" s="120"/>
-      <c r="BN15" s="120"/>
-      <c r="BO15" s="120"/>
-      <c r="BP15" s="120"/>
-      <c r="BQ15" s="120"/>
-      <c r="BR15" s="120"/>
-      <c r="BS15" s="120"/>
-      <c r="BT15" s="120"/>
+      <c r="C15" s="57"/>
+      <c r="D15" s="57"/>
+      <c r="E15" s="57"/>
+      <c r="F15" s="57"/>
+      <c r="G15" s="57"/>
+      <c r="H15" s="57"/>
+      <c r="I15" s="57"/>
+      <c r="J15" s="57"/>
+      <c r="K15" s="62"/>
+      <c r="L15" s="62"/>
+      <c r="M15" s="62"/>
+      <c r="N15" s="62"/>
+      <c r="O15" s="62"/>
+      <c r="P15" s="80"/>
+      <c r="Q15" s="81"/>
+      <c r="R15" s="81"/>
+      <c r="S15" s="81"/>
+      <c r="T15" s="81"/>
+      <c r="U15" s="81"/>
+      <c r="V15" s="81"/>
+      <c r="W15" s="81"/>
+      <c r="X15" s="81"/>
+      <c r="Y15" s="82"/>
+      <c r="Z15" s="90"/>
+      <c r="AA15" s="91"/>
+      <c r="AB15" s="87"/>
+      <c r="AC15" s="118"/>
+      <c r="AD15" s="118"/>
+      <c r="AE15" s="118"/>
+      <c r="AF15" s="118"/>
+      <c r="AG15" s="118"/>
+      <c r="AH15" s="118"/>
+      <c r="AI15" s="118"/>
+      <c r="AJ15" s="118"/>
+      <c r="AK15" s="118"/>
+      <c r="AL15" s="118"/>
+      <c r="AM15" s="118"/>
+      <c r="AN15" s="118"/>
+      <c r="AO15" s="118"/>
+      <c r="AP15" s="118"/>
+      <c r="AQ15" s="118"/>
+      <c r="AR15" s="118"/>
+      <c r="AS15" s="118"/>
+      <c r="AT15" s="118"/>
+      <c r="AU15" s="118"/>
+      <c r="AV15" s="118"/>
+      <c r="AW15" s="118"/>
+      <c r="AX15" s="118"/>
+      <c r="AY15" s="118"/>
+      <c r="AZ15" s="118"/>
+      <c r="BA15" s="118"/>
+      <c r="BB15" s="118"/>
+      <c r="BC15" s="118"/>
+      <c r="BD15" s="118"/>
+      <c r="BE15" s="118"/>
+      <c r="BF15" s="118"/>
+      <c r="BG15" s="118"/>
+      <c r="BH15" s="118"/>
+      <c r="BI15" s="118"/>
+      <c r="BJ15" s="118"/>
+      <c r="BK15" s="118"/>
+      <c r="BL15" s="118"/>
+      <c r="BM15" s="118"/>
+      <c r="BN15" s="185"/>
+      <c r="BO15" s="118"/>
+      <c r="BP15" s="118"/>
+      <c r="BQ15" s="118"/>
+      <c r="BR15" s="118"/>
+      <c r="BS15" s="118"/>
+      <c r="BT15" s="118"/>
     </row>
     <row r="16" spans="1:72" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="40"/>
-      <c r="B16" s="45"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="41"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="41"/>
-      <c r="I16" s="41"/>
-      <c r="J16" s="41"/>
-      <c r="K16" s="46"/>
-      <c r="L16" s="46"/>
-      <c r="M16" s="46"/>
-      <c r="N16" s="46"/>
-      <c r="O16" s="46"/>
-      <c r="P16" s="66"/>
-      <c r="Q16" s="67"/>
-      <c r="R16" s="67"/>
-      <c r="S16" s="67"/>
-      <c r="T16" s="67"/>
-      <c r="U16" s="67"/>
-      <c r="V16" s="67"/>
-      <c r="W16" s="67"/>
-      <c r="X16" s="67"/>
-      <c r="Y16" s="68"/>
-      <c r="Z16" s="71"/>
-      <c r="AA16" s="72"/>
-      <c r="AB16" s="118"/>
-      <c r="AC16" s="121"/>
-      <c r="AD16" s="121"/>
-      <c r="AE16" s="121"/>
-      <c r="AF16" s="121"/>
-      <c r="AG16" s="121"/>
-      <c r="AH16" s="121"/>
-      <c r="AI16" s="121"/>
-      <c r="AJ16" s="121"/>
-      <c r="AK16" s="121"/>
-      <c r="AL16" s="121"/>
-      <c r="AM16" s="121"/>
-      <c r="AN16" s="121"/>
-      <c r="AO16" s="121"/>
-      <c r="AP16" s="121"/>
-      <c r="AQ16" s="121"/>
-      <c r="AR16" s="121"/>
-      <c r="AS16" s="121"/>
-      <c r="AT16" s="121"/>
-      <c r="AU16" s="121"/>
-      <c r="AV16" s="121"/>
-      <c r="AW16" s="121"/>
-      <c r="AX16" s="121"/>
-      <c r="AY16" s="121"/>
-      <c r="AZ16" s="121"/>
-      <c r="BA16" s="121"/>
-      <c r="BB16" s="121"/>
-      <c r="BC16" s="121"/>
-      <c r="BD16" s="121"/>
-      <c r="BE16" s="121"/>
-      <c r="BF16" s="121"/>
-      <c r="BG16" s="121"/>
-      <c r="BH16" s="121"/>
-      <c r="BI16" s="121"/>
-      <c r="BJ16" s="121"/>
-      <c r="BK16" s="121"/>
-      <c r="BL16" s="121"/>
-      <c r="BM16" s="121"/>
-      <c r="BN16" s="121"/>
-      <c r="BO16" s="121"/>
-      <c r="BP16" s="121"/>
-      <c r="BQ16" s="121"/>
-      <c r="BR16" s="121"/>
-      <c r="BS16" s="121"/>
-      <c r="BT16" s="121"/>
+      <c r="A16" s="56"/>
+      <c r="B16" s="61"/>
+      <c r="C16" s="57"/>
+      <c r="D16" s="57"/>
+      <c r="E16" s="57"/>
+      <c r="F16" s="57"/>
+      <c r="G16" s="57"/>
+      <c r="H16" s="57"/>
+      <c r="I16" s="57"/>
+      <c r="J16" s="57"/>
+      <c r="K16" s="62"/>
+      <c r="L16" s="62"/>
+      <c r="M16" s="62"/>
+      <c r="N16" s="62"/>
+      <c r="O16" s="62"/>
+      <c r="P16" s="83"/>
+      <c r="Q16" s="84"/>
+      <c r="R16" s="84"/>
+      <c r="S16" s="84"/>
+      <c r="T16" s="84"/>
+      <c r="U16" s="84"/>
+      <c r="V16" s="84"/>
+      <c r="W16" s="84"/>
+      <c r="X16" s="84"/>
+      <c r="Y16" s="85"/>
+      <c r="Z16" s="90"/>
+      <c r="AA16" s="91"/>
+      <c r="AB16" s="87"/>
+      <c r="AC16" s="119"/>
+      <c r="AD16" s="119"/>
+      <c r="AE16" s="119"/>
+      <c r="AF16" s="119"/>
+      <c r="AG16" s="119"/>
+      <c r="AH16" s="119"/>
+      <c r="AI16" s="119"/>
+      <c r="AJ16" s="119"/>
+      <c r="AK16" s="119"/>
+      <c r="AL16" s="119"/>
+      <c r="AM16" s="119"/>
+      <c r="AN16" s="119"/>
+      <c r="AO16" s="119"/>
+      <c r="AP16" s="119"/>
+      <c r="AQ16" s="119"/>
+      <c r="AR16" s="119"/>
+      <c r="AS16" s="119"/>
+      <c r="AT16" s="119"/>
+      <c r="AU16" s="119"/>
+      <c r="AV16" s="119"/>
+      <c r="AW16" s="119"/>
+      <c r="AX16" s="119"/>
+      <c r="AY16" s="119"/>
+      <c r="AZ16" s="119"/>
+      <c r="BA16" s="119"/>
+      <c r="BB16" s="119"/>
+      <c r="BC16" s="119"/>
+      <c r="BD16" s="119"/>
+      <c r="BE16" s="119"/>
+      <c r="BF16" s="119"/>
+      <c r="BG16" s="119"/>
+      <c r="BH16" s="119"/>
+      <c r="BI16" s="119"/>
+      <c r="BJ16" s="119"/>
+      <c r="BK16" s="119"/>
+      <c r="BL16" s="119"/>
+      <c r="BM16" s="119"/>
+      <c r="BN16" s="186"/>
+      <c r="BO16" s="119"/>
+      <c r="BP16" s="119"/>
+      <c r="BQ16" s="119"/>
+      <c r="BR16" s="119"/>
+      <c r="BS16" s="119"/>
+      <c r="BT16" s="119"/>
     </row>
     <row r="17" spans="1:72" x14ac:dyDescent="0.3">
-      <c r="A17" s="40"/>
-      <c r="B17" s="45" t="s">
+      <c r="A17" s="56"/>
+      <c r="B17" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="46"/>
-      <c r="D17" s="46"/>
-      <c r="E17" s="46"/>
-      <c r="F17" s="46"/>
-      <c r="G17" s="46"/>
-      <c r="H17" s="46"/>
-      <c r="I17" s="46"/>
-      <c r="J17" s="46"/>
-      <c r="K17" s="46"/>
-      <c r="L17" s="41"/>
-      <c r="M17" s="41"/>
-      <c r="N17" s="41"/>
-      <c r="O17" s="41"/>
-      <c r="P17" s="46"/>
-      <c r="Q17" s="42"/>
-      <c r="R17" s="42"/>
-      <c r="S17" s="42"/>
-      <c r="T17" s="42"/>
-      <c r="U17" s="46"/>
-      <c r="V17" s="46"/>
-      <c r="W17" s="46"/>
-      <c r="X17" s="46"/>
-      <c r="Y17" s="46"/>
-      <c r="Z17" s="71"/>
-      <c r="AA17" s="72"/>
-      <c r="AB17" s="118"/>
-      <c r="AC17" s="120"/>
-      <c r="AD17" s="120"/>
-      <c r="AE17" s="120"/>
-      <c r="AF17" s="120"/>
-      <c r="AG17" s="120"/>
-      <c r="AH17" s="120"/>
-      <c r="AI17" s="120"/>
-      <c r="AJ17" s="120"/>
-      <c r="AK17" s="120"/>
-      <c r="AL17" s="120"/>
-      <c r="AM17" s="120"/>
-      <c r="AN17" s="120"/>
-      <c r="AO17" s="120"/>
-      <c r="AP17" s="120"/>
-      <c r="AQ17" s="120"/>
-      <c r="AR17" s="120"/>
-      <c r="AS17" s="120"/>
-      <c r="AT17" s="120"/>
-      <c r="AU17" s="120"/>
-      <c r="AV17" s="120"/>
-      <c r="AW17" s="120"/>
-      <c r="AX17" s="120"/>
-      <c r="AY17" s="120"/>
-      <c r="AZ17" s="120"/>
-      <c r="BA17" s="120"/>
-      <c r="BB17" s="120"/>
-      <c r="BC17" s="120"/>
-      <c r="BD17" s="120"/>
-      <c r="BE17" s="120"/>
-      <c r="BF17" s="120"/>
-      <c r="BG17" s="120"/>
-      <c r="BH17" s="120"/>
-      <c r="BI17" s="120"/>
-      <c r="BJ17" s="120"/>
-      <c r="BK17" s="120"/>
-      <c r="BL17" s="120"/>
-      <c r="BM17" s="120"/>
-      <c r="BN17" s="120"/>
-      <c r="BO17" s="120"/>
-      <c r="BP17" s="120"/>
-      <c r="BQ17" s="120"/>
-      <c r="BR17" s="120"/>
-      <c r="BS17" s="120"/>
-      <c r="BT17" s="120"/>
+      <c r="C17" s="62"/>
+      <c r="D17" s="62"/>
+      <c r="E17" s="62"/>
+      <c r="F17" s="62"/>
+      <c r="G17" s="62"/>
+      <c r="H17" s="62"/>
+      <c r="I17" s="62"/>
+      <c r="J17" s="62"/>
+      <c r="K17" s="62"/>
+      <c r="L17" s="57"/>
+      <c r="M17" s="57"/>
+      <c r="N17" s="57"/>
+      <c r="O17" s="57"/>
+      <c r="P17" s="62"/>
+      <c r="Q17" s="58"/>
+      <c r="R17" s="58"/>
+      <c r="S17" s="58"/>
+      <c r="T17" s="58"/>
+      <c r="U17" s="62"/>
+      <c r="V17" s="62"/>
+      <c r="W17" s="62"/>
+      <c r="X17" s="62"/>
+      <c r="Y17" s="62"/>
+      <c r="Z17" s="90"/>
+      <c r="AA17" s="91"/>
+      <c r="AB17" s="87"/>
+      <c r="AC17" s="118"/>
+      <c r="AD17" s="118"/>
+      <c r="AE17" s="118"/>
+      <c r="AF17" s="118"/>
+      <c r="AG17" s="118"/>
+      <c r="AH17" s="118"/>
+      <c r="AI17" s="118"/>
+      <c r="AJ17" s="118"/>
+      <c r="AK17" s="118"/>
+      <c r="AL17" s="118"/>
+      <c r="AM17" s="118"/>
+      <c r="AN17" s="118"/>
+      <c r="AO17" s="118"/>
+      <c r="AP17" s="118"/>
+      <c r="AQ17" s="118"/>
+      <c r="AR17" s="118"/>
+      <c r="AS17" s="118"/>
+      <c r="AT17" s="118"/>
+      <c r="AU17" s="118"/>
+      <c r="AV17" s="118"/>
+      <c r="AW17" s="118"/>
+      <c r="AX17" s="118"/>
+      <c r="AY17" s="118"/>
+      <c r="AZ17" s="118"/>
+      <c r="BA17" s="118"/>
+      <c r="BB17" s="118"/>
+      <c r="BC17" s="118"/>
+      <c r="BD17" s="118"/>
+      <c r="BE17" s="118"/>
+      <c r="BF17" s="118"/>
+      <c r="BG17" s="118"/>
+      <c r="BH17" s="118"/>
+      <c r="BI17" s="118"/>
+      <c r="BJ17" s="118"/>
+      <c r="BK17" s="118"/>
+      <c r="BL17" s="118"/>
+      <c r="BM17" s="118"/>
+      <c r="BN17" s="118"/>
+      <c r="BO17" s="118"/>
+      <c r="BP17" s="118"/>
+      <c r="BQ17" s="118"/>
+      <c r="BR17" s="118"/>
+      <c r="BS17" s="118"/>
+      <c r="BT17" s="118"/>
     </row>
     <row r="18" spans="1:72" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="40"/>
-      <c r="B18" s="45"/>
-      <c r="C18" s="46"/>
-      <c r="D18" s="46"/>
-      <c r="E18" s="46"/>
-      <c r="F18" s="46"/>
-      <c r="G18" s="46"/>
-      <c r="H18" s="46"/>
-      <c r="I18" s="46"/>
-      <c r="J18" s="46"/>
-      <c r="K18" s="46"/>
-      <c r="L18" s="41"/>
-      <c r="M18" s="41"/>
-      <c r="N18" s="41"/>
-      <c r="O18" s="41"/>
-      <c r="P18" s="46"/>
-      <c r="Q18" s="42"/>
-      <c r="R18" s="42"/>
-      <c r="S18" s="42"/>
-      <c r="T18" s="42"/>
-      <c r="U18" s="46"/>
-      <c r="V18" s="46"/>
-      <c r="W18" s="46"/>
-      <c r="X18" s="46"/>
-      <c r="Y18" s="46"/>
-      <c r="Z18" s="71"/>
-      <c r="AA18" s="72"/>
-      <c r="AB18" s="118"/>
-      <c r="AC18" s="121"/>
-      <c r="AD18" s="121"/>
-      <c r="AE18" s="121"/>
-      <c r="AF18" s="121"/>
-      <c r="AG18" s="121"/>
-      <c r="AH18" s="121"/>
-      <c r="AI18" s="121"/>
-      <c r="AJ18" s="121"/>
-      <c r="AK18" s="121"/>
-      <c r="AL18" s="121"/>
-      <c r="AM18" s="121"/>
-      <c r="AN18" s="121"/>
-      <c r="AO18" s="121"/>
-      <c r="AP18" s="121"/>
-      <c r="AQ18" s="121"/>
-      <c r="AR18" s="121"/>
-      <c r="AS18" s="121"/>
-      <c r="AT18" s="121"/>
-      <c r="AU18" s="121"/>
-      <c r="AV18" s="121"/>
-      <c r="AW18" s="121"/>
-      <c r="AX18" s="121"/>
-      <c r="AY18" s="121"/>
-      <c r="AZ18" s="121"/>
-      <c r="BA18" s="121"/>
-      <c r="BB18" s="121"/>
-      <c r="BC18" s="121"/>
-      <c r="BD18" s="121"/>
-      <c r="BE18" s="121"/>
-      <c r="BF18" s="121"/>
-      <c r="BG18" s="121"/>
-      <c r="BH18" s="121"/>
-      <c r="BI18" s="121"/>
-      <c r="BJ18" s="121"/>
-      <c r="BK18" s="121"/>
-      <c r="BL18" s="121"/>
-      <c r="BM18" s="121"/>
-      <c r="BN18" s="121"/>
-      <c r="BO18" s="121"/>
-      <c r="BP18" s="121"/>
-      <c r="BQ18" s="121"/>
-      <c r="BR18" s="121"/>
-      <c r="BS18" s="121"/>
-      <c r="BT18" s="121"/>
+      <c r="A18" s="56"/>
+      <c r="B18" s="61"/>
+      <c r="C18" s="62"/>
+      <c r="D18" s="62"/>
+      <c r="E18" s="62"/>
+      <c r="F18" s="62"/>
+      <c r="G18" s="62"/>
+      <c r="H18" s="62"/>
+      <c r="I18" s="62"/>
+      <c r="J18" s="62"/>
+      <c r="K18" s="62"/>
+      <c r="L18" s="57"/>
+      <c r="M18" s="57"/>
+      <c r="N18" s="57"/>
+      <c r="O18" s="57"/>
+      <c r="P18" s="62"/>
+      <c r="Q18" s="58"/>
+      <c r="R18" s="58"/>
+      <c r="S18" s="58"/>
+      <c r="T18" s="58"/>
+      <c r="U18" s="62"/>
+      <c r="V18" s="62"/>
+      <c r="W18" s="62"/>
+      <c r="X18" s="62"/>
+      <c r="Y18" s="62"/>
+      <c r="Z18" s="90"/>
+      <c r="AA18" s="91"/>
+      <c r="AB18" s="87"/>
+      <c r="AC18" s="119"/>
+      <c r="AD18" s="119"/>
+      <c r="AE18" s="119"/>
+      <c r="AF18" s="119"/>
+      <c r="AG18" s="119"/>
+      <c r="AH18" s="119"/>
+      <c r="AI18" s="119"/>
+      <c r="AJ18" s="119"/>
+      <c r="AK18" s="119"/>
+      <c r="AL18" s="119"/>
+      <c r="AM18" s="119"/>
+      <c r="AN18" s="119"/>
+      <c r="AO18" s="119"/>
+      <c r="AP18" s="119"/>
+      <c r="AQ18" s="119"/>
+      <c r="AR18" s="119"/>
+      <c r="AS18" s="119"/>
+      <c r="AT18" s="119"/>
+      <c r="AU18" s="119"/>
+      <c r="AV18" s="119"/>
+      <c r="AW18" s="119"/>
+      <c r="AX18" s="119"/>
+      <c r="AY18" s="119"/>
+      <c r="AZ18" s="119"/>
+      <c r="BA18" s="119"/>
+      <c r="BB18" s="119"/>
+      <c r="BC18" s="119"/>
+      <c r="BD18" s="119"/>
+      <c r="BE18" s="119"/>
+      <c r="BF18" s="119"/>
+      <c r="BG18" s="119"/>
+      <c r="BH18" s="119"/>
+      <c r="BI18" s="119"/>
+      <c r="BJ18" s="119"/>
+      <c r="BK18" s="119"/>
+      <c r="BL18" s="119"/>
+      <c r="BM18" s="119"/>
+      <c r="BN18" s="119"/>
+      <c r="BO18" s="119"/>
+      <c r="BP18" s="119"/>
+      <c r="BQ18" s="119"/>
+      <c r="BR18" s="119"/>
+      <c r="BS18" s="119"/>
+      <c r="BT18" s="119"/>
     </row>
     <row r="19" spans="1:72" x14ac:dyDescent="0.3">
-      <c r="A19" s="40"/>
-      <c r="B19" s="45" t="s">
+      <c r="A19" s="56"/>
+      <c r="B19" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="C19" s="46"/>
-      <c r="D19" s="46"/>
-      <c r="E19" s="46"/>
-      <c r="F19" s="46"/>
-      <c r="G19" s="46"/>
-      <c r="H19" s="46"/>
-      <c r="I19" s="46"/>
-      <c r="J19" s="46"/>
-      <c r="K19" s="41"/>
-      <c r="L19" s="46"/>
-      <c r="M19" s="46"/>
-      <c r="N19" s="46"/>
-      <c r="O19" s="46"/>
-      <c r="P19" s="46"/>
-      <c r="Q19" s="46"/>
-      <c r="R19" s="46"/>
-      <c r="S19" s="46"/>
-      <c r="T19" s="46"/>
-      <c r="U19" s="46"/>
-      <c r="V19" s="46"/>
-      <c r="W19" s="41"/>
-      <c r="X19" s="46"/>
-      <c r="Y19" s="46"/>
-      <c r="Z19" s="71"/>
-      <c r="AA19" s="72"/>
-      <c r="AB19" s="118"/>
-      <c r="AC19" s="122"/>
-      <c r="AD19" s="122"/>
-      <c r="AE19" s="122"/>
-      <c r="AF19" s="122"/>
-      <c r="AG19" s="122"/>
-      <c r="AH19" s="122"/>
-      <c r="AI19" s="122"/>
-      <c r="AJ19" s="122"/>
-      <c r="AK19" s="122"/>
-      <c r="AL19" s="122"/>
-      <c r="AM19" s="122"/>
-      <c r="AN19" s="122"/>
-      <c r="AO19" s="122"/>
-      <c r="AP19" s="122"/>
-      <c r="AQ19" s="122"/>
-      <c r="AR19" s="122"/>
-      <c r="AS19" s="122"/>
-      <c r="AT19" s="122"/>
-      <c r="AU19" s="122"/>
-      <c r="AV19" s="122"/>
-      <c r="AW19" s="122"/>
-      <c r="AX19" s="122"/>
-      <c r="AY19" s="122"/>
-      <c r="AZ19" s="122"/>
-      <c r="BA19" s="122"/>
-      <c r="BB19" s="122"/>
-      <c r="BC19" s="122"/>
-      <c r="BD19" s="122"/>
-      <c r="BE19" s="122"/>
-      <c r="BF19" s="122"/>
-      <c r="BG19" s="122"/>
-      <c r="BH19" s="122"/>
-      <c r="BI19" s="122"/>
-      <c r="BJ19" s="122"/>
-      <c r="BK19" s="122"/>
-      <c r="BL19" s="122"/>
-      <c r="BM19" s="122"/>
-      <c r="BN19" s="122"/>
-      <c r="BO19" s="122"/>
-      <c r="BP19" s="122"/>
-      <c r="BQ19" s="122"/>
-      <c r="BR19" s="122"/>
-      <c r="BS19" s="122"/>
-      <c r="BT19" s="122"/>
+      <c r="C19" s="62"/>
+      <c r="D19" s="62"/>
+      <c r="E19" s="62"/>
+      <c r="F19" s="62"/>
+      <c r="G19" s="62"/>
+      <c r="H19" s="62"/>
+      <c r="I19" s="62"/>
+      <c r="J19" s="62"/>
+      <c r="K19" s="57"/>
+      <c r="L19" s="62"/>
+      <c r="M19" s="62"/>
+      <c r="N19" s="62"/>
+      <c r="O19" s="62"/>
+      <c r="P19" s="62"/>
+      <c r="Q19" s="62"/>
+      <c r="R19" s="62"/>
+      <c r="S19" s="62"/>
+      <c r="T19" s="62"/>
+      <c r="U19" s="62"/>
+      <c r="V19" s="62"/>
+      <c r="W19" s="57"/>
+      <c r="X19" s="62"/>
+      <c r="Y19" s="62"/>
+      <c r="Z19" s="90"/>
+      <c r="AA19" s="91"/>
+      <c r="AB19" s="87"/>
+      <c r="AC19" s="120"/>
+      <c r="AD19" s="120"/>
+      <c r="AE19" s="120"/>
+      <c r="AF19" s="120"/>
+      <c r="AG19" s="120"/>
+      <c r="AH19" s="120"/>
+      <c r="AI19" s="120"/>
+      <c r="AJ19" s="120"/>
+      <c r="AK19" s="120"/>
+      <c r="AL19" s="120"/>
+      <c r="AM19" s="120"/>
+      <c r="AN19" s="120"/>
+      <c r="AO19" s="120"/>
+      <c r="AP19" s="120"/>
+      <c r="AQ19" s="120"/>
+      <c r="AR19" s="120"/>
+      <c r="AS19" s="120"/>
+      <c r="AT19" s="120"/>
+      <c r="AU19" s="120"/>
+      <c r="AV19" s="120"/>
+      <c r="AW19" s="120"/>
+      <c r="AX19" s="120"/>
+      <c r="AY19" s="120"/>
+      <c r="AZ19" s="120"/>
+      <c r="BA19" s="120"/>
+      <c r="BB19" s="120"/>
+      <c r="BC19" s="120"/>
+      <c r="BD19" s="120"/>
+      <c r="BE19" s="120"/>
+      <c r="BF19" s="120"/>
+      <c r="BG19" s="120"/>
+      <c r="BH19" s="120"/>
+      <c r="BI19" s="120"/>
+      <c r="BJ19" s="120"/>
+      <c r="BK19" s="120"/>
+      <c r="BL19" s="120"/>
+      <c r="BM19" s="120"/>
+      <c r="BN19" s="120"/>
+      <c r="BO19" s="120"/>
+      <c r="BP19" s="120"/>
+      <c r="BQ19" s="120"/>
+      <c r="BR19" s="120"/>
+      <c r="BS19" s="120"/>
+      <c r="BT19" s="120"/>
     </row>
     <row r="20" spans="1:72" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="40"/>
-      <c r="B20" s="45"/>
-      <c r="C20" s="46"/>
-      <c r="D20" s="46"/>
-      <c r="E20" s="46"/>
-      <c r="F20" s="46"/>
-      <c r="G20" s="46"/>
-      <c r="H20" s="46"/>
-      <c r="I20" s="46"/>
-      <c r="J20" s="46"/>
-      <c r="K20" s="41"/>
-      <c r="L20" s="46"/>
-      <c r="M20" s="46"/>
-      <c r="N20" s="46"/>
-      <c r="O20" s="46"/>
-      <c r="P20" s="46"/>
-      <c r="Q20" s="46"/>
-      <c r="R20" s="46"/>
-      <c r="S20" s="46"/>
-      <c r="T20" s="46"/>
-      <c r="U20" s="46"/>
-      <c r="V20" s="46"/>
-      <c r="W20" s="41"/>
-      <c r="X20" s="46"/>
-      <c r="Y20" s="46"/>
-      <c r="Z20" s="71"/>
-      <c r="AA20" s="72"/>
-      <c r="AB20" s="118"/>
-      <c r="AC20" s="123"/>
-      <c r="AD20" s="123"/>
-      <c r="AE20" s="123"/>
-      <c r="AF20" s="123"/>
-      <c r="AG20" s="123"/>
-      <c r="AH20" s="123"/>
-      <c r="AI20" s="123"/>
-      <c r="AJ20" s="123"/>
-      <c r="AK20" s="123"/>
-      <c r="AL20" s="123"/>
-      <c r="AM20" s="123"/>
-      <c r="AN20" s="123"/>
-      <c r="AO20" s="123"/>
-      <c r="AP20" s="123"/>
-      <c r="AQ20" s="123"/>
-      <c r="AR20" s="123"/>
-      <c r="AS20" s="123"/>
-      <c r="AT20" s="123"/>
-      <c r="AU20" s="123"/>
-      <c r="AV20" s="123"/>
-      <c r="AW20" s="123"/>
-      <c r="AX20" s="123"/>
-      <c r="AY20" s="123"/>
-      <c r="AZ20" s="123"/>
-      <c r="BA20" s="123"/>
-      <c r="BB20" s="123"/>
-      <c r="BC20" s="123"/>
-      <c r="BD20" s="123"/>
-      <c r="BE20" s="123"/>
-      <c r="BF20" s="123"/>
-      <c r="BG20" s="123"/>
-      <c r="BH20" s="123"/>
-      <c r="BI20" s="123"/>
-      <c r="BJ20" s="123"/>
-      <c r="BK20" s="123"/>
-      <c r="BL20" s="123"/>
-      <c r="BM20" s="123"/>
-      <c r="BN20" s="123"/>
-      <c r="BO20" s="123"/>
-      <c r="BP20" s="123"/>
-      <c r="BQ20" s="123"/>
-      <c r="BR20" s="123"/>
-      <c r="BS20" s="123"/>
-      <c r="BT20" s="123"/>
+      <c r="A20" s="56"/>
+      <c r="B20" s="61"/>
+      <c r="C20" s="62"/>
+      <c r="D20" s="62"/>
+      <c r="E20" s="62"/>
+      <c r="F20" s="62"/>
+      <c r="G20" s="62"/>
+      <c r="H20" s="62"/>
+      <c r="I20" s="62"/>
+      <c r="J20" s="62"/>
+      <c r="K20" s="57"/>
+      <c r="L20" s="62"/>
+      <c r="M20" s="62"/>
+      <c r="N20" s="62"/>
+      <c r="O20" s="62"/>
+      <c r="P20" s="62"/>
+      <c r="Q20" s="62"/>
+      <c r="R20" s="62"/>
+      <c r="S20" s="62"/>
+      <c r="T20" s="62"/>
+      <c r="U20" s="62"/>
+      <c r="V20" s="62"/>
+      <c r="W20" s="57"/>
+      <c r="X20" s="62"/>
+      <c r="Y20" s="62"/>
+      <c r="Z20" s="90"/>
+      <c r="AA20" s="91"/>
+      <c r="AB20" s="87"/>
+      <c r="AC20" s="121"/>
+      <c r="AD20" s="121"/>
+      <c r="AE20" s="121"/>
+      <c r="AF20" s="121"/>
+      <c r="AG20" s="121"/>
+      <c r="AH20" s="121"/>
+      <c r="AI20" s="121"/>
+      <c r="AJ20" s="121"/>
+      <c r="AK20" s="121"/>
+      <c r="AL20" s="121"/>
+      <c r="AM20" s="121"/>
+      <c r="AN20" s="121"/>
+      <c r="AO20" s="121"/>
+      <c r="AP20" s="121"/>
+      <c r="AQ20" s="121"/>
+      <c r="AR20" s="121"/>
+      <c r="AS20" s="121"/>
+      <c r="AT20" s="121"/>
+      <c r="AU20" s="121"/>
+      <c r="AV20" s="121"/>
+      <c r="AW20" s="121"/>
+      <c r="AX20" s="121"/>
+      <c r="AY20" s="121"/>
+      <c r="AZ20" s="121"/>
+      <c r="BA20" s="121"/>
+      <c r="BB20" s="121"/>
+      <c r="BC20" s="121"/>
+      <c r="BD20" s="121"/>
+      <c r="BE20" s="121"/>
+      <c r="BF20" s="121"/>
+      <c r="BG20" s="121"/>
+      <c r="BH20" s="121"/>
+      <c r="BI20" s="121"/>
+      <c r="BJ20" s="121"/>
+      <c r="BK20" s="121"/>
+      <c r="BL20" s="121"/>
+      <c r="BM20" s="121"/>
+      <c r="BN20" s="121"/>
+      <c r="BO20" s="121"/>
+      <c r="BP20" s="121"/>
+      <c r="BQ20" s="121"/>
+      <c r="BR20" s="121"/>
+      <c r="BS20" s="121"/>
+      <c r="BT20" s="121"/>
     </row>
     <row r="21" spans="1:72" x14ac:dyDescent="0.3">
-      <c r="A21" s="40"/>
-      <c r="B21" s="45" t="s">
+      <c r="A21" s="56"/>
+      <c r="B21" s="61" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="46"/>
-      <c r="D21" s="46"/>
-      <c r="E21" s="46"/>
-      <c r="F21" s="46"/>
-      <c r="G21" s="46"/>
-      <c r="H21" s="46"/>
-      <c r="I21" s="46"/>
-      <c r="J21" s="46"/>
-      <c r="K21" s="46"/>
-      <c r="L21" s="46"/>
-      <c r="M21" s="46"/>
-      <c r="N21" s="46"/>
-      <c r="O21" s="46"/>
-      <c r="P21" s="46"/>
-      <c r="Q21" s="46"/>
-      <c r="R21" s="46"/>
-      <c r="S21" s="46"/>
-      <c r="T21" s="46"/>
-      <c r="U21" s="46"/>
-      <c r="V21" s="46"/>
-      <c r="W21" s="42"/>
-      <c r="X21" s="25"/>
-      <c r="Y21" s="27"/>
-      <c r="Z21" s="41"/>
-      <c r="AA21" s="41"/>
-      <c r="AB21" s="118"/>
-      <c r="AC21" s="122"/>
-      <c r="AD21" s="122"/>
-      <c r="AE21" s="122"/>
-      <c r="AF21" s="122"/>
-      <c r="AG21" s="122"/>
-      <c r="AH21" s="122"/>
-      <c r="AI21" s="122"/>
-      <c r="AJ21" s="122"/>
-      <c r="AK21" s="122"/>
-      <c r="AL21" s="122"/>
-      <c r="AM21" s="122"/>
-      <c r="AN21" s="122"/>
-      <c r="AO21" s="122"/>
-      <c r="AP21" s="122"/>
-      <c r="AQ21" s="122"/>
-      <c r="AR21" s="122"/>
-      <c r="AS21" s="122"/>
-      <c r="AT21" s="122"/>
-      <c r="AU21" s="122"/>
-      <c r="AV21" s="122"/>
-      <c r="AW21" s="122"/>
-      <c r="AX21" s="122"/>
-      <c r="AY21" s="122"/>
-      <c r="AZ21" s="122"/>
-      <c r="BA21" s="122"/>
-      <c r="BB21" s="122"/>
-      <c r="BC21" s="122"/>
-      <c r="BD21" s="122"/>
-      <c r="BE21" s="122"/>
-      <c r="BF21" s="122"/>
-      <c r="BG21" s="122"/>
-      <c r="BH21" s="122"/>
-      <c r="BI21" s="122"/>
-      <c r="BJ21" s="122"/>
-      <c r="BK21" s="122"/>
-      <c r="BL21" s="122"/>
-      <c r="BM21" s="122"/>
-      <c r="BN21" s="122"/>
-      <c r="BO21" s="122"/>
-      <c r="BP21" s="122"/>
-      <c r="BQ21" s="122"/>
-      <c r="BR21" s="122"/>
-      <c r="BS21" s="122"/>
-      <c r="BT21" s="122"/>
+      <c r="C21" s="62"/>
+      <c r="D21" s="62"/>
+      <c r="E21" s="62"/>
+      <c r="F21" s="62"/>
+      <c r="G21" s="62"/>
+      <c r="H21" s="62"/>
+      <c r="I21" s="62"/>
+      <c r="J21" s="62"/>
+      <c r="K21" s="62"/>
+      <c r="L21" s="62"/>
+      <c r="M21" s="62"/>
+      <c r="N21" s="62"/>
+      <c r="O21" s="62"/>
+      <c r="P21" s="62"/>
+      <c r="Q21" s="62"/>
+      <c r="R21" s="62"/>
+      <c r="S21" s="62"/>
+      <c r="T21" s="62"/>
+      <c r="U21" s="62"/>
+      <c r="V21" s="62"/>
+      <c r="W21" s="58"/>
+      <c r="X21" s="41"/>
+      <c r="Y21" s="43"/>
+      <c r="Z21" s="57"/>
+      <c r="AA21" s="57"/>
+      <c r="AB21" s="87"/>
+      <c r="AC21" s="120"/>
+      <c r="AD21" s="120"/>
+      <c r="AE21" s="120"/>
+      <c r="AF21" s="120"/>
+      <c r="AG21" s="120"/>
+      <c r="AH21" s="120"/>
+      <c r="AI21" s="120"/>
+      <c r="AJ21" s="120"/>
+      <c r="AK21" s="120"/>
+      <c r="AL21" s="120"/>
+      <c r="AM21" s="120"/>
+      <c r="AN21" s="120"/>
+      <c r="AO21" s="120"/>
+      <c r="AP21" s="120"/>
+      <c r="AQ21" s="120"/>
+      <c r="AR21" s="120"/>
+      <c r="AS21" s="120"/>
+      <c r="AT21" s="120"/>
+      <c r="AU21" s="120"/>
+      <c r="AV21" s="120"/>
+      <c r="AW21" s="120"/>
+      <c r="AX21" s="120"/>
+      <c r="AY21" s="120"/>
+      <c r="AZ21" s="120"/>
+      <c r="BA21" s="120"/>
+      <c r="BB21" s="120"/>
+      <c r="BC21" s="120"/>
+      <c r="BD21" s="120"/>
+      <c r="BE21" s="120"/>
+      <c r="BF21" s="120"/>
+      <c r="BG21" s="120"/>
+      <c r="BH21" s="120"/>
+      <c r="BI21" s="120"/>
+      <c r="BJ21" s="120"/>
+      <c r="BK21" s="120"/>
+      <c r="BL21" s="120"/>
+      <c r="BM21" s="120"/>
+      <c r="BN21" s="120"/>
+      <c r="BO21" s="120"/>
+      <c r="BP21" s="120"/>
+      <c r="BQ21" s="120"/>
+      <c r="BR21" s="120"/>
+      <c r="BS21" s="120"/>
+      <c r="BT21" s="120"/>
     </row>
     <row r="22" spans="1:72" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="40"/>
-      <c r="B22" s="27"/>
-      <c r="C22" s="70"/>
-      <c r="D22" s="70"/>
-      <c r="E22" s="70"/>
-      <c r="F22" s="70"/>
-      <c r="G22" s="70"/>
-      <c r="H22" s="70"/>
-      <c r="I22" s="70"/>
-      <c r="J22" s="70"/>
-      <c r="K22" s="70"/>
-      <c r="L22" s="70"/>
-      <c r="M22" s="70"/>
-      <c r="N22" s="70"/>
-      <c r="O22" s="70"/>
-      <c r="P22" s="70"/>
-      <c r="Q22" s="70"/>
-      <c r="R22" s="70"/>
-      <c r="S22" s="70"/>
-      <c r="T22" s="70"/>
-      <c r="U22" s="70"/>
-      <c r="V22" s="70"/>
-      <c r="W22" s="43"/>
-      <c r="X22" s="61"/>
-      <c r="Y22" s="62"/>
-      <c r="Z22" s="69"/>
-      <c r="AA22" s="69"/>
-      <c r="AB22" s="119"/>
-      <c r="AC22" s="123"/>
-      <c r="AD22" s="123"/>
-      <c r="AE22" s="123"/>
-      <c r="AF22" s="123"/>
-      <c r="AG22" s="123"/>
-      <c r="AH22" s="123"/>
-      <c r="AI22" s="123"/>
-      <c r="AJ22" s="123"/>
-      <c r="AK22" s="123"/>
-      <c r="AL22" s="123"/>
-      <c r="AM22" s="123"/>
-      <c r="AN22" s="123"/>
-      <c r="AO22" s="123"/>
-      <c r="AP22" s="123"/>
-      <c r="AQ22" s="123"/>
-      <c r="AR22" s="123"/>
-      <c r="AS22" s="123"/>
-      <c r="AT22" s="123"/>
-      <c r="AU22" s="123"/>
-      <c r="AV22" s="123"/>
-      <c r="AW22" s="123"/>
-      <c r="AX22" s="123"/>
-      <c r="AY22" s="123"/>
-      <c r="AZ22" s="123"/>
-      <c r="BA22" s="123"/>
-      <c r="BB22" s="123"/>
-      <c r="BC22" s="123"/>
-      <c r="BD22" s="123"/>
-      <c r="BE22" s="123"/>
-      <c r="BF22" s="123"/>
-      <c r="BG22" s="123"/>
-      <c r="BH22" s="123"/>
-      <c r="BI22" s="123"/>
-      <c r="BJ22" s="123"/>
-      <c r="BK22" s="123"/>
-      <c r="BL22" s="123"/>
-      <c r="BM22" s="123"/>
-      <c r="BN22" s="123"/>
-      <c r="BO22" s="123"/>
-      <c r="BP22" s="123"/>
-      <c r="BQ22" s="123"/>
-      <c r="BR22" s="123"/>
-      <c r="BS22" s="123"/>
-      <c r="BT22" s="123"/>
+      <c r="A22" s="56"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="89"/>
+      <c r="D22" s="89"/>
+      <c r="E22" s="89"/>
+      <c r="F22" s="89"/>
+      <c r="G22" s="89"/>
+      <c r="H22" s="89"/>
+      <c r="I22" s="89"/>
+      <c r="J22" s="89"/>
+      <c r="K22" s="89"/>
+      <c r="L22" s="89"/>
+      <c r="M22" s="89"/>
+      <c r="N22" s="89"/>
+      <c r="O22" s="89"/>
+      <c r="P22" s="89"/>
+      <c r="Q22" s="89"/>
+      <c r="R22" s="89"/>
+      <c r="S22" s="89"/>
+      <c r="T22" s="89"/>
+      <c r="U22" s="89"/>
+      <c r="V22" s="89"/>
+      <c r="W22" s="59"/>
+      <c r="X22" s="78"/>
+      <c r="Y22" s="79"/>
+      <c r="Z22" s="86"/>
+      <c r="AA22" s="86"/>
+      <c r="AB22" s="88"/>
+      <c r="AC22" s="121"/>
+      <c r="AD22" s="121"/>
+      <c r="AE22" s="121"/>
+      <c r="AF22" s="121"/>
+      <c r="AG22" s="121"/>
+      <c r="AH22" s="121"/>
+      <c r="AI22" s="121"/>
+      <c r="AJ22" s="121"/>
+      <c r="AK22" s="121"/>
+      <c r="AL22" s="121"/>
+      <c r="AM22" s="121"/>
+      <c r="AN22" s="121"/>
+      <c r="AO22" s="121"/>
+      <c r="AP22" s="121"/>
+      <c r="AQ22" s="121"/>
+      <c r="AR22" s="121"/>
+      <c r="AS22" s="121"/>
+      <c r="AT22" s="121"/>
+      <c r="AU22" s="121"/>
+      <c r="AV22" s="121"/>
+      <c r="AW22" s="121"/>
+      <c r="AX22" s="121"/>
+      <c r="AY22" s="121"/>
+      <c r="AZ22" s="121"/>
+      <c r="BA22" s="121"/>
+      <c r="BB22" s="121"/>
+      <c r="BC22" s="121"/>
+      <c r="BD22" s="121"/>
+      <c r="BE22" s="121"/>
+      <c r="BF22" s="121"/>
+      <c r="BG22" s="121"/>
+      <c r="BH22" s="121"/>
+      <c r="BI22" s="121"/>
+      <c r="BJ22" s="121"/>
+      <c r="BK22" s="121"/>
+      <c r="BL22" s="121"/>
+      <c r="BM22" s="121"/>
+      <c r="BN22" s="121"/>
+      <c r="BO22" s="121"/>
+      <c r="BP22" s="121"/>
+      <c r="BQ22" s="121"/>
+      <c r="BR22" s="121"/>
+      <c r="BS22" s="121"/>
+      <c r="BT22" s="121"/>
     </row>
     <row r="23" spans="1:72" x14ac:dyDescent="0.3">
-      <c r="A23" s="40"/>
-      <c r="B23" s="36" t="s">
+      <c r="A23" s="56"/>
+      <c r="B23" s="52" t="s">
         <v>55</v>
       </c>
-      <c r="C23" s="23"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="32"/>
-      <c r="F23" s="32"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="32"/>
-      <c r="I23" s="32"/>
-      <c r="J23" s="32"/>
-      <c r="K23" s="32"/>
-      <c r="L23" s="32"/>
-      <c r="M23" s="32"/>
-      <c r="N23" s="31"/>
-      <c r="O23" s="31"/>
-      <c r="P23" s="31"/>
-      <c r="Q23" s="32"/>
-      <c r="R23" s="32"/>
-      <c r="S23" s="32"/>
-      <c r="T23" s="32"/>
-      <c r="U23" s="32"/>
-      <c r="V23" s="32"/>
-      <c r="W23" s="31"/>
-      <c r="X23" s="31"/>
-      <c r="Y23" s="31"/>
-      <c r="Z23" s="31"/>
-      <c r="AA23" s="31"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="47"/>
+      <c r="E23" s="48"/>
+      <c r="F23" s="48"/>
+      <c r="G23" s="48"/>
+      <c r="H23" s="48"/>
+      <c r="I23" s="48"/>
+      <c r="J23" s="48"/>
+      <c r="K23" s="48"/>
+      <c r="L23" s="48"/>
+      <c r="M23" s="48"/>
+      <c r="N23" s="47"/>
+      <c r="O23" s="47"/>
+      <c r="P23" s="47"/>
+      <c r="Q23" s="48"/>
+      <c r="R23" s="48"/>
+      <c r="S23" s="48"/>
+      <c r="T23" s="48"/>
+      <c r="U23" s="48"/>
+      <c r="V23" s="48"/>
+      <c r="W23" s="47"/>
+      <c r="X23" s="47"/>
+      <c r="Y23" s="47"/>
+      <c r="Z23" s="47"/>
+      <c r="AA23" s="47"/>
       <c r="AB23" s="2"/>
-      <c r="AC23" s="122"/>
-      <c r="AD23" s="122"/>
-      <c r="AE23" s="122"/>
-      <c r="AF23" s="122"/>
-      <c r="AG23" s="122"/>
-      <c r="AH23" s="122"/>
-      <c r="AI23" s="122"/>
-      <c r="AJ23" s="122"/>
-      <c r="AK23" s="122"/>
-      <c r="AL23" s="122"/>
-      <c r="AM23" s="122"/>
-      <c r="AN23" s="122"/>
-      <c r="AO23" s="122"/>
-      <c r="AP23" s="122"/>
-      <c r="AQ23" s="122"/>
-      <c r="AR23" s="122"/>
-      <c r="AS23" s="122"/>
-      <c r="AT23" s="122"/>
-      <c r="AU23" s="122"/>
-      <c r="AV23" s="122"/>
-      <c r="AW23" s="122"/>
-      <c r="AX23" s="122"/>
-      <c r="AY23" s="122"/>
-      <c r="AZ23" s="122"/>
-      <c r="BA23" s="122"/>
-      <c r="BB23" s="122"/>
-      <c r="BC23" s="122"/>
-      <c r="BD23" s="122"/>
-      <c r="BE23" s="122"/>
-      <c r="BF23" s="122"/>
-      <c r="BG23" s="122"/>
-      <c r="BH23" s="122"/>
-      <c r="BI23" s="122"/>
-      <c r="BJ23" s="122"/>
-      <c r="BK23" s="122"/>
-      <c r="BL23" s="122"/>
-      <c r="BM23" s="122"/>
-      <c r="BN23" s="122"/>
-      <c r="BO23" s="122"/>
-      <c r="BP23" s="122"/>
-      <c r="BQ23" s="122"/>
-      <c r="BR23" s="122"/>
-      <c r="BS23" s="122"/>
-      <c r="BT23" s="122"/>
+      <c r="AC23" s="120"/>
+      <c r="AD23" s="120"/>
+      <c r="AE23" s="120"/>
+      <c r="AF23" s="120"/>
+      <c r="AG23" s="120"/>
+      <c r="AH23" s="120"/>
+      <c r="AI23" s="120"/>
+      <c r="AJ23" s="120"/>
+      <c r="AK23" s="120"/>
+      <c r="AL23" s="120"/>
+      <c r="AM23" s="120"/>
+      <c r="AN23" s="120"/>
+      <c r="AO23" s="120"/>
+      <c r="AP23" s="120"/>
+      <c r="AQ23" s="120"/>
+      <c r="AR23" s="120"/>
+      <c r="AS23" s="120"/>
+      <c r="AT23" s="120"/>
+      <c r="AU23" s="120"/>
+      <c r="AV23" s="120"/>
+      <c r="AW23" s="120"/>
+      <c r="AX23" s="120"/>
+      <c r="AY23" s="120"/>
+      <c r="AZ23" s="120"/>
+      <c r="BA23" s="120"/>
+      <c r="BB23" s="120"/>
+      <c r="BC23" s="120"/>
+      <c r="BD23" s="120"/>
+      <c r="BE23" s="120"/>
+      <c r="BF23" s="120"/>
+      <c r="BG23" s="120"/>
+      <c r="BH23" s="120"/>
+      <c r="BI23" s="120"/>
+      <c r="BJ23" s="120"/>
+      <c r="BK23" s="120"/>
+      <c r="BL23" s="120"/>
+      <c r="BM23" s="120"/>
+      <c r="BN23" s="120"/>
+      <c r="BO23" s="120"/>
+      <c r="BP23" s="120"/>
+      <c r="BQ23" s="120"/>
+      <c r="BR23" s="120"/>
+      <c r="BS23" s="120"/>
+      <c r="BT23" s="120"/>
     </row>
     <row r="24" spans="1:72" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="40"/>
-      <c r="B24" s="37"/>
-      <c r="C24" s="23"/>
-      <c r="D24" s="31"/>
-      <c r="E24" s="32"/>
-      <c r="F24" s="32"/>
-      <c r="G24" s="32"/>
-      <c r="H24" s="32"/>
-      <c r="I24" s="32"/>
-      <c r="J24" s="32"/>
-      <c r="K24" s="32"/>
-      <c r="L24" s="32"/>
-      <c r="M24" s="32"/>
-      <c r="N24" s="31"/>
-      <c r="O24" s="31"/>
-      <c r="P24" s="31"/>
-      <c r="Q24" s="32"/>
-      <c r="R24" s="32"/>
-      <c r="S24" s="32"/>
-      <c r="T24" s="32"/>
-      <c r="U24" s="32"/>
-      <c r="V24" s="32"/>
-      <c r="W24" s="44"/>
-      <c r="X24" s="44"/>
-      <c r="Y24" s="44"/>
-      <c r="Z24" s="44"/>
-      <c r="AA24" s="44"/>
+      <c r="A24" s="56"/>
+      <c r="B24" s="53"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="47"/>
+      <c r="E24" s="48"/>
+      <c r="F24" s="48"/>
+      <c r="G24" s="48"/>
+      <c r="H24" s="48"/>
+      <c r="I24" s="48"/>
+      <c r="J24" s="48"/>
+      <c r="K24" s="48"/>
+      <c r="L24" s="48"/>
+      <c r="M24" s="48"/>
+      <c r="N24" s="47"/>
+      <c r="O24" s="47"/>
+      <c r="P24" s="47"/>
+      <c r="Q24" s="48"/>
+      <c r="R24" s="48"/>
+      <c r="S24" s="48"/>
+      <c r="T24" s="48"/>
+      <c r="U24" s="48"/>
+      <c r="V24" s="48"/>
+      <c r="W24" s="60"/>
+      <c r="X24" s="60"/>
+      <c r="Y24" s="60"/>
+      <c r="Z24" s="60"/>
+      <c r="AA24" s="60"/>
       <c r="AB24" s="2"/>
-      <c r="AC24" s="123"/>
-      <c r="AD24" s="123"/>
-      <c r="AE24" s="123"/>
-      <c r="AF24" s="123"/>
-      <c r="AG24" s="123"/>
-      <c r="AH24" s="123"/>
-      <c r="AI24" s="123"/>
-      <c r="AJ24" s="123"/>
-      <c r="AK24" s="123"/>
-      <c r="AL24" s="123"/>
-      <c r="AM24" s="123"/>
-      <c r="AN24" s="123"/>
-      <c r="AO24" s="123"/>
-      <c r="AP24" s="123"/>
-      <c r="AQ24" s="123"/>
-      <c r="AR24" s="123"/>
-      <c r="AS24" s="123"/>
-      <c r="AT24" s="123"/>
-      <c r="AU24" s="123"/>
-      <c r="AV24" s="123"/>
-      <c r="AW24" s="123"/>
-      <c r="AX24" s="123"/>
-      <c r="AY24" s="123"/>
-      <c r="AZ24" s="123"/>
-      <c r="BA24" s="123"/>
-      <c r="BB24" s="123"/>
-      <c r="BC24" s="123"/>
-      <c r="BD24" s="123"/>
-      <c r="BE24" s="123"/>
-      <c r="BF24" s="123"/>
-      <c r="BG24" s="123"/>
-      <c r="BH24" s="123"/>
-      <c r="BI24" s="123"/>
-      <c r="BJ24" s="123"/>
-      <c r="BK24" s="123"/>
-      <c r="BL24" s="123"/>
-      <c r="BM24" s="123"/>
-      <c r="BN24" s="123"/>
-      <c r="BO24" s="123"/>
-      <c r="BP24" s="123"/>
-      <c r="BQ24" s="123"/>
-      <c r="BR24" s="123"/>
-      <c r="BS24" s="123"/>
-      <c r="BT24" s="123"/>
+      <c r="AC24" s="121"/>
+      <c r="AD24" s="121"/>
+      <c r="AE24" s="121"/>
+      <c r="AF24" s="121"/>
+      <c r="AG24" s="121"/>
+      <c r="AH24" s="121"/>
+      <c r="AI24" s="121"/>
+      <c r="AJ24" s="121"/>
+      <c r="AK24" s="121"/>
+      <c r="AL24" s="121"/>
+      <c r="AM24" s="121"/>
+      <c r="AN24" s="121"/>
+      <c r="AO24" s="121"/>
+      <c r="AP24" s="121"/>
+      <c r="AQ24" s="121"/>
+      <c r="AR24" s="121"/>
+      <c r="AS24" s="121"/>
+      <c r="AT24" s="121"/>
+      <c r="AU24" s="121"/>
+      <c r="AV24" s="121"/>
+      <c r="AW24" s="121"/>
+      <c r="AX24" s="121"/>
+      <c r="AY24" s="121"/>
+      <c r="AZ24" s="121"/>
+      <c r="BA24" s="121"/>
+      <c r="BB24" s="121"/>
+      <c r="BC24" s="121"/>
+      <c r="BD24" s="121"/>
+      <c r="BE24" s="121"/>
+      <c r="BF24" s="121"/>
+      <c r="BG24" s="121"/>
+      <c r="BH24" s="121"/>
+      <c r="BI24" s="121"/>
+      <c r="BJ24" s="121"/>
+      <c r="BK24" s="121"/>
+      <c r="BL24" s="121"/>
+      <c r="BM24" s="121"/>
+      <c r="BN24" s="121"/>
+      <c r="BO24" s="121"/>
+      <c r="BP24" s="121"/>
+      <c r="BQ24" s="121"/>
+      <c r="BR24" s="121"/>
+      <c r="BS24" s="121"/>
+      <c r="BT24" s="121"/>
     </row>
     <row r="25" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B25" s="22" t="s">
+      <c r="B25" s="38" t="s">
         <v>24</v>
       </c>
       <c r="C25" s="4" t="s">
@@ -5011,56 +5506,56 @@
       <c r="AB25" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="AC25" s="115"/>
-      <c r="AD25" s="115"/>
-      <c r="AE25" s="115"/>
-      <c r="AF25" s="115"/>
-      <c r="AG25" s="115"/>
-      <c r="AH25" s="115"/>
-      <c r="AI25" s="115"/>
-      <c r="AJ25" s="115"/>
-      <c r="AK25" s="115"/>
-      <c r="AL25" s="115"/>
-      <c r="AM25" s="115"/>
-      <c r="AN25" s="115"/>
-      <c r="AO25" s="115"/>
-      <c r="AP25" s="115"/>
-      <c r="AQ25" s="115"/>
-      <c r="AR25" s="115"/>
-      <c r="AS25" s="115"/>
-      <c r="AT25" s="115"/>
-      <c r="AU25" s="115"/>
-      <c r="AV25" s="115"/>
-      <c r="AW25" s="115"/>
-      <c r="AX25" s="115"/>
-      <c r="AY25" s="115"/>
-      <c r="AZ25" s="115"/>
-      <c r="BA25" s="115"/>
-      <c r="BB25" s="115"/>
-      <c r="BC25" s="115"/>
-      <c r="BD25" s="115"/>
-      <c r="BE25" s="115"/>
-      <c r="BF25" s="115"/>
-      <c r="BG25" s="115"/>
-      <c r="BH25" s="115"/>
-      <c r="BI25" s="115"/>
-      <c r="BJ25" s="115"/>
-      <c r="BK25" s="115"/>
-      <c r="BL25" s="115"/>
-      <c r="BM25" s="115"/>
-      <c r="BN25" s="115"/>
-      <c r="BO25" s="115"/>
-      <c r="BP25" s="115"/>
-      <c r="BQ25" s="115"/>
-      <c r="BR25" s="115"/>
-      <c r="BS25" s="115"/>
-      <c r="BT25" s="115"/>
+      <c r="AC25" s="35"/>
+      <c r="AD25" s="35"/>
+      <c r="AE25" s="35"/>
+      <c r="AF25" s="35"/>
+      <c r="AG25" s="35"/>
+      <c r="AH25" s="35"/>
+      <c r="AI25" s="35"/>
+      <c r="AJ25" s="35"/>
+      <c r="AK25" s="35"/>
+      <c r="AL25" s="35"/>
+      <c r="AM25" s="35"/>
+      <c r="AN25" s="35"/>
+      <c r="AO25" s="35"/>
+      <c r="AP25" s="35"/>
+      <c r="AQ25" s="35"/>
+      <c r="AR25" s="35"/>
+      <c r="AS25" s="35"/>
+      <c r="AT25" s="35"/>
+      <c r="AU25" s="35"/>
+      <c r="AV25" s="35"/>
+      <c r="AW25" s="35"/>
+      <c r="AX25" s="35"/>
+      <c r="AY25" s="35"/>
+      <c r="AZ25" s="35"/>
+      <c r="BA25" s="35"/>
+      <c r="BB25" s="35"/>
+      <c r="BC25" s="35"/>
+      <c r="BD25" s="35"/>
+      <c r="BE25" s="35"/>
+      <c r="BF25" s="35"/>
+      <c r="BG25" s="35"/>
+      <c r="BH25" s="35"/>
+      <c r="BI25" s="35"/>
+      <c r="BJ25" s="35"/>
+      <c r="BK25" s="35"/>
+      <c r="BL25" s="35"/>
+      <c r="BM25" s="35"/>
+      <c r="BN25" s="35"/>
+      <c r="BO25" s="35"/>
+      <c r="BP25" s="35"/>
+      <c r="BQ25" s="35"/>
+      <c r="BR25" s="35"/>
+      <c r="BS25" s="35"/>
+      <c r="BT25" s="35"/>
     </row>
     <row r="26" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="B26" s="24"/>
+      <c r="B26" s="40"/>
       <c r="C26" s="5" t="s">
         <v>60</v>
       </c>
@@ -5102,56 +5597,56 @@
       <c r="AB26" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="AC26" s="115"/>
-      <c r="AD26" s="115"/>
-      <c r="AE26" s="115"/>
-      <c r="AF26" s="115"/>
-      <c r="AG26" s="115"/>
-      <c r="AH26" s="115"/>
-      <c r="AI26" s="115"/>
-      <c r="AJ26" s="115"/>
-      <c r="AK26" s="115"/>
-      <c r="AL26" s="115"/>
-      <c r="AM26" s="115"/>
-      <c r="AN26" s="115"/>
-      <c r="AO26" s="115"/>
-      <c r="AP26" s="115"/>
-      <c r="AQ26" s="115"/>
-      <c r="AR26" s="115"/>
-      <c r="AS26" s="115"/>
-      <c r="AT26" s="115"/>
-      <c r="AU26" s="115"/>
-      <c r="AV26" s="115"/>
-      <c r="AW26" s="115"/>
-      <c r="AX26" s="115"/>
-      <c r="AY26" s="115"/>
-      <c r="AZ26" s="115"/>
-      <c r="BA26" s="115"/>
-      <c r="BB26" s="115"/>
-      <c r="BC26" s="115"/>
-      <c r="BD26" s="115"/>
-      <c r="BE26" s="115"/>
-      <c r="BF26" s="115"/>
-      <c r="BG26" s="115"/>
-      <c r="BH26" s="115"/>
-      <c r="BI26" s="115"/>
-      <c r="BJ26" s="115"/>
-      <c r="BK26" s="115"/>
-      <c r="BL26" s="115"/>
-      <c r="BM26" s="115"/>
-      <c r="BN26" s="115"/>
-      <c r="BO26" s="115"/>
-      <c r="BP26" s="115"/>
-      <c r="BQ26" s="115"/>
-      <c r="BR26" s="115"/>
-      <c r="BS26" s="115"/>
-      <c r="BT26" s="115"/>
+      <c r="AC26" s="35"/>
+      <c r="AD26" s="35"/>
+      <c r="AE26" s="35"/>
+      <c r="AF26" s="35"/>
+      <c r="AG26" s="35"/>
+      <c r="AH26" s="35"/>
+      <c r="AI26" s="35"/>
+      <c r="AJ26" s="35"/>
+      <c r="AK26" s="35"/>
+      <c r="AL26" s="35"/>
+      <c r="AM26" s="35"/>
+      <c r="AN26" s="35"/>
+      <c r="AO26" s="35"/>
+      <c r="AP26" s="35"/>
+      <c r="AQ26" s="35"/>
+      <c r="AR26" s="35"/>
+      <c r="AS26" s="35"/>
+      <c r="AT26" s="35"/>
+      <c r="AU26" s="35"/>
+      <c r="AV26" s="35"/>
+      <c r="AW26" s="35"/>
+      <c r="AX26" s="35"/>
+      <c r="AY26" s="35"/>
+      <c r="AZ26" s="35"/>
+      <c r="BA26" s="35"/>
+      <c r="BB26" s="35"/>
+      <c r="BC26" s="35"/>
+      <c r="BD26" s="35"/>
+      <c r="BE26" s="35"/>
+      <c r="BF26" s="35"/>
+      <c r="BG26" s="35"/>
+      <c r="BH26" s="35"/>
+      <c r="BI26" s="35"/>
+      <c r="BJ26" s="35"/>
+      <c r="BK26" s="35"/>
+      <c r="BL26" s="35"/>
+      <c r="BM26" s="35"/>
+      <c r="BN26" s="35"/>
+      <c r="BO26" s="35"/>
+      <c r="BP26" s="35"/>
+      <c r="BQ26" s="35"/>
+      <c r="BR26" s="35"/>
+      <c r="BS26" s="35"/>
+      <c r="BT26" s="35"/>
     </row>
     <row r="27" spans="1:72" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B27" s="33"/>
+      <c r="B27" s="49"/>
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
@@ -5181,57 +5676,57 @@
       <c r="Y27" s="6"/>
       <c r="Z27" s="6"/>
       <c r="AA27" s="6"/>
-      <c r="AB27" s="109"/>
-      <c r="AC27" s="116"/>
-      <c r="AD27" s="116"/>
-      <c r="AE27" s="116"/>
-      <c r="AF27" s="116"/>
-      <c r="AG27" s="116"/>
-      <c r="AH27" s="116"/>
-      <c r="AI27" s="116"/>
-      <c r="AJ27" s="116"/>
-      <c r="AK27" s="116"/>
-      <c r="AL27" s="116"/>
-      <c r="AM27" s="116"/>
-      <c r="AN27" s="116"/>
-      <c r="AO27" s="116"/>
-      <c r="AP27" s="116"/>
-      <c r="AQ27" s="116"/>
-      <c r="AR27" s="116"/>
-      <c r="AS27" s="116"/>
-      <c r="AT27" s="116"/>
-      <c r="AU27" s="116"/>
-      <c r="AV27" s="116"/>
-      <c r="AW27" s="116"/>
-      <c r="AX27" s="116"/>
-      <c r="AY27" s="116"/>
-      <c r="AZ27" s="116"/>
-      <c r="BA27" s="116"/>
-      <c r="BB27" s="116"/>
-      <c r="BC27" s="116"/>
-      <c r="BD27" s="116"/>
-      <c r="BE27" s="116"/>
-      <c r="BF27" s="116"/>
-      <c r="BG27" s="116"/>
-      <c r="BH27" s="116"/>
-      <c r="BI27" s="116"/>
-      <c r="BJ27" s="116"/>
-      <c r="BK27" s="116"/>
-      <c r="BL27" s="116"/>
-      <c r="BM27" s="116"/>
-      <c r="BN27" s="116"/>
-      <c r="BO27" s="116"/>
-      <c r="BP27" s="116"/>
-      <c r="BQ27" s="116"/>
-      <c r="BR27" s="116"/>
-      <c r="BS27" s="116"/>
-      <c r="BT27" s="116"/>
+      <c r="AB27" s="29"/>
+      <c r="AC27" s="36"/>
+      <c r="AD27" s="36"/>
+      <c r="AE27" s="36"/>
+      <c r="AF27" s="36"/>
+      <c r="AG27" s="36"/>
+      <c r="AH27" s="36"/>
+      <c r="AI27" s="36"/>
+      <c r="AJ27" s="36"/>
+      <c r="AK27" s="36"/>
+      <c r="AL27" s="36"/>
+      <c r="AM27" s="36"/>
+      <c r="AN27" s="36"/>
+      <c r="AO27" s="36"/>
+      <c r="AP27" s="36"/>
+      <c r="AQ27" s="36"/>
+      <c r="AR27" s="36"/>
+      <c r="AS27" s="36"/>
+      <c r="AT27" s="36"/>
+      <c r="AU27" s="36"/>
+      <c r="AV27" s="36"/>
+      <c r="AW27" s="36"/>
+      <c r="AX27" s="36"/>
+      <c r="AY27" s="36"/>
+      <c r="AZ27" s="36"/>
+      <c r="BA27" s="36"/>
+      <c r="BB27" s="36"/>
+      <c r="BC27" s="36"/>
+      <c r="BD27" s="36"/>
+      <c r="BE27" s="36"/>
+      <c r="BF27" s="36"/>
+      <c r="BG27" s="36"/>
+      <c r="BH27" s="36"/>
+      <c r="BI27" s="36"/>
+      <c r="BJ27" s="36"/>
+      <c r="BK27" s="36"/>
+      <c r="BL27" s="36"/>
+      <c r="BM27" s="36"/>
+      <c r="BN27" s="36"/>
+      <c r="BO27" s="36"/>
+      <c r="BP27" s="36"/>
+      <c r="BQ27" s="36"/>
+      <c r="BR27" s="36"/>
+      <c r="BS27" s="36"/>
+      <c r="BT27" s="36"/>
     </row>
     <row r="28" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B28" s="22" t="s">
+      <c r="B28" s="38" t="s">
         <v>40</v>
       </c>
       <c r="C28" s="4" t="s">
@@ -5286,56 +5781,56 @@
         <v>49</v>
       </c>
       <c r="AB28" s="19"/>
-      <c r="AC28" s="115"/>
-      <c r="AD28" s="115"/>
-      <c r="AE28" s="115"/>
-      <c r="AF28" s="115"/>
-      <c r="AG28" s="115"/>
-      <c r="AH28" s="115"/>
-      <c r="AI28" s="115"/>
-      <c r="AJ28" s="115"/>
-      <c r="AK28" s="115"/>
-      <c r="AL28" s="115"/>
-      <c r="AM28" s="115"/>
-      <c r="AN28" s="115"/>
-      <c r="AO28" s="115"/>
-      <c r="AP28" s="115"/>
-      <c r="AQ28" s="115"/>
-      <c r="AR28" s="115"/>
-      <c r="AS28" s="115"/>
-      <c r="AT28" s="115"/>
-      <c r="AU28" s="115"/>
-      <c r="AV28" s="115"/>
-      <c r="AW28" s="115"/>
-      <c r="AX28" s="115"/>
-      <c r="AY28" s="115"/>
-      <c r="AZ28" s="115"/>
-      <c r="BA28" s="115"/>
-      <c r="BB28" s="115"/>
-      <c r="BC28" s="115"/>
-      <c r="BD28" s="115"/>
-      <c r="BE28" s="115"/>
-      <c r="BF28" s="115"/>
-      <c r="BG28" s="115"/>
-      <c r="BH28" s="115"/>
-      <c r="BI28" s="115"/>
-      <c r="BJ28" s="115"/>
-      <c r="BK28" s="115"/>
-      <c r="BL28" s="115"/>
-      <c r="BM28" s="115"/>
-      <c r="BN28" s="115"/>
-      <c r="BO28" s="115"/>
-      <c r="BP28" s="115"/>
-      <c r="BQ28" s="115"/>
-      <c r="BR28" s="115"/>
-      <c r="BS28" s="115"/>
-      <c r="BT28" s="115"/>
+      <c r="AC28" s="35"/>
+      <c r="AD28" s="35"/>
+      <c r="AE28" s="35"/>
+      <c r="AF28" s="35"/>
+      <c r="AG28" s="35"/>
+      <c r="AH28" s="35"/>
+      <c r="AI28" s="35"/>
+      <c r="AJ28" s="35"/>
+      <c r="AK28" s="35"/>
+      <c r="AL28" s="35"/>
+      <c r="AM28" s="35"/>
+      <c r="AN28" s="35"/>
+      <c r="AO28" s="35"/>
+      <c r="AP28" s="35"/>
+      <c r="AQ28" s="35"/>
+      <c r="AR28" s="35"/>
+      <c r="AS28" s="35"/>
+      <c r="AT28" s="35"/>
+      <c r="AU28" s="35"/>
+      <c r="AV28" s="35"/>
+      <c r="AW28" s="35"/>
+      <c r="AX28" s="35"/>
+      <c r="AY28" s="35"/>
+      <c r="AZ28" s="35"/>
+      <c r="BA28" s="35"/>
+      <c r="BB28" s="35"/>
+      <c r="BC28" s="35"/>
+      <c r="BD28" s="35"/>
+      <c r="BE28" s="35"/>
+      <c r="BF28" s="35"/>
+      <c r="BG28" s="35"/>
+      <c r="BH28" s="35"/>
+      <c r="BI28" s="35"/>
+      <c r="BJ28" s="35"/>
+      <c r="BK28" s="35"/>
+      <c r="BL28" s="35"/>
+      <c r="BM28" s="35"/>
+      <c r="BN28" s="35"/>
+      <c r="BO28" s="35"/>
+      <c r="BP28" s="35"/>
+      <c r="BQ28" s="35"/>
+      <c r="BR28" s="35"/>
+      <c r="BS28" s="35"/>
+      <c r="BT28" s="35"/>
     </row>
     <row r="29" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="B29" s="24"/>
+      <c r="B29" s="40"/>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
       <c r="E29" s="5"/>
@@ -5372,56 +5867,56 @@
       </c>
       <c r="AA29" s="5"/>
       <c r="AB29" s="20"/>
-      <c r="AC29" s="115"/>
-      <c r="AD29" s="115"/>
-      <c r="AE29" s="115"/>
-      <c r="AF29" s="115"/>
-      <c r="AG29" s="115"/>
-      <c r="AH29" s="115"/>
-      <c r="AI29" s="115"/>
-      <c r="AJ29" s="115"/>
-      <c r="AK29" s="115"/>
-      <c r="AL29" s="115"/>
-      <c r="AM29" s="115"/>
-      <c r="AN29" s="115"/>
-      <c r="AO29" s="115"/>
-      <c r="AP29" s="115"/>
-      <c r="AQ29" s="115"/>
-      <c r="AR29" s="115"/>
-      <c r="AS29" s="115"/>
-      <c r="AT29" s="115"/>
-      <c r="AU29" s="115"/>
-      <c r="AV29" s="115"/>
-      <c r="AW29" s="115"/>
-      <c r="AX29" s="115"/>
-      <c r="AY29" s="115"/>
-      <c r="AZ29" s="115"/>
-      <c r="BA29" s="115"/>
-      <c r="BB29" s="115"/>
-      <c r="BC29" s="115"/>
-      <c r="BD29" s="115"/>
-      <c r="BE29" s="115"/>
-      <c r="BF29" s="115"/>
-      <c r="BG29" s="115"/>
-      <c r="BH29" s="115"/>
-      <c r="BI29" s="115"/>
-      <c r="BJ29" s="115"/>
-      <c r="BK29" s="115"/>
-      <c r="BL29" s="115"/>
-      <c r="BM29" s="115"/>
-      <c r="BN29" s="115"/>
-      <c r="BO29" s="115"/>
-      <c r="BP29" s="115"/>
-      <c r="BQ29" s="115"/>
-      <c r="BR29" s="115"/>
-      <c r="BS29" s="115"/>
-      <c r="BT29" s="115"/>
+      <c r="AC29" s="35"/>
+      <c r="AD29" s="35"/>
+      <c r="AE29" s="35"/>
+      <c r="AF29" s="35"/>
+      <c r="AG29" s="35"/>
+      <c r="AH29" s="35"/>
+      <c r="AI29" s="35"/>
+      <c r="AJ29" s="35"/>
+      <c r="AK29" s="35"/>
+      <c r="AL29" s="35"/>
+      <c r="AM29" s="35"/>
+      <c r="AN29" s="35"/>
+      <c r="AO29" s="35"/>
+      <c r="AP29" s="35"/>
+      <c r="AQ29" s="35"/>
+      <c r="AR29" s="35"/>
+      <c r="AS29" s="35"/>
+      <c r="AT29" s="35"/>
+      <c r="AU29" s="35"/>
+      <c r="AV29" s="35"/>
+      <c r="AW29" s="35"/>
+      <c r="AX29" s="35"/>
+      <c r="AY29" s="35"/>
+      <c r="AZ29" s="35"/>
+      <c r="BA29" s="35"/>
+      <c r="BB29" s="35"/>
+      <c r="BC29" s="35"/>
+      <c r="BD29" s="35"/>
+      <c r="BE29" s="35"/>
+      <c r="BF29" s="35"/>
+      <c r="BG29" s="35"/>
+      <c r="BH29" s="35"/>
+      <c r="BI29" s="35"/>
+      <c r="BJ29" s="35"/>
+      <c r="BK29" s="35"/>
+      <c r="BL29" s="35"/>
+      <c r="BM29" s="35"/>
+      <c r="BN29" s="35"/>
+      <c r="BO29" s="35"/>
+      <c r="BP29" s="35"/>
+      <c r="BQ29" s="35"/>
+      <c r="BR29" s="35"/>
+      <c r="BS29" s="35"/>
+      <c r="BT29" s="35"/>
     </row>
     <row r="30" spans="1:72" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B30" s="33"/>
+      <c r="B30" s="49"/>
       <c r="C30" s="6" t="s">
         <v>58</v>
       </c>
@@ -5497,59 +5992,119 @@
       <c r="AA30" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="AB30" s="109" t="s">
+      <c r="AB30" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="AC30" s="116"/>
-      <c r="AD30" s="116"/>
-      <c r="AE30" s="116"/>
-      <c r="AF30" s="116"/>
-      <c r="AG30" s="116"/>
-      <c r="AH30" s="116"/>
-      <c r="AI30" s="116"/>
-      <c r="AJ30" s="116"/>
-      <c r="AK30" s="116"/>
-      <c r="AL30" s="116"/>
-      <c r="AM30" s="116"/>
-      <c r="AN30" s="116"/>
-      <c r="AO30" s="116"/>
-      <c r="AP30" s="116"/>
-      <c r="AQ30" s="116"/>
-      <c r="AR30" s="116"/>
-      <c r="AS30" s="116"/>
-      <c r="AT30" s="116"/>
-      <c r="AU30" s="116"/>
-      <c r="AV30" s="116"/>
-      <c r="AW30" s="116"/>
-      <c r="AX30" s="116"/>
-      <c r="AY30" s="116"/>
-      <c r="AZ30" s="116"/>
-      <c r="BA30" s="116"/>
-      <c r="BB30" s="116"/>
-      <c r="BC30" s="116"/>
-      <c r="BD30" s="116"/>
-      <c r="BE30" s="116"/>
-      <c r="BF30" s="116"/>
-      <c r="BG30" s="116"/>
-      <c r="BH30" s="116"/>
-      <c r="BI30" s="116"/>
-      <c r="BJ30" s="116"/>
-      <c r="BK30" s="116"/>
-      <c r="BL30" s="116"/>
-      <c r="BM30" s="116"/>
-      <c r="BN30" s="116"/>
-      <c r="BO30" s="116"/>
-      <c r="BP30" s="116"/>
-      <c r="BQ30" s="116"/>
-      <c r="BR30" s="116"/>
-      <c r="BS30" s="116"/>
-      <c r="BT30" s="116"/>
+      <c r="AC30" s="36"/>
+      <c r="AD30" s="36"/>
+      <c r="AE30" s="36"/>
+      <c r="AF30" s="36"/>
+      <c r="AG30" s="36"/>
+      <c r="AH30" s="36"/>
+      <c r="AI30" s="36"/>
+      <c r="AJ30" s="36"/>
+      <c r="AK30" s="36"/>
+      <c r="AL30" s="36"/>
+      <c r="AM30" s="36"/>
+      <c r="AN30" s="36"/>
+      <c r="AO30" s="36"/>
+      <c r="AP30" s="36"/>
+      <c r="AQ30" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="AR30" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="AS30" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="AT30" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="AU30" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="AV30" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="AW30" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="AX30" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="AY30" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="AZ30" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="BA30" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="BB30" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="BC30" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="BD30" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="BE30" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="BF30" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="BG30" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH30" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="BI30" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="BJ30" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="BK30" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="BL30" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="BM30" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="BN30" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="BO30" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="BP30" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="BQ30" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="BR30" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="BS30" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="BT30" s="29" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="31" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B31" s="22" t="s">
+      <c r="B31" s="38" t="s">
         <v>41</v>
       </c>
       <c r="C31" s="4" t="s">
@@ -5604,56 +6159,56 @@
       <c r="AB31" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="AC31" s="115"/>
-      <c r="AD31" s="115"/>
-      <c r="AE31" s="115"/>
-      <c r="AF31" s="115"/>
-      <c r="AG31" s="115"/>
-      <c r="AH31" s="115"/>
-      <c r="AI31" s="115"/>
-      <c r="AJ31" s="115"/>
-      <c r="AK31" s="115"/>
-      <c r="AL31" s="115"/>
-      <c r="AM31" s="115"/>
-      <c r="AN31" s="115"/>
-      <c r="AO31" s="115"/>
-      <c r="AP31" s="115"/>
-      <c r="AQ31" s="115"/>
-      <c r="AR31" s="115"/>
-      <c r="AS31" s="115"/>
-      <c r="AT31" s="115"/>
-      <c r="AU31" s="115"/>
-      <c r="AV31" s="115"/>
-      <c r="AW31" s="115"/>
-      <c r="AX31" s="115"/>
-      <c r="AY31" s="115"/>
-      <c r="AZ31" s="115"/>
-      <c r="BA31" s="115"/>
-      <c r="BB31" s="115"/>
-      <c r="BC31" s="115"/>
-      <c r="BD31" s="115"/>
-      <c r="BE31" s="115"/>
-      <c r="BF31" s="115"/>
-      <c r="BG31" s="115"/>
-      <c r="BH31" s="115"/>
-      <c r="BI31" s="115"/>
-      <c r="BJ31" s="115"/>
-      <c r="BK31" s="115"/>
-      <c r="BL31" s="115"/>
-      <c r="BM31" s="115"/>
-      <c r="BN31" s="115"/>
-      <c r="BO31" s="115"/>
-      <c r="BP31" s="115"/>
-      <c r="BQ31" s="115"/>
-      <c r="BR31" s="115"/>
-      <c r="BS31" s="115"/>
-      <c r="BT31" s="115"/>
+      <c r="AC31" s="35"/>
+      <c r="AD31" s="35"/>
+      <c r="AE31" s="35"/>
+      <c r="AF31" s="35"/>
+      <c r="AG31" s="35"/>
+      <c r="AH31" s="35"/>
+      <c r="AI31" s="35"/>
+      <c r="AJ31" s="35"/>
+      <c r="AK31" s="35"/>
+      <c r="AL31" s="35"/>
+      <c r="AM31" s="35"/>
+      <c r="AN31" s="35"/>
+      <c r="AO31" s="35"/>
+      <c r="AP31" s="35"/>
+      <c r="AQ31" s="35"/>
+      <c r="AR31" s="35"/>
+      <c r="AS31" s="35"/>
+      <c r="AT31" s="35"/>
+      <c r="AU31" s="35"/>
+      <c r="AV31" s="35"/>
+      <c r="AW31" s="35"/>
+      <c r="AX31" s="35"/>
+      <c r="AY31" s="35"/>
+      <c r="AZ31" s="35"/>
+      <c r="BA31" s="35"/>
+      <c r="BB31" s="35"/>
+      <c r="BC31" s="35"/>
+      <c r="BD31" s="35"/>
+      <c r="BE31" s="35"/>
+      <c r="BF31" s="35"/>
+      <c r="BG31" s="35"/>
+      <c r="BH31" s="35"/>
+      <c r="BI31" s="35"/>
+      <c r="BJ31" s="35"/>
+      <c r="BK31" s="35"/>
+      <c r="BL31" s="35"/>
+      <c r="BM31" s="35"/>
+      <c r="BN31" s="35"/>
+      <c r="BO31" s="35"/>
+      <c r="BP31" s="35"/>
+      <c r="BQ31" s="35"/>
+      <c r="BR31" s="35"/>
+      <c r="BS31" s="35"/>
+      <c r="BT31" s="35"/>
     </row>
     <row r="32" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="B32" s="24"/>
+      <c r="B32" s="40"/>
       <c r="C32" s="5" t="s">
         <v>61</v>
       </c>
@@ -5722,56 +6277,56 @@
       <c r="AB32" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="AC32" s="115"/>
-      <c r="AD32" s="115"/>
-      <c r="AE32" s="115"/>
-      <c r="AF32" s="115"/>
-      <c r="AG32" s="115"/>
-      <c r="AH32" s="115"/>
-      <c r="AI32" s="115"/>
-      <c r="AJ32" s="115"/>
-      <c r="AK32" s="115"/>
-      <c r="AL32" s="115"/>
-      <c r="AM32" s="115"/>
-      <c r="AN32" s="115"/>
-      <c r="AO32" s="115"/>
-      <c r="AP32" s="115"/>
-      <c r="AQ32" s="115"/>
-      <c r="AR32" s="115"/>
-      <c r="AS32" s="115"/>
-      <c r="AT32" s="115"/>
-      <c r="AU32" s="115"/>
-      <c r="AV32" s="115"/>
-      <c r="AW32" s="115"/>
-      <c r="AX32" s="115"/>
-      <c r="AY32" s="115"/>
-      <c r="AZ32" s="115"/>
-      <c r="BA32" s="115"/>
-      <c r="BB32" s="115"/>
-      <c r="BC32" s="115"/>
-      <c r="BD32" s="115"/>
-      <c r="BE32" s="115"/>
-      <c r="BF32" s="115"/>
-      <c r="BG32" s="115"/>
-      <c r="BH32" s="115"/>
-      <c r="BI32" s="115"/>
-      <c r="BJ32" s="115"/>
-      <c r="BK32" s="115"/>
-      <c r="BL32" s="115"/>
-      <c r="BM32" s="115"/>
-      <c r="BN32" s="115"/>
-      <c r="BO32" s="115"/>
-      <c r="BP32" s="115"/>
-      <c r="BQ32" s="115"/>
-      <c r="BR32" s="115"/>
-      <c r="BS32" s="115"/>
-      <c r="BT32" s="115"/>
+      <c r="AC32" s="35"/>
+      <c r="AD32" s="35"/>
+      <c r="AE32" s="35"/>
+      <c r="AF32" s="35"/>
+      <c r="AG32" s="35"/>
+      <c r="AH32" s="35"/>
+      <c r="AI32" s="35"/>
+      <c r="AJ32" s="35"/>
+      <c r="AK32" s="35"/>
+      <c r="AL32" s="35"/>
+      <c r="AM32" s="35"/>
+      <c r="AN32" s="35"/>
+      <c r="AO32" s="35"/>
+      <c r="AP32" s="35"/>
+      <c r="AQ32" s="35"/>
+      <c r="AR32" s="35"/>
+      <c r="AS32" s="35"/>
+      <c r="AT32" s="35"/>
+      <c r="AU32" s="35"/>
+      <c r="AV32" s="35"/>
+      <c r="AW32" s="35"/>
+      <c r="AX32" s="35"/>
+      <c r="AY32" s="35"/>
+      <c r="AZ32" s="35"/>
+      <c r="BA32" s="35"/>
+      <c r="BB32" s="35"/>
+      <c r="BC32" s="35"/>
+      <c r="BD32" s="35"/>
+      <c r="BE32" s="35"/>
+      <c r="BF32" s="35"/>
+      <c r="BG32" s="35"/>
+      <c r="BH32" s="35"/>
+      <c r="BI32" s="35"/>
+      <c r="BJ32" s="35"/>
+      <c r="BK32" s="35"/>
+      <c r="BL32" s="35"/>
+      <c r="BM32" s="35"/>
+      <c r="BN32" s="35"/>
+      <c r="BO32" s="35"/>
+      <c r="BP32" s="35"/>
+      <c r="BQ32" s="35"/>
+      <c r="BR32" s="35"/>
+      <c r="BS32" s="35"/>
+      <c r="BT32" s="35"/>
     </row>
     <row r="33" spans="1:72" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B33" s="33"/>
+      <c r="B33" s="49"/>
       <c r="C33" s="6"/>
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
@@ -5799,57 +6354,57 @@
       <c r="Y33" s="6"/>
       <c r="Z33" s="6"/>
       <c r="AA33" s="6"/>
-      <c r="AB33" s="109"/>
-      <c r="AC33" s="116"/>
-      <c r="AD33" s="116"/>
-      <c r="AE33" s="116"/>
-      <c r="AF33" s="116"/>
-      <c r="AG33" s="116"/>
-      <c r="AH33" s="116"/>
-      <c r="AI33" s="116"/>
-      <c r="AJ33" s="116"/>
-      <c r="AK33" s="116"/>
-      <c r="AL33" s="116"/>
-      <c r="AM33" s="116"/>
-      <c r="AN33" s="116"/>
-      <c r="AO33" s="116"/>
-      <c r="AP33" s="116"/>
-      <c r="AQ33" s="116"/>
-      <c r="AR33" s="116"/>
-      <c r="AS33" s="116"/>
-      <c r="AT33" s="116"/>
-      <c r="AU33" s="116"/>
-      <c r="AV33" s="116"/>
-      <c r="AW33" s="116"/>
-      <c r="AX33" s="116"/>
-      <c r="AY33" s="116"/>
-      <c r="AZ33" s="116"/>
-      <c r="BA33" s="116"/>
-      <c r="BB33" s="116"/>
-      <c r="BC33" s="116"/>
-      <c r="BD33" s="116"/>
-      <c r="BE33" s="116"/>
-      <c r="BF33" s="116"/>
-      <c r="BG33" s="116"/>
-      <c r="BH33" s="116"/>
-      <c r="BI33" s="116"/>
-      <c r="BJ33" s="116"/>
-      <c r="BK33" s="116"/>
-      <c r="BL33" s="116"/>
-      <c r="BM33" s="116"/>
-      <c r="BN33" s="116"/>
-      <c r="BO33" s="116"/>
-      <c r="BP33" s="116"/>
-      <c r="BQ33" s="116"/>
-      <c r="BR33" s="116"/>
-      <c r="BS33" s="116"/>
-      <c r="BT33" s="116"/>
+      <c r="AB33" s="29"/>
+      <c r="AC33" s="36"/>
+      <c r="AD33" s="36"/>
+      <c r="AE33" s="36"/>
+      <c r="AF33" s="36"/>
+      <c r="AG33" s="36"/>
+      <c r="AH33" s="36"/>
+      <c r="AI33" s="36"/>
+      <c r="AJ33" s="36"/>
+      <c r="AK33" s="36"/>
+      <c r="AL33" s="36"/>
+      <c r="AM33" s="36"/>
+      <c r="AN33" s="36"/>
+      <c r="AO33" s="36"/>
+      <c r="AP33" s="36"/>
+      <c r="AQ33" s="36"/>
+      <c r="AR33" s="36"/>
+      <c r="AS33" s="36"/>
+      <c r="AT33" s="36"/>
+      <c r="AU33" s="36"/>
+      <c r="AV33" s="36"/>
+      <c r="AW33" s="36"/>
+      <c r="AX33" s="36"/>
+      <c r="AY33" s="36"/>
+      <c r="AZ33" s="36"/>
+      <c r="BA33" s="36"/>
+      <c r="BB33" s="36"/>
+      <c r="BC33" s="36"/>
+      <c r="BD33" s="36"/>
+      <c r="BE33" s="36"/>
+      <c r="BF33" s="36"/>
+      <c r="BG33" s="36"/>
+      <c r="BH33" s="36"/>
+      <c r="BI33" s="36"/>
+      <c r="BJ33" s="36"/>
+      <c r="BK33" s="36"/>
+      <c r="BL33" s="36"/>
+      <c r="BM33" s="36"/>
+      <c r="BN33" s="36"/>
+      <c r="BO33" s="36"/>
+      <c r="BP33" s="36"/>
+      <c r="BQ33" s="36"/>
+      <c r="BR33" s="36"/>
+      <c r="BS33" s="36"/>
+      <c r="BT33" s="36"/>
     </row>
     <row r="34" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="36" t="s">
+      <c r="B34" s="52" t="s">
         <v>42</v>
       </c>
       <c r="C34" s="4" t="s">
@@ -5908,56 +6463,56 @@
       <c r="AB34" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="AC34" s="115"/>
-      <c r="AD34" s="115"/>
-      <c r="AE34" s="115"/>
-      <c r="AF34" s="115"/>
-      <c r="AG34" s="115"/>
-      <c r="AH34" s="115"/>
-      <c r="AI34" s="115"/>
-      <c r="AJ34" s="115"/>
-      <c r="AK34" s="115"/>
-      <c r="AL34" s="115"/>
-      <c r="AM34" s="115"/>
-      <c r="AN34" s="115"/>
-      <c r="AO34" s="115"/>
-      <c r="AP34" s="115"/>
-      <c r="AQ34" s="115"/>
-      <c r="AR34" s="115"/>
-      <c r="AS34" s="115"/>
-      <c r="AT34" s="115"/>
-      <c r="AU34" s="115"/>
-      <c r="AV34" s="115"/>
-      <c r="AW34" s="115"/>
-      <c r="AX34" s="115"/>
-      <c r="AY34" s="115"/>
-      <c r="AZ34" s="115"/>
-      <c r="BA34" s="115"/>
-      <c r="BB34" s="115"/>
-      <c r="BC34" s="115"/>
-      <c r="BD34" s="115"/>
-      <c r="BE34" s="115"/>
-      <c r="BF34" s="115"/>
-      <c r="BG34" s="115"/>
-      <c r="BH34" s="115"/>
-      <c r="BI34" s="115"/>
-      <c r="BJ34" s="115"/>
-      <c r="BK34" s="115"/>
-      <c r="BL34" s="115"/>
-      <c r="BM34" s="115"/>
-      <c r="BN34" s="115"/>
-      <c r="BO34" s="115"/>
-      <c r="BP34" s="115"/>
-      <c r="BQ34" s="115"/>
-      <c r="BR34" s="115"/>
-      <c r="BS34" s="115"/>
-      <c r="BT34" s="115"/>
+      <c r="AC34" s="35"/>
+      <c r="AD34" s="35"/>
+      <c r="AE34" s="35"/>
+      <c r="AF34" s="35"/>
+      <c r="AG34" s="35"/>
+      <c r="AH34" s="35"/>
+      <c r="AI34" s="35"/>
+      <c r="AJ34" s="35"/>
+      <c r="AK34" s="35"/>
+      <c r="AL34" s="35"/>
+      <c r="AM34" s="35"/>
+      <c r="AN34" s="35"/>
+      <c r="AO34" s="35"/>
+      <c r="AP34" s="35"/>
+      <c r="AQ34" s="35"/>
+      <c r="AR34" s="35"/>
+      <c r="AS34" s="35"/>
+      <c r="AT34" s="35"/>
+      <c r="AU34" s="35"/>
+      <c r="AV34" s="35"/>
+      <c r="AW34" s="35"/>
+      <c r="AX34" s="35"/>
+      <c r="AY34" s="35"/>
+      <c r="AZ34" s="35"/>
+      <c r="BA34" s="35"/>
+      <c r="BB34" s="35"/>
+      <c r="BC34" s="35"/>
+      <c r="BD34" s="35"/>
+      <c r="BE34" s="35"/>
+      <c r="BF34" s="35"/>
+      <c r="BG34" s="35"/>
+      <c r="BH34" s="35"/>
+      <c r="BI34" s="35"/>
+      <c r="BJ34" s="35"/>
+      <c r="BK34" s="35"/>
+      <c r="BL34" s="35"/>
+      <c r="BM34" s="35"/>
+      <c r="BN34" s="35"/>
+      <c r="BO34" s="35"/>
+      <c r="BP34" s="35"/>
+      <c r="BQ34" s="35"/>
+      <c r="BR34" s="35"/>
+      <c r="BS34" s="35"/>
+      <c r="BT34" s="35"/>
     </row>
     <row r="35" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="B35" s="37"/>
+      <c r="B35" s="53"/>
       <c r="C35" s="5"/>
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
@@ -6002,56 +6557,56 @@
       <c r="Z35" s="5"/>
       <c r="AA35" s="5"/>
       <c r="AB35" s="20"/>
-      <c r="AC35" s="115"/>
-      <c r="AD35" s="115"/>
-      <c r="AE35" s="115"/>
-      <c r="AF35" s="115"/>
-      <c r="AG35" s="115"/>
-      <c r="AH35" s="115"/>
-      <c r="AI35" s="115"/>
-      <c r="AJ35" s="115"/>
-      <c r="AK35" s="115"/>
-      <c r="AL35" s="115"/>
-      <c r="AM35" s="115"/>
-      <c r="AN35" s="115"/>
-      <c r="AO35" s="115"/>
-      <c r="AP35" s="115"/>
-      <c r="AQ35" s="115"/>
-      <c r="AR35" s="115"/>
-      <c r="AS35" s="115"/>
-      <c r="AT35" s="115"/>
-      <c r="AU35" s="115"/>
-      <c r="AV35" s="115"/>
-      <c r="AW35" s="115"/>
-      <c r="AX35" s="115"/>
-      <c r="AY35" s="115"/>
-      <c r="AZ35" s="115"/>
-      <c r="BA35" s="115"/>
-      <c r="BB35" s="115"/>
-      <c r="BC35" s="115"/>
-      <c r="BD35" s="115"/>
-      <c r="BE35" s="115"/>
-      <c r="BF35" s="115"/>
-      <c r="BG35" s="115"/>
-      <c r="BH35" s="115"/>
-      <c r="BI35" s="115"/>
-      <c r="BJ35" s="115"/>
-      <c r="BK35" s="115"/>
-      <c r="BL35" s="115"/>
-      <c r="BM35" s="115"/>
-      <c r="BN35" s="115"/>
-      <c r="BO35" s="115"/>
-      <c r="BP35" s="115"/>
-      <c r="BQ35" s="115"/>
-      <c r="BR35" s="115"/>
-      <c r="BS35" s="115"/>
-      <c r="BT35" s="115"/>
+      <c r="AC35" s="35"/>
+      <c r="AD35" s="35"/>
+      <c r="AE35" s="35"/>
+      <c r="AF35" s="35"/>
+      <c r="AG35" s="35"/>
+      <c r="AH35" s="35"/>
+      <c r="AI35" s="35"/>
+      <c r="AJ35" s="35"/>
+      <c r="AK35" s="35"/>
+      <c r="AL35" s="35"/>
+      <c r="AM35" s="35"/>
+      <c r="AN35" s="35"/>
+      <c r="AO35" s="35"/>
+      <c r="AP35" s="35"/>
+      <c r="AQ35" s="35"/>
+      <c r="AR35" s="35"/>
+      <c r="AS35" s="35"/>
+      <c r="AT35" s="35"/>
+      <c r="AU35" s="35"/>
+      <c r="AV35" s="35"/>
+      <c r="AW35" s="35"/>
+      <c r="AX35" s="35"/>
+      <c r="AY35" s="35"/>
+      <c r="AZ35" s="35"/>
+      <c r="BA35" s="35"/>
+      <c r="BB35" s="35"/>
+      <c r="BC35" s="35"/>
+      <c r="BD35" s="35"/>
+      <c r="BE35" s="35"/>
+      <c r="BF35" s="35"/>
+      <c r="BG35" s="35"/>
+      <c r="BH35" s="35"/>
+      <c r="BI35" s="35"/>
+      <c r="BJ35" s="35"/>
+      <c r="BK35" s="35"/>
+      <c r="BL35" s="35"/>
+      <c r="BM35" s="35"/>
+      <c r="BN35" s="35"/>
+      <c r="BO35" s="35"/>
+      <c r="BP35" s="35"/>
+      <c r="BQ35" s="35"/>
+      <c r="BR35" s="35"/>
+      <c r="BS35" s="35"/>
+      <c r="BT35" s="35"/>
     </row>
     <row r="36" spans="1:72" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B36" s="38"/>
+      <c r="B36" s="54"/>
       <c r="C36" s="6"/>
       <c r="D36" s="6"/>
       <c r="E36" s="6"/>
@@ -6081,57 +6636,57 @@
       <c r="Y36" s="6"/>
       <c r="Z36" s="6"/>
       <c r="AA36" s="6"/>
-      <c r="AB36" s="109"/>
-      <c r="AC36" s="116"/>
-      <c r="AD36" s="116"/>
-      <c r="AE36" s="116"/>
-      <c r="AF36" s="116"/>
-      <c r="AG36" s="116"/>
-      <c r="AH36" s="116"/>
-      <c r="AI36" s="116"/>
-      <c r="AJ36" s="116"/>
-      <c r="AK36" s="116"/>
-      <c r="AL36" s="116"/>
-      <c r="AM36" s="116"/>
-      <c r="AN36" s="116"/>
-      <c r="AO36" s="116"/>
-      <c r="AP36" s="116"/>
-      <c r="AQ36" s="116"/>
-      <c r="AR36" s="116"/>
-      <c r="AS36" s="116"/>
-      <c r="AT36" s="116"/>
-      <c r="AU36" s="116"/>
-      <c r="AV36" s="116"/>
-      <c r="AW36" s="116"/>
-      <c r="AX36" s="116"/>
-      <c r="AY36" s="116"/>
-      <c r="AZ36" s="116"/>
-      <c r="BA36" s="116"/>
-      <c r="BB36" s="116"/>
-      <c r="BC36" s="116"/>
-      <c r="BD36" s="116"/>
-      <c r="BE36" s="116"/>
-      <c r="BF36" s="116"/>
-      <c r="BG36" s="116"/>
-      <c r="BH36" s="116"/>
-      <c r="BI36" s="116"/>
-      <c r="BJ36" s="116"/>
-      <c r="BK36" s="116"/>
-      <c r="BL36" s="116"/>
-      <c r="BM36" s="116"/>
-      <c r="BN36" s="116"/>
-      <c r="BO36" s="116"/>
-      <c r="BP36" s="116"/>
-      <c r="BQ36" s="116"/>
-      <c r="BR36" s="116"/>
-      <c r="BS36" s="116"/>
-      <c r="BT36" s="116"/>
+      <c r="AB36" s="29"/>
+      <c r="AC36" s="36"/>
+      <c r="AD36" s="36"/>
+      <c r="AE36" s="36"/>
+      <c r="AF36" s="36"/>
+      <c r="AG36" s="36"/>
+      <c r="AH36" s="36"/>
+      <c r="AI36" s="36"/>
+      <c r="AJ36" s="36"/>
+      <c r="AK36" s="36"/>
+      <c r="AL36" s="36"/>
+      <c r="AM36" s="36"/>
+      <c r="AN36" s="36"/>
+      <c r="AO36" s="36"/>
+      <c r="AP36" s="36"/>
+      <c r="AQ36" s="36"/>
+      <c r="AR36" s="36"/>
+      <c r="AS36" s="36"/>
+      <c r="AT36" s="36"/>
+      <c r="AU36" s="36"/>
+      <c r="AV36" s="36"/>
+      <c r="AW36" s="36"/>
+      <c r="AX36" s="36"/>
+      <c r="AY36" s="36"/>
+      <c r="AZ36" s="36"/>
+      <c r="BA36" s="36"/>
+      <c r="BB36" s="36"/>
+      <c r="BC36" s="36"/>
+      <c r="BD36" s="36"/>
+      <c r="BE36" s="36"/>
+      <c r="BF36" s="36"/>
+      <c r="BG36" s="36"/>
+      <c r="BH36" s="36"/>
+      <c r="BI36" s="36"/>
+      <c r="BJ36" s="36"/>
+      <c r="BK36" s="36"/>
+      <c r="BL36" s="36"/>
+      <c r="BM36" s="36"/>
+      <c r="BN36" s="36"/>
+      <c r="BO36" s="36"/>
+      <c r="BP36" s="36"/>
+      <c r="BQ36" s="36"/>
+      <c r="BR36" s="36"/>
+      <c r="BS36" s="36"/>
+      <c r="BT36" s="36"/>
     </row>
     <row r="37" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B37" s="22" t="s">
+      <c r="B37" s="38" t="s">
         <v>43</v>
       </c>
       <c r="C37" s="4" t="s">
@@ -6202,56 +6757,56 @@
         <v>49</v>
       </c>
       <c r="AB37" s="19"/>
-      <c r="AC37" s="115"/>
-      <c r="AD37" s="115"/>
-      <c r="AE37" s="115"/>
-      <c r="AF37" s="115"/>
-      <c r="AG37" s="115"/>
-      <c r="AH37" s="115"/>
-      <c r="AI37" s="115"/>
-      <c r="AJ37" s="115"/>
-      <c r="AK37" s="115"/>
-      <c r="AL37" s="115"/>
-      <c r="AM37" s="115"/>
-      <c r="AN37" s="115"/>
-      <c r="AO37" s="115"/>
-      <c r="AP37" s="115"/>
-      <c r="AQ37" s="115"/>
-      <c r="AR37" s="115"/>
-      <c r="AS37" s="115"/>
-      <c r="AT37" s="115"/>
-      <c r="AU37" s="115"/>
-      <c r="AV37" s="115"/>
-      <c r="AW37" s="115"/>
-      <c r="AX37" s="115"/>
-      <c r="AY37" s="115"/>
-      <c r="AZ37" s="115"/>
-      <c r="BA37" s="115"/>
-      <c r="BB37" s="115"/>
-      <c r="BC37" s="115"/>
-      <c r="BD37" s="115"/>
-      <c r="BE37" s="115"/>
-      <c r="BF37" s="115"/>
-      <c r="BG37" s="115"/>
-      <c r="BH37" s="115"/>
-      <c r="BI37" s="115"/>
-      <c r="BJ37" s="115"/>
-      <c r="BK37" s="115"/>
-      <c r="BL37" s="115"/>
-      <c r="BM37" s="115"/>
-      <c r="BN37" s="115"/>
-      <c r="BO37" s="115"/>
-      <c r="BP37" s="115"/>
-      <c r="BQ37" s="115"/>
-      <c r="BR37" s="115"/>
-      <c r="BS37" s="115"/>
-      <c r="BT37" s="115"/>
+      <c r="AC37" s="35"/>
+      <c r="AD37" s="35"/>
+      <c r="AE37" s="35"/>
+      <c r="AF37" s="35"/>
+      <c r="AG37" s="35"/>
+      <c r="AH37" s="35"/>
+      <c r="AI37" s="35"/>
+      <c r="AJ37" s="35"/>
+      <c r="AK37" s="35"/>
+      <c r="AL37" s="35"/>
+      <c r="AM37" s="35"/>
+      <c r="AN37" s="35"/>
+      <c r="AO37" s="35"/>
+      <c r="AP37" s="35"/>
+      <c r="AQ37" s="35"/>
+      <c r="AR37" s="35"/>
+      <c r="AS37" s="35"/>
+      <c r="AT37" s="35"/>
+      <c r="AU37" s="35"/>
+      <c r="AV37" s="35"/>
+      <c r="AW37" s="35"/>
+      <c r="AX37" s="35"/>
+      <c r="AY37" s="35"/>
+      <c r="AZ37" s="35"/>
+      <c r="BA37" s="35"/>
+      <c r="BB37" s="35"/>
+      <c r="BC37" s="35"/>
+      <c r="BD37" s="35"/>
+      <c r="BE37" s="35"/>
+      <c r="BF37" s="35"/>
+      <c r="BG37" s="35"/>
+      <c r="BH37" s="35"/>
+      <c r="BI37" s="35"/>
+      <c r="BJ37" s="35"/>
+      <c r="BK37" s="35"/>
+      <c r="BL37" s="35"/>
+      <c r="BM37" s="35"/>
+      <c r="BN37" s="35"/>
+      <c r="BO37" s="35"/>
+      <c r="BP37" s="35"/>
+      <c r="BQ37" s="35"/>
+      <c r="BR37" s="35"/>
+      <c r="BS37" s="35"/>
+      <c r="BT37" s="35"/>
     </row>
     <row r="38" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A38" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="B38" s="24"/>
+      <c r="B38" s="40"/>
       <c r="C38" s="5"/>
       <c r="D38" s="5"/>
       <c r="E38" s="5" t="s">
@@ -6295,56 +6850,56 @@
       </c>
       <c r="AA38" s="5"/>
       <c r="AB38" s="20"/>
-      <c r="AC38" s="115"/>
-      <c r="AD38" s="115"/>
-      <c r="AE38" s="115"/>
-      <c r="AF38" s="115"/>
-      <c r="AG38" s="115"/>
-      <c r="AH38" s="115"/>
-      <c r="AI38" s="115"/>
-      <c r="AJ38" s="115"/>
-      <c r="AK38" s="115"/>
-      <c r="AL38" s="115"/>
-      <c r="AM38" s="115"/>
-      <c r="AN38" s="115"/>
-      <c r="AO38" s="115"/>
-      <c r="AP38" s="115"/>
-      <c r="AQ38" s="115"/>
-      <c r="AR38" s="115"/>
-      <c r="AS38" s="115"/>
-      <c r="AT38" s="115"/>
-      <c r="AU38" s="115"/>
-      <c r="AV38" s="115"/>
-      <c r="AW38" s="115"/>
-      <c r="AX38" s="115"/>
-      <c r="AY38" s="115"/>
-      <c r="AZ38" s="115"/>
-      <c r="BA38" s="115"/>
-      <c r="BB38" s="115"/>
-      <c r="BC38" s="115"/>
-      <c r="BD38" s="115"/>
-      <c r="BE38" s="115"/>
-      <c r="BF38" s="115"/>
-      <c r="BG38" s="115"/>
-      <c r="BH38" s="115"/>
-      <c r="BI38" s="115"/>
-      <c r="BJ38" s="115"/>
-      <c r="BK38" s="115"/>
-      <c r="BL38" s="115"/>
-      <c r="BM38" s="115"/>
-      <c r="BN38" s="115"/>
-      <c r="BO38" s="115"/>
-      <c r="BP38" s="115"/>
-      <c r="BQ38" s="115"/>
-      <c r="BR38" s="115"/>
-      <c r="BS38" s="115"/>
-      <c r="BT38" s="115"/>
+      <c r="AC38" s="35"/>
+      <c r="AD38" s="35"/>
+      <c r="AE38" s="35"/>
+      <c r="AF38" s="35"/>
+      <c r="AG38" s="35"/>
+      <c r="AH38" s="35"/>
+      <c r="AI38" s="35"/>
+      <c r="AJ38" s="35"/>
+      <c r="AK38" s="35"/>
+      <c r="AL38" s="35"/>
+      <c r="AM38" s="35"/>
+      <c r="AN38" s="35"/>
+      <c r="AO38" s="35"/>
+      <c r="AP38" s="35"/>
+      <c r="AQ38" s="35"/>
+      <c r="AR38" s="35"/>
+      <c r="AS38" s="35"/>
+      <c r="AT38" s="35"/>
+      <c r="AU38" s="35"/>
+      <c r="AV38" s="35"/>
+      <c r="AW38" s="35"/>
+      <c r="AX38" s="35"/>
+      <c r="AY38" s="35"/>
+      <c r="AZ38" s="35"/>
+      <c r="BA38" s="35"/>
+      <c r="BB38" s="35"/>
+      <c r="BC38" s="35"/>
+      <c r="BD38" s="35"/>
+      <c r="BE38" s="35"/>
+      <c r="BF38" s="35"/>
+      <c r="BG38" s="35"/>
+      <c r="BH38" s="35"/>
+      <c r="BI38" s="35"/>
+      <c r="BJ38" s="35"/>
+      <c r="BK38" s="35"/>
+      <c r="BL38" s="35"/>
+      <c r="BM38" s="35"/>
+      <c r="BN38" s="35"/>
+      <c r="BO38" s="35"/>
+      <c r="BP38" s="35"/>
+      <c r="BQ38" s="35"/>
+      <c r="BR38" s="35"/>
+      <c r="BS38" s="35"/>
+      <c r="BT38" s="35"/>
     </row>
     <row r="39" spans="1:72" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B39" s="33"/>
+      <c r="B39" s="49"/>
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
@@ -6376,57 +6931,57 @@
       <c r="Y39" s="6"/>
       <c r="Z39" s="6"/>
       <c r="AA39" s="6"/>
-      <c r="AB39" s="109"/>
-      <c r="AC39" s="116"/>
-      <c r="AD39" s="116"/>
-      <c r="AE39" s="116"/>
-      <c r="AF39" s="116"/>
-      <c r="AG39" s="116"/>
-      <c r="AH39" s="116"/>
-      <c r="AI39" s="116"/>
-      <c r="AJ39" s="116"/>
-      <c r="AK39" s="116"/>
-      <c r="AL39" s="116"/>
-      <c r="AM39" s="116"/>
-      <c r="AN39" s="116"/>
-      <c r="AO39" s="116"/>
-      <c r="AP39" s="116"/>
-      <c r="AQ39" s="116"/>
-      <c r="AR39" s="116"/>
-      <c r="AS39" s="116"/>
-      <c r="AT39" s="116"/>
-      <c r="AU39" s="116"/>
-      <c r="AV39" s="116"/>
-      <c r="AW39" s="116"/>
-      <c r="AX39" s="116"/>
-      <c r="AY39" s="116"/>
-      <c r="AZ39" s="116"/>
-      <c r="BA39" s="116"/>
-      <c r="BB39" s="116"/>
-      <c r="BC39" s="116"/>
-      <c r="BD39" s="116"/>
-      <c r="BE39" s="116"/>
-      <c r="BF39" s="116"/>
-      <c r="BG39" s="116"/>
-      <c r="BH39" s="116"/>
-      <c r="BI39" s="116"/>
-      <c r="BJ39" s="116"/>
-      <c r="BK39" s="116"/>
-      <c r="BL39" s="116"/>
-      <c r="BM39" s="116"/>
-      <c r="BN39" s="116"/>
-      <c r="BO39" s="116"/>
-      <c r="BP39" s="116"/>
-      <c r="BQ39" s="116"/>
-      <c r="BR39" s="116"/>
-      <c r="BS39" s="116"/>
-      <c r="BT39" s="116"/>
+      <c r="AB39" s="29"/>
+      <c r="AC39" s="36"/>
+      <c r="AD39" s="36"/>
+      <c r="AE39" s="36"/>
+      <c r="AF39" s="36"/>
+      <c r="AG39" s="36"/>
+      <c r="AH39" s="36"/>
+      <c r="AI39" s="36"/>
+      <c r="AJ39" s="36"/>
+      <c r="AK39" s="36"/>
+      <c r="AL39" s="36"/>
+      <c r="AM39" s="36"/>
+      <c r="AN39" s="36"/>
+      <c r="AO39" s="36"/>
+      <c r="AP39" s="36"/>
+      <c r="AQ39" s="36"/>
+      <c r="AR39" s="36"/>
+      <c r="AS39" s="36"/>
+      <c r="AT39" s="36"/>
+      <c r="AU39" s="36"/>
+      <c r="AV39" s="36"/>
+      <c r="AW39" s="36"/>
+      <c r="AX39" s="36"/>
+      <c r="AY39" s="36"/>
+      <c r="AZ39" s="36"/>
+      <c r="BA39" s="36"/>
+      <c r="BB39" s="36"/>
+      <c r="BC39" s="36"/>
+      <c r="BD39" s="36"/>
+      <c r="BE39" s="36"/>
+      <c r="BF39" s="36"/>
+      <c r="BG39" s="36"/>
+      <c r="BH39" s="36"/>
+      <c r="BI39" s="36"/>
+      <c r="BJ39" s="36"/>
+      <c r="BK39" s="36"/>
+      <c r="BL39" s="36"/>
+      <c r="BM39" s="36"/>
+      <c r="BN39" s="36"/>
+      <c r="BO39" s="36"/>
+      <c r="BP39" s="36"/>
+      <c r="BQ39" s="36"/>
+      <c r="BR39" s="36"/>
+      <c r="BS39" s="36"/>
+      <c r="BT39" s="36"/>
     </row>
     <row r="40" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B40" s="22" t="s">
+      <c r="B40" s="38" t="s">
         <v>44</v>
       </c>
       <c r="C40" s="4" t="s">
@@ -6479,56 +7034,56 @@
         <v>60</v>
       </c>
       <c r="AB40" s="19"/>
-      <c r="AC40" s="115"/>
-      <c r="AD40" s="115"/>
-      <c r="AE40" s="115"/>
-      <c r="AF40" s="115"/>
-      <c r="AG40" s="115"/>
-      <c r="AH40" s="115"/>
-      <c r="AI40" s="115"/>
-      <c r="AJ40" s="115"/>
-      <c r="AK40" s="115"/>
-      <c r="AL40" s="115"/>
-      <c r="AM40" s="115"/>
-      <c r="AN40" s="115"/>
-      <c r="AO40" s="115"/>
-      <c r="AP40" s="115"/>
-      <c r="AQ40" s="115"/>
-      <c r="AR40" s="115"/>
-      <c r="AS40" s="115"/>
-      <c r="AT40" s="115"/>
-      <c r="AU40" s="115"/>
-      <c r="AV40" s="115"/>
-      <c r="AW40" s="115"/>
-      <c r="AX40" s="115"/>
-      <c r="AY40" s="115"/>
-      <c r="AZ40" s="115"/>
-      <c r="BA40" s="115"/>
-      <c r="BB40" s="115"/>
-      <c r="BC40" s="115"/>
-      <c r="BD40" s="115"/>
-      <c r="BE40" s="115"/>
-      <c r="BF40" s="115"/>
-      <c r="BG40" s="115"/>
-      <c r="BH40" s="115"/>
-      <c r="BI40" s="115"/>
-      <c r="BJ40" s="115"/>
-      <c r="BK40" s="115"/>
-      <c r="BL40" s="115"/>
-      <c r="BM40" s="115"/>
-      <c r="BN40" s="115"/>
-      <c r="BO40" s="115"/>
-      <c r="BP40" s="115"/>
-      <c r="BQ40" s="115"/>
-      <c r="BR40" s="115"/>
-      <c r="BS40" s="115"/>
-      <c r="BT40" s="115"/>
+      <c r="AC40" s="35"/>
+      <c r="AD40" s="35"/>
+      <c r="AE40" s="35"/>
+      <c r="AF40" s="35"/>
+      <c r="AG40" s="35"/>
+      <c r="AH40" s="35"/>
+      <c r="AI40" s="35"/>
+      <c r="AJ40" s="35"/>
+      <c r="AK40" s="35"/>
+      <c r="AL40" s="35"/>
+      <c r="AM40" s="35"/>
+      <c r="AN40" s="35"/>
+      <c r="AO40" s="35"/>
+      <c r="AP40" s="35"/>
+      <c r="AQ40" s="35"/>
+      <c r="AR40" s="35"/>
+      <c r="AS40" s="35"/>
+      <c r="AT40" s="35"/>
+      <c r="AU40" s="35"/>
+      <c r="AV40" s="35"/>
+      <c r="AW40" s="35"/>
+      <c r="AX40" s="35"/>
+      <c r="AY40" s="35"/>
+      <c r="AZ40" s="35"/>
+      <c r="BA40" s="35"/>
+      <c r="BB40" s="35"/>
+      <c r="BC40" s="35"/>
+      <c r="BD40" s="35"/>
+      <c r="BE40" s="35"/>
+      <c r="BF40" s="35"/>
+      <c r="BG40" s="35"/>
+      <c r="BH40" s="35"/>
+      <c r="BI40" s="35"/>
+      <c r="BJ40" s="35"/>
+      <c r="BK40" s="35"/>
+      <c r="BL40" s="35"/>
+      <c r="BM40" s="35"/>
+      <c r="BN40" s="35"/>
+      <c r="BO40" s="35"/>
+      <c r="BP40" s="35"/>
+      <c r="BQ40" s="35"/>
+      <c r="BR40" s="35"/>
+      <c r="BS40" s="35"/>
+      <c r="BT40" s="35"/>
     </row>
     <row r="41" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="B41" s="24"/>
+      <c r="B41" s="40"/>
       <c r="C41" s="5"/>
       <c r="D41" s="5"/>
       <c r="E41" s="5"/>
@@ -6587,56 +7142,58 @@
       </c>
       <c r="AA41" s="5"/>
       <c r="AB41" s="20"/>
-      <c r="AC41" s="115"/>
-      <c r="AD41" s="115"/>
-      <c r="AE41" s="115"/>
-      <c r="AF41" s="115"/>
-      <c r="AG41" s="115"/>
-      <c r="AH41" s="115"/>
-      <c r="AI41" s="115"/>
-      <c r="AJ41" s="115"/>
-      <c r="AK41" s="115"/>
-      <c r="AL41" s="115"/>
-      <c r="AM41" s="115"/>
-      <c r="AN41" s="115"/>
-      <c r="AO41" s="115"/>
-      <c r="AP41" s="115"/>
-      <c r="AQ41" s="115"/>
-      <c r="AR41" s="115"/>
-      <c r="AS41" s="115"/>
-      <c r="AT41" s="115"/>
-      <c r="AU41" s="115"/>
-      <c r="AV41" s="115"/>
-      <c r="AW41" s="115"/>
-      <c r="AX41" s="115"/>
-      <c r="AY41" s="115"/>
-      <c r="AZ41" s="115"/>
-      <c r="BA41" s="115"/>
-      <c r="BB41" s="115"/>
-      <c r="BC41" s="115"/>
-      <c r="BD41" s="115"/>
-      <c r="BE41" s="115"/>
-      <c r="BF41" s="115"/>
-      <c r="BG41" s="115"/>
-      <c r="BH41" s="115"/>
-      <c r="BI41" s="115"/>
-      <c r="BJ41" s="115"/>
-      <c r="BK41" s="115"/>
-      <c r="BL41" s="115"/>
-      <c r="BM41" s="115"/>
-      <c r="BN41" s="115"/>
-      <c r="BO41" s="115"/>
-      <c r="BP41" s="115"/>
-      <c r="BQ41" s="115"/>
-      <c r="BR41" s="115"/>
-      <c r="BS41" s="115"/>
-      <c r="BT41" s="115"/>
+      <c r="AC41" s="35"/>
+      <c r="AD41" s="35"/>
+      <c r="AE41" s="35"/>
+      <c r="AF41" s="35"/>
+      <c r="AG41" s="35"/>
+      <c r="AH41" s="35"/>
+      <c r="AI41" s="35"/>
+      <c r="AJ41" s="35"/>
+      <c r="AK41" s="35"/>
+      <c r="AL41" s="35"/>
+      <c r="AM41" s="35"/>
+      <c r="AN41" s="35"/>
+      <c r="AO41" s="35"/>
+      <c r="AP41" s="35"/>
+      <c r="AQ41" s="35"/>
+      <c r="AR41" s="35"/>
+      <c r="AS41" s="35"/>
+      <c r="AT41" s="35"/>
+      <c r="AU41" s="35"/>
+      <c r="AV41" s="35"/>
+      <c r="AW41" s="35"/>
+      <c r="AX41" s="35"/>
+      <c r="AY41" s="35"/>
+      <c r="AZ41" s="35"/>
+      <c r="BA41" s="35"/>
+      <c r="BB41" s="35"/>
+      <c r="BC41" s="35"/>
+      <c r="BD41" s="35"/>
+      <c r="BE41" s="35"/>
+      <c r="BF41" s="35"/>
+      <c r="BG41" s="35"/>
+      <c r="BH41" s="35"/>
+      <c r="BI41" s="35"/>
+      <c r="BJ41" s="35"/>
+      <c r="BK41" s="35"/>
+      <c r="BL41" s="35"/>
+      <c r="BM41" s="35"/>
+      <c r="BN41" s="35"/>
+      <c r="BO41" s="35"/>
+      <c r="BP41" s="35"/>
+      <c r="BQ41" s="35"/>
+      <c r="BR41" s="35"/>
+      <c r="BS41" s="122" t="s">
+        <v>191</v>
+      </c>
+      <c r="BT41" s="35"/>
     </row>
     <row r="42" spans="1:72" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B42" s="33"/>
+      <c r="B42" s="49"/>
       <c r="C42" s="6"/>
       <c r="D42" s="6" t="s">
         <v>49</v>
@@ -6666,59 +7223,59 @@
       <c r="Y42" s="6"/>
       <c r="Z42" s="6"/>
       <c r="AA42" s="6"/>
-      <c r="AB42" s="109" t="s">
+      <c r="AB42" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="AC42" s="116"/>
-      <c r="AD42" s="116"/>
-      <c r="AE42" s="116"/>
-      <c r="AF42" s="116"/>
-      <c r="AG42" s="116"/>
-      <c r="AH42" s="116"/>
-      <c r="AI42" s="116"/>
-      <c r="AJ42" s="116"/>
-      <c r="AK42" s="116"/>
-      <c r="AL42" s="116"/>
-      <c r="AM42" s="116"/>
-      <c r="AN42" s="116"/>
-      <c r="AO42" s="116"/>
-      <c r="AP42" s="116"/>
-      <c r="AQ42" s="116"/>
-      <c r="AR42" s="116"/>
-      <c r="AS42" s="116"/>
-      <c r="AT42" s="116"/>
-      <c r="AU42" s="116"/>
-      <c r="AV42" s="116"/>
-      <c r="AW42" s="116"/>
-      <c r="AX42" s="116"/>
-      <c r="AY42" s="116"/>
-      <c r="AZ42" s="116"/>
-      <c r="BA42" s="116"/>
-      <c r="BB42" s="116"/>
-      <c r="BC42" s="116"/>
-      <c r="BD42" s="116"/>
-      <c r="BE42" s="116"/>
-      <c r="BF42" s="116"/>
-      <c r="BG42" s="116"/>
-      <c r="BH42" s="116"/>
-      <c r="BI42" s="116"/>
-      <c r="BJ42" s="116"/>
-      <c r="BK42" s="116"/>
-      <c r="BL42" s="116"/>
-      <c r="BM42" s="116"/>
-      <c r="BN42" s="116"/>
-      <c r="BO42" s="116"/>
-      <c r="BP42" s="116"/>
-      <c r="BQ42" s="116"/>
-      <c r="BR42" s="116"/>
-      <c r="BS42" s="116"/>
-      <c r="BT42" s="116"/>
+      <c r="AC42" s="36"/>
+      <c r="AD42" s="36"/>
+      <c r="AE42" s="36"/>
+      <c r="AF42" s="36"/>
+      <c r="AG42" s="36"/>
+      <c r="AH42" s="36"/>
+      <c r="AI42" s="36"/>
+      <c r="AJ42" s="36"/>
+      <c r="AK42" s="36"/>
+      <c r="AL42" s="36"/>
+      <c r="AM42" s="36"/>
+      <c r="AN42" s="36"/>
+      <c r="AO42" s="36"/>
+      <c r="AP42" s="36"/>
+      <c r="AQ42" s="36"/>
+      <c r="AR42" s="36"/>
+      <c r="AS42" s="36"/>
+      <c r="AT42" s="36"/>
+      <c r="AU42" s="36"/>
+      <c r="AV42" s="36"/>
+      <c r="AW42" s="36"/>
+      <c r="AX42" s="36"/>
+      <c r="AY42" s="36"/>
+      <c r="AZ42" s="36"/>
+      <c r="BA42" s="36"/>
+      <c r="BB42" s="36"/>
+      <c r="BC42" s="36"/>
+      <c r="BD42" s="36"/>
+      <c r="BE42" s="36"/>
+      <c r="BF42" s="36"/>
+      <c r="BG42" s="36"/>
+      <c r="BH42" s="36"/>
+      <c r="BI42" s="36"/>
+      <c r="BJ42" s="36"/>
+      <c r="BK42" s="36"/>
+      <c r="BL42" s="36"/>
+      <c r="BM42" s="36"/>
+      <c r="BN42" s="36"/>
+      <c r="BO42" s="36"/>
+      <c r="BP42" s="36"/>
+      <c r="BQ42" s="36"/>
+      <c r="BR42" s="36"/>
+      <c r="BS42" s="36"/>
+      <c r="BT42" s="36"/>
     </row>
     <row r="43" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A43" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B43" s="22" t="s">
+      <c r="B43" s="38" t="s">
         <v>45</v>
       </c>
       <c r="C43" s="4"/>
@@ -6774,59 +7331,59 @@
       <c r="AA43" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="AB43" s="110" t="s">
+      <c r="AB43" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="AC43" s="115"/>
-      <c r="AD43" s="115"/>
-      <c r="AE43" s="115"/>
-      <c r="AF43" s="115"/>
-      <c r="AG43" s="115"/>
-      <c r="AH43" s="115"/>
-      <c r="AI43" s="115"/>
-      <c r="AJ43" s="115"/>
-      <c r="AK43" s="115"/>
-      <c r="AL43" s="115"/>
-      <c r="AM43" s="115"/>
-      <c r="AN43" s="115"/>
-      <c r="AO43" s="115"/>
-      <c r="AP43" s="115"/>
-      <c r="AQ43" s="115"/>
-      <c r="AR43" s="115"/>
-      <c r="AS43" s="115"/>
-      <c r="AT43" s="115"/>
-      <c r="AU43" s="115"/>
-      <c r="AV43" s="115"/>
-      <c r="AW43" s="115"/>
-      <c r="AX43" s="115"/>
-      <c r="AY43" s="115"/>
-      <c r="AZ43" s="115"/>
-      <c r="BA43" s="115"/>
-      <c r="BB43" s="115"/>
-      <c r="BC43" s="115"/>
-      <c r="BD43" s="115"/>
-      <c r="BE43" s="115"/>
-      <c r="BF43" s="115"/>
-      <c r="BG43" s="115"/>
-      <c r="BH43" s="115"/>
-      <c r="BI43" s="115"/>
-      <c r="BJ43" s="115"/>
-      <c r="BK43" s="115"/>
-      <c r="BL43" s="115"/>
-      <c r="BM43" s="115"/>
-      <c r="BN43" s="115"/>
-      <c r="BO43" s="115"/>
-      <c r="BP43" s="115"/>
-      <c r="BQ43" s="115"/>
-      <c r="BR43" s="115"/>
-      <c r="BS43" s="115"/>
-      <c r="BT43" s="115"/>
+      <c r="AC43" s="35"/>
+      <c r="AD43" s="35"/>
+      <c r="AE43" s="35"/>
+      <c r="AF43" s="35"/>
+      <c r="AG43" s="35"/>
+      <c r="AH43" s="35"/>
+      <c r="AI43" s="35"/>
+      <c r="AJ43" s="35"/>
+      <c r="AK43" s="35"/>
+      <c r="AL43" s="35"/>
+      <c r="AM43" s="35"/>
+      <c r="AN43" s="35"/>
+      <c r="AO43" s="35"/>
+      <c r="AP43" s="35"/>
+      <c r="AQ43" s="35"/>
+      <c r="AR43" s="35"/>
+      <c r="AS43" s="35"/>
+      <c r="AT43" s="35"/>
+      <c r="AU43" s="35"/>
+      <c r="AV43" s="35"/>
+      <c r="AW43" s="35"/>
+      <c r="AX43" s="35"/>
+      <c r="AY43" s="35"/>
+      <c r="AZ43" s="35"/>
+      <c r="BA43" s="35"/>
+      <c r="BB43" s="35"/>
+      <c r="BC43" s="35"/>
+      <c r="BD43" s="35"/>
+      <c r="BE43" s="35"/>
+      <c r="BF43" s="35"/>
+      <c r="BG43" s="35"/>
+      <c r="BH43" s="35"/>
+      <c r="BI43" s="35"/>
+      <c r="BJ43" s="35"/>
+      <c r="BK43" s="35"/>
+      <c r="BL43" s="35"/>
+      <c r="BM43" s="35"/>
+      <c r="BN43" s="35"/>
+      <c r="BO43" s="35"/>
+      <c r="BP43" s="35"/>
+      <c r="BQ43" s="35"/>
+      <c r="BR43" s="35"/>
+      <c r="BS43" s="35"/>
+      <c r="BT43" s="35"/>
     </row>
     <row r="44" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A44" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="B44" s="24"/>
+      <c r="B44" s="40"/>
       <c r="C44" s="5"/>
       <c r="D44" s="5"/>
       <c r="E44" s="5"/>
@@ -6873,56 +7430,56 @@
       </c>
       <c r="AA44" s="5"/>
       <c r="AB44" s="20"/>
-      <c r="AC44" s="115"/>
-      <c r="AD44" s="115"/>
-      <c r="AE44" s="115"/>
-      <c r="AF44" s="115"/>
-      <c r="AG44" s="115"/>
-      <c r="AH44" s="115"/>
-      <c r="AI44" s="115"/>
-      <c r="AJ44" s="115"/>
-      <c r="AK44" s="115"/>
-      <c r="AL44" s="115"/>
-      <c r="AM44" s="115"/>
-      <c r="AN44" s="115"/>
-      <c r="AO44" s="115"/>
-      <c r="AP44" s="115"/>
-      <c r="AQ44" s="115"/>
-      <c r="AR44" s="115"/>
-      <c r="AS44" s="115"/>
-      <c r="AT44" s="115"/>
-      <c r="AU44" s="115"/>
-      <c r="AV44" s="115"/>
-      <c r="AW44" s="115"/>
-      <c r="AX44" s="115"/>
-      <c r="AY44" s="115"/>
-      <c r="AZ44" s="115"/>
-      <c r="BA44" s="115"/>
-      <c r="BB44" s="115"/>
-      <c r="BC44" s="115"/>
-      <c r="BD44" s="115"/>
-      <c r="BE44" s="115"/>
-      <c r="BF44" s="115"/>
-      <c r="BG44" s="115"/>
-      <c r="BH44" s="115"/>
-      <c r="BI44" s="115"/>
-      <c r="BJ44" s="115"/>
-      <c r="BK44" s="115"/>
-      <c r="BL44" s="115"/>
-      <c r="BM44" s="115"/>
-      <c r="BN44" s="115"/>
-      <c r="BO44" s="115"/>
-      <c r="BP44" s="115"/>
-      <c r="BQ44" s="115"/>
-      <c r="BR44" s="115"/>
-      <c r="BS44" s="115"/>
-      <c r="BT44" s="115"/>
+      <c r="AC44" s="35"/>
+      <c r="AD44" s="35"/>
+      <c r="AE44" s="35"/>
+      <c r="AF44" s="35"/>
+      <c r="AG44" s="35"/>
+      <c r="AH44" s="35"/>
+      <c r="AI44" s="35"/>
+      <c r="AJ44" s="35"/>
+      <c r="AK44" s="35"/>
+      <c r="AL44" s="35"/>
+      <c r="AM44" s="35"/>
+      <c r="AN44" s="35"/>
+      <c r="AO44" s="35"/>
+      <c r="AP44" s="35"/>
+      <c r="AQ44" s="35"/>
+      <c r="AR44" s="35"/>
+      <c r="AS44" s="35"/>
+      <c r="AT44" s="35"/>
+      <c r="AU44" s="35"/>
+      <c r="AV44" s="35"/>
+      <c r="AW44" s="35"/>
+      <c r="AX44" s="35"/>
+      <c r="AY44" s="35"/>
+      <c r="AZ44" s="35"/>
+      <c r="BA44" s="35"/>
+      <c r="BB44" s="35"/>
+      <c r="BC44" s="35"/>
+      <c r="BD44" s="35"/>
+      <c r="BE44" s="35"/>
+      <c r="BF44" s="35"/>
+      <c r="BG44" s="35"/>
+      <c r="BH44" s="35"/>
+      <c r="BI44" s="35"/>
+      <c r="BJ44" s="35"/>
+      <c r="BK44" s="35"/>
+      <c r="BL44" s="35"/>
+      <c r="BM44" s="35"/>
+      <c r="BN44" s="35"/>
+      <c r="BO44" s="35"/>
+      <c r="BP44" s="35"/>
+      <c r="BQ44" s="35"/>
+      <c r="BR44" s="35"/>
+      <c r="BS44" s="35"/>
+      <c r="BT44" s="35"/>
     </row>
     <row r="45" spans="1:72" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B45" s="33"/>
+      <c r="B45" s="49"/>
       <c r="C45" s="6"/>
       <c r="D45" s="6" t="s">
         <v>49</v>
@@ -6952,59 +7509,59 @@
       <c r="Y45" s="6"/>
       <c r="Z45" s="6"/>
       <c r="AA45" s="6"/>
-      <c r="AB45" s="109" t="s">
+      <c r="AB45" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="AC45" s="116"/>
-      <c r="AD45" s="116"/>
-      <c r="AE45" s="116"/>
-      <c r="AF45" s="116"/>
-      <c r="AG45" s="116"/>
-      <c r="AH45" s="116"/>
-      <c r="AI45" s="116"/>
-      <c r="AJ45" s="116"/>
-      <c r="AK45" s="116"/>
-      <c r="AL45" s="116"/>
-      <c r="AM45" s="116"/>
-      <c r="AN45" s="116"/>
-      <c r="AO45" s="116"/>
-      <c r="AP45" s="116"/>
-      <c r="AQ45" s="116"/>
-      <c r="AR45" s="116"/>
-      <c r="AS45" s="116"/>
-      <c r="AT45" s="116"/>
-      <c r="AU45" s="116"/>
-      <c r="AV45" s="116"/>
-      <c r="AW45" s="116"/>
-      <c r="AX45" s="116"/>
-      <c r="AY45" s="116"/>
-      <c r="AZ45" s="116"/>
-      <c r="BA45" s="116"/>
-      <c r="BB45" s="116"/>
-      <c r="BC45" s="116"/>
-      <c r="BD45" s="116"/>
-      <c r="BE45" s="116"/>
-      <c r="BF45" s="116"/>
-      <c r="BG45" s="116"/>
-      <c r="BH45" s="116"/>
-      <c r="BI45" s="116"/>
-      <c r="BJ45" s="116"/>
-      <c r="BK45" s="116"/>
-      <c r="BL45" s="116"/>
-      <c r="BM45" s="116"/>
-      <c r="BN45" s="116"/>
-      <c r="BO45" s="116"/>
-      <c r="BP45" s="116"/>
-      <c r="BQ45" s="116"/>
-      <c r="BR45" s="116"/>
-      <c r="BS45" s="116"/>
-      <c r="BT45" s="116"/>
+      <c r="AC45" s="36"/>
+      <c r="AD45" s="36"/>
+      <c r="AE45" s="36"/>
+      <c r="AF45" s="36"/>
+      <c r="AG45" s="36"/>
+      <c r="AH45" s="36"/>
+      <c r="AI45" s="36"/>
+      <c r="AJ45" s="36"/>
+      <c r="AK45" s="36"/>
+      <c r="AL45" s="36"/>
+      <c r="AM45" s="36"/>
+      <c r="AN45" s="36"/>
+      <c r="AO45" s="36"/>
+      <c r="AP45" s="36"/>
+      <c r="AQ45" s="36"/>
+      <c r="AR45" s="36"/>
+      <c r="AS45" s="36"/>
+      <c r="AT45" s="36"/>
+      <c r="AU45" s="36"/>
+      <c r="AV45" s="36"/>
+      <c r="AW45" s="36"/>
+      <c r="AX45" s="36"/>
+      <c r="AY45" s="36"/>
+      <c r="AZ45" s="36"/>
+      <c r="BA45" s="36"/>
+      <c r="BB45" s="36"/>
+      <c r="BC45" s="36"/>
+      <c r="BD45" s="36"/>
+      <c r="BE45" s="36"/>
+      <c r="BF45" s="36"/>
+      <c r="BG45" s="36"/>
+      <c r="BH45" s="36"/>
+      <c r="BI45" s="36"/>
+      <c r="BJ45" s="36"/>
+      <c r="BK45" s="36"/>
+      <c r="BL45" s="36"/>
+      <c r="BM45" s="36"/>
+      <c r="BN45" s="36"/>
+      <c r="BO45" s="36"/>
+      <c r="BP45" s="36"/>
+      <c r="BQ45" s="36"/>
+      <c r="BR45" s="36"/>
+      <c r="BS45" s="36"/>
+      <c r="BT45" s="36"/>
     </row>
     <row r="46" spans="1:72" x14ac:dyDescent="0.3">
-      <c r="A46" s="21" t="s">
+      <c r="A46" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="B46" s="22"/>
+      <c r="B46" s="38"/>
       <c r="C46" s="10">
         <v>45992</v>
       </c>
@@ -7104,789 +7661,898 @@
         <f t="shared" si="4"/>
         <v>46160</v>
       </c>
-      <c r="AB46" s="96">
+      <c r="AB46" s="23">
         <f t="shared" si="4"/>
         <v>46167</v>
       </c>
-      <c r="AC46" s="111">
-        <f>AB46+7</f>
+      <c r="AC46" s="31">
+        <f t="shared" ref="AC46:BT46" si="5">AB46+7</f>
         <v>46174</v>
       </c>
-      <c r="AD46" s="111">
-        <f>AC46+7</f>
+      <c r="AD46" s="31">
+        <f t="shared" si="5"/>
         <v>46181</v>
       </c>
-      <c r="AE46" s="111">
-        <f>AD46+7</f>
+      <c r="AE46" s="31">
+        <f t="shared" si="5"/>
         <v>46188</v>
       </c>
-      <c r="AF46" s="111">
-        <f>AE46+7</f>
+      <c r="AF46" s="31">
+        <f t="shared" si="5"/>
         <v>46195</v>
       </c>
-      <c r="AG46" s="112">
-        <f>AF46+7</f>
+      <c r="AG46" s="32">
+        <f t="shared" si="5"/>
         <v>46202</v>
       </c>
-      <c r="AH46" s="113">
-        <f>AG46+7</f>
+      <c r="AH46" s="33">
+        <f t="shared" si="5"/>
         <v>46209</v>
       </c>
-      <c r="AI46" s="114">
-        <f>AH46+7</f>
+      <c r="AI46" s="34">
+        <f t="shared" si="5"/>
         <v>46216</v>
       </c>
-      <c r="AJ46" s="111">
-        <f>AI46+7</f>
+      <c r="AJ46" s="31">
+        <f t="shared" si="5"/>
         <v>46223</v>
       </c>
-      <c r="AK46" s="112">
-        <f>AJ46+7</f>
+      <c r="AK46" s="32">
+        <f t="shared" si="5"/>
         <v>46230</v>
       </c>
-      <c r="AL46" s="113">
-        <f>AK46+7</f>
+      <c r="AL46" s="33">
+        <f t="shared" si="5"/>
         <v>46237</v>
       </c>
-      <c r="AM46" s="114">
-        <f>AL46+7</f>
+      <c r="AM46" s="34">
+        <f t="shared" si="5"/>
         <v>46244</v>
       </c>
-      <c r="AN46" s="111">
-        <f>AM46+7</f>
+      <c r="AN46" s="31">
+        <f t="shared" si="5"/>
         <v>46251</v>
       </c>
-      <c r="AO46" s="111">
-        <f>AN46+7</f>
+      <c r="AO46" s="31">
+        <f t="shared" si="5"/>
         <v>46258</v>
       </c>
-      <c r="AP46" s="112">
-        <f>AO46+7</f>
+      <c r="AP46" s="32">
+        <f t="shared" si="5"/>
         <v>46265</v>
       </c>
-      <c r="AQ46" s="113">
-        <f>AP46+7</f>
+      <c r="AQ46" s="33">
+        <f t="shared" si="5"/>
         <v>46272</v>
       </c>
-      <c r="AR46" s="114">
-        <f>AQ46+7</f>
+      <c r="AR46" s="34">
+        <f t="shared" si="5"/>
         <v>46279</v>
       </c>
-      <c r="AS46" s="111">
-        <f>AR46+7</f>
+      <c r="AS46" s="31">
+        <f t="shared" si="5"/>
         <v>46286</v>
       </c>
-      <c r="AT46" s="112">
-        <f>AS46+7</f>
+      <c r="AT46" s="32">
+        <f t="shared" si="5"/>
         <v>46293</v>
       </c>
-      <c r="AU46" s="113">
-        <f>AT46+7</f>
+      <c r="AU46" s="33">
+        <f t="shared" si="5"/>
         <v>46300</v>
       </c>
-      <c r="AV46" s="114">
-        <f>AU46+7</f>
+      <c r="AV46" s="34">
+        <f t="shared" si="5"/>
         <v>46307</v>
       </c>
-      <c r="AW46" s="111">
-        <f>AV46+7</f>
+      <c r="AW46" s="31">
+        <f t="shared" si="5"/>
         <v>46314</v>
       </c>
-      <c r="AX46" s="112">
-        <f>AW46+7</f>
+      <c r="AX46" s="32">
+        <f t="shared" si="5"/>
         <v>46321</v>
       </c>
-      <c r="AY46" s="113">
-        <f>AX46+7</f>
+      <c r="AY46" s="33">
+        <f t="shared" si="5"/>
         <v>46328</v>
       </c>
-      <c r="AZ46" s="114">
-        <f>AY46+7</f>
+      <c r="AZ46" s="34">
+        <f t="shared" si="5"/>
         <v>46335</v>
       </c>
-      <c r="BA46" s="111">
-        <f>AZ46+7</f>
+      <c r="BA46" s="31">
+        <f t="shared" si="5"/>
         <v>46342</v>
       </c>
-      <c r="BB46" s="111">
-        <f>BA46+7</f>
+      <c r="BB46" s="31">
+        <f t="shared" si="5"/>
         <v>46349</v>
       </c>
-      <c r="BC46" s="112">
-        <f>BB46+7</f>
+      <c r="BC46" s="32">
+        <f t="shared" si="5"/>
         <v>46356</v>
       </c>
-      <c r="BD46" s="113">
-        <f>BC46+7</f>
+      <c r="BD46" s="33">
+        <f t="shared" si="5"/>
         <v>46363</v>
       </c>
-      <c r="BE46" s="114">
-        <f>BD46+7</f>
+      <c r="BE46" s="34">
+        <f t="shared" si="5"/>
         <v>46370</v>
       </c>
-      <c r="BF46" s="111">
-        <f>BE46+7</f>
+      <c r="BF46" s="31">
+        <f t="shared" si="5"/>
         <v>46377</v>
       </c>
-      <c r="BG46" s="112">
-        <f>BF46+7</f>
+      <c r="BG46" s="32">
+        <f t="shared" si="5"/>
         <v>46384</v>
       </c>
-      <c r="BH46" s="113">
-        <f>BG46+7</f>
+      <c r="BH46" s="33">
+        <f t="shared" si="5"/>
         <v>46391</v>
       </c>
-      <c r="BI46" s="114">
-        <f>BH46+7</f>
+      <c r="BI46" s="34">
+        <f t="shared" si="5"/>
         <v>46398</v>
       </c>
-      <c r="BJ46" s="111">
-        <f>BI46+7</f>
+      <c r="BJ46" s="31">
+        <f t="shared" si="5"/>
         <v>46405</v>
       </c>
-      <c r="BK46" s="112">
-        <f>BJ46+7</f>
+      <c r="BK46" s="32">
+        <f t="shared" si="5"/>
         <v>46412</v>
       </c>
-      <c r="BL46" s="113">
-        <f>BK46+7</f>
+      <c r="BL46" s="33">
+        <f t="shared" si="5"/>
         <v>46419</v>
       </c>
-      <c r="BM46" s="114">
-        <f>BL46+7</f>
+      <c r="BM46" s="34">
+        <f t="shared" si="5"/>
         <v>46426</v>
       </c>
-      <c r="BN46" s="111">
-        <f>BM46+7</f>
+      <c r="BN46" s="31">
+        <f t="shared" si="5"/>
         <v>46433</v>
       </c>
-      <c r="BO46" s="112">
-        <f>BN46+7</f>
+      <c r="BO46" s="32">
+        <f t="shared" si="5"/>
         <v>46440</v>
       </c>
-      <c r="BP46" s="113">
-        <f>BO46+7</f>
+      <c r="BP46" s="33">
+        <f t="shared" si="5"/>
         <v>46447</v>
       </c>
-      <c r="BQ46" s="114">
-        <f>BP46+7</f>
+      <c r="BQ46" s="34">
+        <f t="shared" si="5"/>
         <v>46454</v>
       </c>
-      <c r="BR46" s="111">
-        <f>BQ46+7</f>
+      <c r="BR46" s="31">
+        <f t="shared" si="5"/>
         <v>46461</v>
       </c>
-      <c r="BS46" s="111">
-        <f>BR46+7</f>
+      <c r="BS46" s="31">
+        <f t="shared" si="5"/>
         <v>46468</v>
       </c>
-      <c r="BT46" s="111">
-        <f>BS46+7</f>
+      <c r="BT46" s="31">
+        <f t="shared" si="5"/>
         <v>46475</v>
       </c>
     </row>
     <row r="47" spans="1:72" x14ac:dyDescent="0.3">
-      <c r="A47" s="23"/>
-      <c r="B47" s="24"/>
+      <c r="A47" s="39"/>
+      <c r="B47" s="40"/>
       <c r="C47" s="13">
         <f>C46+6</f>
         <v>45998</v>
       </c>
       <c r="D47" s="13">
-        <f t="shared" ref="D47:AA47" si="5">D46+6</f>
+        <f t="shared" ref="D47:AA47" si="6">D46+6</f>
         <v>46005</v>
       </c>
       <c r="E47" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>46012</v>
       </c>
       <c r="F47" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>46019</v>
       </c>
       <c r="G47" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>46026</v>
       </c>
       <c r="H47" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>46033</v>
       </c>
       <c r="I47" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>46040</v>
       </c>
       <c r="J47" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>46047</v>
       </c>
       <c r="K47" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>46054</v>
       </c>
       <c r="L47" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>46061</v>
       </c>
       <c r="M47" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>46068</v>
       </c>
       <c r="N47" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>46075</v>
       </c>
       <c r="O47" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>46082</v>
       </c>
       <c r="P47" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>46089</v>
       </c>
       <c r="Q47" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>46096</v>
       </c>
       <c r="R47" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>46103</v>
       </c>
       <c r="S47" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>46110</v>
       </c>
       <c r="T47" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>46117</v>
       </c>
       <c r="U47" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>46124</v>
       </c>
       <c r="V47" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>46131</v>
       </c>
       <c r="W47" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>46138</v>
       </c>
       <c r="X47" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>46145</v>
       </c>
       <c r="Y47" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>46152</v>
       </c>
       <c r="Z47" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>46159</v>
       </c>
       <c r="AA47" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>46166</v>
       </c>
-      <c r="AB47" s="97">
-        <f>AB46+6</f>
+      <c r="AB47" s="24">
+        <f t="shared" ref="AB47:BT47" si="7">AB46+6</f>
         <v>46173</v>
       </c>
-      <c r="AC47" s="105">
-        <f>AC46+6</f>
+      <c r="AC47" s="25">
+        <f t="shared" si="7"/>
         <v>46180</v>
       </c>
-      <c r="AD47" s="105">
-        <f>AD46+6</f>
+      <c r="AD47" s="25">
+        <f t="shared" si="7"/>
         <v>46187</v>
       </c>
-      <c r="AE47" s="105">
-        <f>AE46+6</f>
+      <c r="AE47" s="25">
+        <f t="shared" si="7"/>
         <v>46194</v>
       </c>
-      <c r="AF47" s="105">
-        <f>AF46+6</f>
+      <c r="AF47" s="25">
+        <f t="shared" si="7"/>
         <v>46201</v>
       </c>
-      <c r="AG47" s="106">
-        <f>AG46+6</f>
+      <c r="AG47" s="26">
+        <f t="shared" si="7"/>
         <v>46208</v>
       </c>
-      <c r="AH47" s="107">
-        <f>AH46+6</f>
+      <c r="AH47" s="27">
+        <f t="shared" si="7"/>
         <v>46215</v>
       </c>
-      <c r="AI47" s="108">
-        <f>AI46+6</f>
+      <c r="AI47" s="28">
+        <f t="shared" si="7"/>
         <v>46222</v>
       </c>
-      <c r="AJ47" s="105">
-        <f>AJ46+6</f>
+      <c r="AJ47" s="25">
+        <f t="shared" si="7"/>
         <v>46229</v>
       </c>
-      <c r="AK47" s="106">
-        <f>AK46+6</f>
+      <c r="AK47" s="26">
+        <f t="shared" si="7"/>
         <v>46236</v>
       </c>
-      <c r="AL47" s="107">
-        <f>AL46+6</f>
+      <c r="AL47" s="27">
+        <f t="shared" si="7"/>
         <v>46243</v>
       </c>
-      <c r="AM47" s="108">
-        <f>AM46+6</f>
+      <c r="AM47" s="28">
+        <f t="shared" si="7"/>
         <v>46250</v>
       </c>
-      <c r="AN47" s="105">
-        <f>AN46+6</f>
+      <c r="AN47" s="25">
+        <f t="shared" si="7"/>
         <v>46257</v>
       </c>
-      <c r="AO47" s="105">
-        <f>AO46+6</f>
+      <c r="AO47" s="25">
+        <f t="shared" si="7"/>
         <v>46264</v>
       </c>
-      <c r="AP47" s="106">
-        <f>AP46+6</f>
+      <c r="AP47" s="26">
+        <f t="shared" si="7"/>
         <v>46271</v>
       </c>
-      <c r="AQ47" s="107">
-        <f>AQ46+6</f>
+      <c r="AQ47" s="27">
+        <f t="shared" si="7"/>
         <v>46278</v>
       </c>
-      <c r="AR47" s="108">
-        <f>AR46+6</f>
+      <c r="AR47" s="28">
+        <f t="shared" si="7"/>
         <v>46285</v>
       </c>
-      <c r="AS47" s="105">
-        <f>AS46+6</f>
+      <c r="AS47" s="25">
+        <f t="shared" si="7"/>
         <v>46292</v>
       </c>
-      <c r="AT47" s="106">
-        <f>AT46+6</f>
+      <c r="AT47" s="26">
+        <f t="shared" si="7"/>
         <v>46299</v>
       </c>
-      <c r="AU47" s="107">
-        <f>AU46+6</f>
+      <c r="AU47" s="27">
+        <f t="shared" si="7"/>
         <v>46306</v>
       </c>
-      <c r="AV47" s="108">
-        <f>AV46+6</f>
+      <c r="AV47" s="28">
+        <f t="shared" si="7"/>
         <v>46313</v>
       </c>
-      <c r="AW47" s="105">
-        <f>AW46+6</f>
+      <c r="AW47" s="25">
+        <f t="shared" si="7"/>
         <v>46320</v>
       </c>
-      <c r="AX47" s="106">
-        <f>AX46+6</f>
+      <c r="AX47" s="26">
+        <f t="shared" si="7"/>
         <v>46327</v>
       </c>
-      <c r="AY47" s="107">
-        <f>AY46+6</f>
+      <c r="AY47" s="27">
+        <f t="shared" si="7"/>
         <v>46334</v>
       </c>
-      <c r="AZ47" s="108">
-        <f>AZ46+6</f>
+      <c r="AZ47" s="28">
+        <f t="shared" si="7"/>
         <v>46341</v>
       </c>
-      <c r="BA47" s="105">
-        <f>BA46+6</f>
+      <c r="BA47" s="25">
+        <f t="shared" si="7"/>
         <v>46348</v>
       </c>
-      <c r="BB47" s="105">
-        <f>BB46+6</f>
+      <c r="BB47" s="25">
+        <f t="shared" si="7"/>
         <v>46355</v>
       </c>
-      <c r="BC47" s="106">
-        <f>BC46+6</f>
+      <c r="BC47" s="26">
+        <f t="shared" si="7"/>
         <v>46362</v>
       </c>
-      <c r="BD47" s="107">
-        <f>BD46+6</f>
+      <c r="BD47" s="27">
+        <f t="shared" si="7"/>
         <v>46369</v>
       </c>
-      <c r="BE47" s="108">
-        <f>BE46+6</f>
+      <c r="BE47" s="28">
+        <f t="shared" si="7"/>
         <v>46376</v>
       </c>
-      <c r="BF47" s="105">
-        <f>BF46+6</f>
+      <c r="BF47" s="25">
+        <f t="shared" si="7"/>
         <v>46383</v>
       </c>
-      <c r="BG47" s="106">
-        <f>BG46+6</f>
+      <c r="BG47" s="26">
+        <f t="shared" si="7"/>
         <v>46390</v>
       </c>
-      <c r="BH47" s="107">
-        <f>BH46+6</f>
+      <c r="BH47" s="27">
+        <f t="shared" si="7"/>
         <v>46397</v>
       </c>
-      <c r="BI47" s="108">
-        <f>BI46+6</f>
+      <c r="BI47" s="28">
+        <f t="shared" si="7"/>
         <v>46404</v>
       </c>
-      <c r="BJ47" s="105">
-        <f>BJ46+6</f>
+      <c r="BJ47" s="25">
+        <f t="shared" si="7"/>
         <v>46411</v>
       </c>
-      <c r="BK47" s="106">
-        <f>BK46+6</f>
+      <c r="BK47" s="26">
+        <f t="shared" si="7"/>
         <v>46418</v>
       </c>
-      <c r="BL47" s="107">
-        <f>BL46+6</f>
+      <c r="BL47" s="27">
+        <f t="shared" si="7"/>
         <v>46425</v>
       </c>
-      <c r="BM47" s="108">
-        <f>BM46+6</f>
+      <c r="BM47" s="28">
+        <f t="shared" si="7"/>
         <v>46432</v>
       </c>
-      <c r="BN47" s="105">
-        <f>BN46+6</f>
+      <c r="BN47" s="25">
+        <f t="shared" si="7"/>
         <v>46439</v>
       </c>
-      <c r="BO47" s="106">
-        <f>BO46+6</f>
+      <c r="BO47" s="26">
+        <f t="shared" si="7"/>
         <v>46446</v>
       </c>
-      <c r="BP47" s="107">
-        <f>BP46+6</f>
+      <c r="BP47" s="27">
+        <f t="shared" si="7"/>
         <v>46453</v>
       </c>
-      <c r="BQ47" s="108">
-        <f>BQ46+6</f>
+      <c r="BQ47" s="28">
+        <f t="shared" si="7"/>
         <v>46460</v>
       </c>
-      <c r="BR47" s="105">
-        <f>BR46+6</f>
+      <c r="BR47" s="25">
+        <f t="shared" si="7"/>
         <v>46467</v>
       </c>
-      <c r="BS47" s="105">
-        <f>BS46+6</f>
+      <c r="BS47" s="25">
+        <f t="shared" si="7"/>
         <v>46474</v>
       </c>
-      <c r="BT47" s="105">
-        <f>BT46+6</f>
+      <c r="BT47" s="25">
+        <f t="shared" si="7"/>
         <v>46481</v>
       </c>
     </row>
     <row r="48" spans="1:72" x14ac:dyDescent="0.3">
-      <c r="A48" s="46" t="s">
+      <c r="A48" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="B48" s="46"/>
-      <c r="C48" s="90">
-        <f>_xlfn.ISOWEEKNUM(C46)</f>
+      <c r="B48" s="62"/>
+      <c r="C48" s="112">
+        <f t="shared" ref="C48:AH48" si="8">_xlfn.ISOWEEKNUM(C46)</f>
         <v>49</v>
       </c>
-      <c r="D48" s="90">
-        <f>_xlfn.ISOWEEKNUM(D46)</f>
+      <c r="D48" s="112">
+        <f t="shared" si="8"/>
         <v>50</v>
       </c>
-      <c r="E48" s="90">
-        <f>_xlfn.ISOWEEKNUM(E46)</f>
+      <c r="E48" s="112">
+        <f t="shared" si="8"/>
         <v>51</v>
       </c>
-      <c r="F48" s="90">
-        <f>_xlfn.ISOWEEKNUM(F46)</f>
+      <c r="F48" s="112">
+        <f t="shared" si="8"/>
         <v>52</v>
       </c>
-      <c r="G48" s="90">
-        <f>_xlfn.ISOWEEKNUM(G46)</f>
+      <c r="G48" s="112">
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="H48" s="90">
-        <f>_xlfn.ISOWEEKNUM(H46)</f>
+      <c r="H48" s="112">
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
-      <c r="I48" s="90">
-        <f>_xlfn.ISOWEEKNUM(I46)</f>
+      <c r="I48" s="112">
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="J48" s="90">
-        <f>_xlfn.ISOWEEKNUM(J46)</f>
+      <c r="J48" s="112">
+        <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="K48" s="90">
-        <f>_xlfn.ISOWEEKNUM(K46)</f>
+      <c r="K48" s="112">
+        <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="L48" s="90">
-        <f>_xlfn.ISOWEEKNUM(L46)</f>
+      <c r="L48" s="112">
+        <f t="shared" si="8"/>
         <v>6</v>
       </c>
-      <c r="M48" s="90">
-        <f>_xlfn.ISOWEEKNUM(M46)</f>
+      <c r="M48" s="112">
+        <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="N48" s="90">
-        <f>_xlfn.ISOWEEKNUM(N46)</f>
+      <c r="N48" s="112">
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
-      <c r="O48" s="90">
-        <f>_xlfn.ISOWEEKNUM(O46)</f>
+      <c r="O48" s="112">
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
-      <c r="P48" s="90">
-        <f>_xlfn.ISOWEEKNUM(P46)</f>
+      <c r="P48" s="112">
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
-      <c r="Q48" s="90">
-        <f>_xlfn.ISOWEEKNUM(Q46)</f>
+      <c r="Q48" s="112">
+        <f t="shared" si="8"/>
         <v>11</v>
       </c>
-      <c r="R48" s="90">
-        <f>_xlfn.ISOWEEKNUM(R46)</f>
+      <c r="R48" s="112">
+        <f t="shared" si="8"/>
         <v>12</v>
       </c>
-      <c r="S48" s="90">
-        <f>_xlfn.ISOWEEKNUM(S46)</f>
+      <c r="S48" s="112">
+        <f t="shared" si="8"/>
         <v>13</v>
       </c>
-      <c r="T48" s="90">
-        <f>_xlfn.ISOWEEKNUM(T46)</f>
+      <c r="T48" s="112">
+        <f t="shared" si="8"/>
         <v>14</v>
       </c>
-      <c r="U48" s="90">
-        <f>_xlfn.ISOWEEKNUM(U46)</f>
+      <c r="U48" s="112">
+        <f t="shared" si="8"/>
         <v>15</v>
       </c>
-      <c r="V48" s="90">
-        <f>_xlfn.ISOWEEKNUM(V46)</f>
+      <c r="V48" s="112">
+        <f t="shared" si="8"/>
         <v>16</v>
       </c>
-      <c r="W48" s="90">
-        <f>_xlfn.ISOWEEKNUM(W46)</f>
+      <c r="W48" s="112">
+        <f t="shared" si="8"/>
         <v>17</v>
       </c>
-      <c r="X48" s="90">
-        <f>_xlfn.ISOWEEKNUM(X46)</f>
+      <c r="X48" s="112">
+        <f t="shared" si="8"/>
         <v>18</v>
       </c>
-      <c r="Y48" s="90">
-        <f>_xlfn.ISOWEEKNUM(Y46)</f>
+      <c r="Y48" s="112">
+        <f t="shared" si="8"/>
         <v>19</v>
       </c>
-      <c r="Z48" s="90">
-        <f>_xlfn.ISOWEEKNUM(Z46)</f>
+      <c r="Z48" s="112">
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="AA48" s="70">
-        <f>_xlfn.ISOWEEKNUM(AA46)</f>
+      <c r="AA48" s="89">
+        <f t="shared" si="8"/>
         <v>21</v>
       </c>
-      <c r="AB48" s="25">
-        <f>_xlfn.ISOWEEKNUM(AB46)</f>
+      <c r="AB48" s="41">
+        <f t="shared" si="8"/>
         <v>22</v>
       </c>
-      <c r="AC48" s="98">
-        <f>_xlfn.ISOWEEKNUM(AC46)</f>
+      <c r="AC48" s="187">
+        <f t="shared" si="8"/>
         <v>23</v>
       </c>
-      <c r="AD48" s="98">
-        <f>_xlfn.ISOWEEKNUM(AD46)</f>
+      <c r="AD48" s="187">
+        <f t="shared" ref="AD48:AF48" si="9">_xlfn.ISOWEEKNUM(AD46)</f>
         <v>24</v>
       </c>
-      <c r="AE48" s="98">
-        <f>_xlfn.ISOWEEKNUM(AE46)</f>
+      <c r="AE48" s="187">
+        <f t="shared" si="9"/>
         <v>25</v>
       </c>
-      <c r="AF48" s="98">
-        <f>_xlfn.ISOWEEKNUM(AF46)</f>
+      <c r="AF48" s="187">
+        <f t="shared" si="9"/>
         <v>26</v>
       </c>
-      <c r="AG48" s="98">
-        <f>_xlfn.ISOWEEKNUM(AG46)</f>
+      <c r="AG48" s="187">
+        <f t="shared" ref="AG48:AM48" si="10">_xlfn.ISOWEEKNUM(AG46)</f>
         <v>27</v>
       </c>
-      <c r="AH48" s="99">
-        <f>_xlfn.ISOWEEKNUM(AH46)</f>
+      <c r="AH48" s="187">
+        <f t="shared" si="10"/>
         <v>28</v>
       </c>
-      <c r="AI48" s="98">
-        <f>_xlfn.ISOWEEKNUM(AI46)</f>
+      <c r="AI48" s="187">
+        <f t="shared" si="10"/>
         <v>29</v>
       </c>
-      <c r="AJ48" s="98">
-        <f>_xlfn.ISOWEEKNUM(AJ46)</f>
+      <c r="AJ48" s="187">
+        <f t="shared" si="10"/>
         <v>30</v>
       </c>
-      <c r="AK48" s="98">
-        <f>_xlfn.ISOWEEKNUM(AK46)</f>
+      <c r="AK48" s="187">
+        <f t="shared" si="10"/>
         <v>31</v>
       </c>
-      <c r="AL48" s="99">
-        <f>_xlfn.ISOWEEKNUM(AL46)</f>
+      <c r="AL48" s="187">
+        <f t="shared" si="10"/>
         <v>32</v>
       </c>
-      <c r="AM48" s="98">
-        <f>_xlfn.ISOWEEKNUM(AM46)</f>
+      <c r="AM48" s="187">
+        <f t="shared" si="10"/>
         <v>33</v>
       </c>
-      <c r="AN48" s="98">
-        <f>_xlfn.ISOWEEKNUM(AN46)</f>
+      <c r="AN48" s="187">
+        <f t="shared" ref="AN48:BS48" si="11">_xlfn.ISOWEEKNUM(AN46)</f>
         <v>34</v>
       </c>
-      <c r="AO48" s="98">
-        <f>_xlfn.ISOWEEKNUM(AO46)</f>
+      <c r="AO48" s="187">
+        <f t="shared" si="11"/>
         <v>35</v>
       </c>
-      <c r="AP48" s="98">
-        <f>_xlfn.ISOWEEKNUM(AP46)</f>
+      <c r="AP48" s="187">
+        <f t="shared" si="11"/>
         <v>36</v>
       </c>
-      <c r="AQ48" s="99">
-        <f>_xlfn.ISOWEEKNUM(AQ46)</f>
+      <c r="AQ48" s="187">
+        <f t="shared" si="11"/>
         <v>37</v>
       </c>
-      <c r="AR48" s="98">
-        <f>_xlfn.ISOWEEKNUM(AR46)</f>
+      <c r="AR48" s="187">
+        <f t="shared" si="11"/>
         <v>38</v>
       </c>
-      <c r="AS48" s="98">
-        <f>_xlfn.ISOWEEKNUM(AS46)</f>
+      <c r="AS48" s="187">
+        <f t="shared" si="11"/>
         <v>39</v>
       </c>
-      <c r="AT48" s="98">
-        <f>_xlfn.ISOWEEKNUM(AT46)</f>
+      <c r="AT48" s="187">
+        <f t="shared" si="11"/>
         <v>40</v>
       </c>
-      <c r="AU48" s="99">
-        <f>_xlfn.ISOWEEKNUM(AU46)</f>
+      <c r="AU48" s="187">
+        <f t="shared" si="11"/>
         <v>41</v>
       </c>
-      <c r="AV48" s="98">
-        <f>_xlfn.ISOWEEKNUM(AV46)</f>
+      <c r="AV48" s="187">
+        <f t="shared" si="11"/>
         <v>42</v>
       </c>
-      <c r="AW48" s="98">
-        <f>_xlfn.ISOWEEKNUM(AW46)</f>
+      <c r="AW48" s="187">
+        <f t="shared" si="11"/>
         <v>43</v>
       </c>
-      <c r="AX48" s="98">
-        <f>_xlfn.ISOWEEKNUM(AX46)</f>
+      <c r="AX48" s="187">
+        <f t="shared" si="11"/>
         <v>44</v>
       </c>
-      <c r="AY48" s="99">
-        <f>_xlfn.ISOWEEKNUM(AY46)</f>
+      <c r="AY48" s="187">
+        <f t="shared" si="11"/>
         <v>45</v>
       </c>
-      <c r="AZ48" s="98">
-        <f>_xlfn.ISOWEEKNUM(AZ46)</f>
+      <c r="AZ48" s="187">
+        <f t="shared" si="11"/>
         <v>46</v>
       </c>
-      <c r="BA48" s="98">
-        <f>_xlfn.ISOWEEKNUM(BA46)</f>
+      <c r="BA48" s="187">
+        <f t="shared" si="11"/>
         <v>47</v>
       </c>
-      <c r="BB48" s="98">
-        <f>_xlfn.ISOWEEKNUM(BB46)</f>
+      <c r="BB48" s="187">
+        <f t="shared" si="11"/>
         <v>48</v>
       </c>
-      <c r="BC48" s="98">
-        <f>_xlfn.ISOWEEKNUM(BC46)</f>
+      <c r="BC48" s="187">
+        <f t="shared" si="11"/>
         <v>49</v>
       </c>
-      <c r="BD48" s="99">
-        <f>_xlfn.ISOWEEKNUM(BD46)</f>
+      <c r="BD48" s="187">
+        <f t="shared" si="11"/>
         <v>50</v>
       </c>
-      <c r="BE48" s="98">
-        <f>_xlfn.ISOWEEKNUM(BE46)</f>
+      <c r="BE48" s="187">
+        <f t="shared" si="11"/>
         <v>51</v>
       </c>
-      <c r="BF48" s="98">
-        <f>_xlfn.ISOWEEKNUM(BF46)</f>
+      <c r="BF48" s="187">
+        <f t="shared" si="11"/>
         <v>52</v>
       </c>
-      <c r="BG48" s="98">
-        <f>_xlfn.ISOWEEKNUM(BG46)</f>
+      <c r="BG48" s="187">
+        <f t="shared" si="11"/>
         <v>53</v>
       </c>
-      <c r="BH48" s="99">
-        <f>_xlfn.ISOWEEKNUM(BH46)</f>
+      <c r="BH48" s="187">
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="BI48" s="98">
-        <f>_xlfn.ISOWEEKNUM(BI46)</f>
+      <c r="BI48" s="187">
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
-      <c r="BJ48" s="98">
-        <f>_xlfn.ISOWEEKNUM(BJ46)</f>
+      <c r="BJ48" s="187">
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
-      <c r="BK48" s="98">
-        <f>_xlfn.ISOWEEKNUM(BK46)</f>
+      <c r="BK48" s="187">
+        <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="BL48" s="99">
-        <f>_xlfn.ISOWEEKNUM(BL46)</f>
+      <c r="BL48" s="187">
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
-      <c r="BM48" s="98">
-        <f>_xlfn.ISOWEEKNUM(BM46)</f>
+      <c r="BM48" s="187">
+        <f t="shared" si="11"/>
         <v>6</v>
       </c>
-      <c r="BN48" s="98">
-        <f>_xlfn.ISOWEEKNUM(BN46)</f>
+      <c r="BN48" s="187">
+        <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="BO48" s="98">
-        <f>_xlfn.ISOWEEKNUM(BO46)</f>
+      <c r="BO48" s="187">
+        <f t="shared" si="11"/>
         <v>8</v>
       </c>
-      <c r="BP48" s="99">
-        <f>_xlfn.ISOWEEKNUM(BP46)</f>
+      <c r="BP48" s="187">
+        <f t="shared" si="11"/>
         <v>9</v>
       </c>
-      <c r="BQ48" s="98">
-        <f>_xlfn.ISOWEEKNUM(BQ46)</f>
+      <c r="BQ48" s="187">
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
-      <c r="BR48" s="98">
-        <f>_xlfn.ISOWEEKNUM(BR46)</f>
+      <c r="BR48" s="187">
+        <f t="shared" si="11"/>
         <v>11</v>
       </c>
-      <c r="BS48" s="98">
-        <f>_xlfn.ISOWEEKNUM(BS46)</f>
+      <c r="BS48" s="187">
+        <f t="shared" si="11"/>
         <v>12</v>
       </c>
-      <c r="BT48" s="98">
-        <f>_xlfn.ISOWEEKNUM(BT46)</f>
+      <c r="BT48" s="187">
+        <f t="shared" ref="BT48" si="12">_xlfn.ISOWEEKNUM(BT46)</f>
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A49" s="46"/>
-      <c r="B49" s="46"/>
-      <c r="C49" s="91"/>
-      <c r="D49" s="91"/>
-      <c r="E49" s="91"/>
-      <c r="F49" s="91"/>
-      <c r="G49" s="91"/>
-      <c r="H49" s="91"/>
-      <c r="I49" s="91"/>
-      <c r="J49" s="91"/>
-      <c r="K49" s="91"/>
-      <c r="L49" s="91"/>
-      <c r="M49" s="91"/>
-      <c r="N49" s="91"/>
-      <c r="O49" s="91"/>
-      <c r="P49" s="91"/>
-      <c r="Q49" s="91"/>
-      <c r="R49" s="91"/>
-      <c r="S49" s="91"/>
-      <c r="T49" s="91"/>
-      <c r="U49" s="91"/>
-      <c r="V49" s="91"/>
-      <c r="W49" s="91"/>
-      <c r="X49" s="91"/>
-      <c r="Y49" s="91"/>
-      <c r="Z49" s="91"/>
-      <c r="AA49" s="92"/>
-      <c r="AB49" s="92"/>
+    <row r="49" spans="1:72" x14ac:dyDescent="0.3">
+      <c r="A49" s="62"/>
+      <c r="B49" s="62"/>
+      <c r="C49" s="113"/>
+      <c r="D49" s="113"/>
+      <c r="E49" s="113"/>
+      <c r="F49" s="113"/>
+      <c r="G49" s="113"/>
+      <c r="H49" s="113"/>
+      <c r="I49" s="113"/>
+      <c r="J49" s="113"/>
+      <c r="K49" s="113"/>
+      <c r="L49" s="113"/>
+      <c r="M49" s="113"/>
+      <c r="N49" s="113"/>
+      <c r="O49" s="113"/>
+      <c r="P49" s="113"/>
+      <c r="Q49" s="113"/>
+      <c r="R49" s="113"/>
+      <c r="S49" s="113"/>
+      <c r="T49" s="113"/>
+      <c r="U49" s="113"/>
+      <c r="V49" s="113"/>
+      <c r="W49" s="113"/>
+      <c r="X49" s="113"/>
+      <c r="Y49" s="113"/>
+      <c r="Z49" s="113"/>
+      <c r="AA49" s="114"/>
+      <c r="AB49" s="114"/>
+      <c r="AC49" s="188"/>
+      <c r="AD49" s="188"/>
+      <c r="AE49" s="188"/>
+      <c r="AF49" s="188"/>
+      <c r="AG49" s="188"/>
+      <c r="AH49" s="188"/>
+      <c r="AI49" s="188"/>
+      <c r="AJ49" s="188"/>
+      <c r="AK49" s="188"/>
+      <c r="AL49" s="188"/>
+      <c r="AM49" s="188"/>
+      <c r="AN49" s="188"/>
+      <c r="AO49" s="188"/>
+      <c r="AP49" s="188"/>
+      <c r="AQ49" s="188"/>
+      <c r="AR49" s="188"/>
+      <c r="AS49" s="188"/>
+      <c r="AT49" s="188"/>
+      <c r="AU49" s="188"/>
+      <c r="AV49" s="188"/>
+      <c r="AW49" s="188"/>
+      <c r="AX49" s="188"/>
+      <c r="AY49" s="188"/>
+      <c r="AZ49" s="188"/>
+      <c r="BA49" s="188"/>
+      <c r="BB49" s="188"/>
+      <c r="BC49" s="188"/>
+      <c r="BD49" s="188"/>
+      <c r="BE49" s="188"/>
+      <c r="BF49" s="188"/>
+      <c r="BG49" s="188"/>
+      <c r="BH49" s="188"/>
+      <c r="BI49" s="188"/>
+      <c r="BJ49" s="188"/>
+      <c r="BK49" s="188"/>
+      <c r="BL49" s="188"/>
+      <c r="BM49" s="188"/>
+      <c r="BN49" s="188"/>
+      <c r="BO49" s="188"/>
+      <c r="BP49" s="188"/>
+      <c r="BQ49" s="188"/>
+      <c r="BR49" s="188"/>
+      <c r="BS49" s="188"/>
+      <c r="BT49" s="188"/>
     </row>
   </sheetData>
-  <mergeCells count="642">
+  <mergeCells count="578">
+    <mergeCell ref="BP48:BP49"/>
+    <mergeCell ref="BQ48:BQ49"/>
+    <mergeCell ref="BR48:BR49"/>
+    <mergeCell ref="BS48:BS49"/>
+    <mergeCell ref="BT48:BT49"/>
+    <mergeCell ref="AE11:AM12"/>
+    <mergeCell ref="AN11:AS12"/>
+    <mergeCell ref="AT11:AZ12"/>
+    <mergeCell ref="BA11:BG12"/>
+    <mergeCell ref="BH11:BM12"/>
+    <mergeCell ref="BN11:BP12"/>
+    <mergeCell ref="BG48:BG49"/>
+    <mergeCell ref="BH48:BH49"/>
+    <mergeCell ref="BI48:BI49"/>
+    <mergeCell ref="BJ48:BJ49"/>
+    <mergeCell ref="BK48:BK49"/>
+    <mergeCell ref="BL48:BL49"/>
+    <mergeCell ref="BM48:BM49"/>
+    <mergeCell ref="BN48:BN49"/>
+    <mergeCell ref="BO48:BO49"/>
+    <mergeCell ref="AX48:AX49"/>
+    <mergeCell ref="AY48:AY49"/>
+    <mergeCell ref="AZ48:AZ49"/>
+    <mergeCell ref="BA48:BA49"/>
+    <mergeCell ref="BB48:BB49"/>
+    <mergeCell ref="BC48:BC49"/>
+    <mergeCell ref="BD48:BD49"/>
+    <mergeCell ref="BE48:BE49"/>
+    <mergeCell ref="BF48:BF49"/>
+    <mergeCell ref="BQ11:BR12"/>
+    <mergeCell ref="AC48:AC49"/>
+    <mergeCell ref="AD48:AD49"/>
+    <mergeCell ref="AE48:AE49"/>
+    <mergeCell ref="AF48:AF49"/>
+    <mergeCell ref="AG48:AG49"/>
+    <mergeCell ref="AH48:AH49"/>
+    <mergeCell ref="AI48:AI49"/>
+    <mergeCell ref="AJ48:AJ49"/>
+    <mergeCell ref="AK48:AK49"/>
+    <mergeCell ref="AL48:AL49"/>
+    <mergeCell ref="AM48:AM49"/>
+    <mergeCell ref="AN48:AN49"/>
+    <mergeCell ref="AO48:AO49"/>
+    <mergeCell ref="AP48:AP49"/>
+    <mergeCell ref="AQ48:AQ49"/>
+    <mergeCell ref="AR48:AR49"/>
+    <mergeCell ref="AS48:AS49"/>
+    <mergeCell ref="AT48:AT49"/>
+    <mergeCell ref="AU48:AU49"/>
+    <mergeCell ref="AV48:AV49"/>
+    <mergeCell ref="AW48:AW49"/>
+    <mergeCell ref="AC3:AD4"/>
+    <mergeCell ref="AC7:AD8"/>
+    <mergeCell ref="BS5:BS6"/>
+    <mergeCell ref="BQ5:BR6"/>
+    <mergeCell ref="BN5:BP6"/>
+    <mergeCell ref="BN3:BS4"/>
+    <mergeCell ref="BD3:BM4"/>
+    <mergeCell ref="AE3:BC4"/>
+    <mergeCell ref="AC5:AD6"/>
+    <mergeCell ref="AE5:AJ6"/>
+    <mergeCell ref="AK5:AP6"/>
+    <mergeCell ref="AQ5:AV6"/>
+    <mergeCell ref="AW5:BC6"/>
+    <mergeCell ref="BD5:BM6"/>
     <mergeCell ref="BL23:BL24"/>
     <mergeCell ref="BM23:BM24"/>
     <mergeCell ref="BN23:BN24"/>
@@ -8135,12 +8801,6 @@
     <mergeCell ref="AY13:AY14"/>
     <mergeCell ref="AZ13:AZ14"/>
     <mergeCell ref="BA13:BA14"/>
-    <mergeCell ref="BM11:BM12"/>
-    <mergeCell ref="BN11:BN12"/>
-    <mergeCell ref="BO11:BO12"/>
-    <mergeCell ref="BP11:BP12"/>
-    <mergeCell ref="BQ11:BQ12"/>
-    <mergeCell ref="BR11:BR12"/>
     <mergeCell ref="BS11:BS12"/>
     <mergeCell ref="BT11:BT12"/>
     <mergeCell ref="AC13:AC14"/>
@@ -8159,42 +8819,7 @@
     <mergeCell ref="AP13:AP14"/>
     <mergeCell ref="AQ13:AQ14"/>
     <mergeCell ref="AR13:AR14"/>
-    <mergeCell ref="BD11:BD12"/>
-    <mergeCell ref="BE11:BE12"/>
-    <mergeCell ref="BF11:BF12"/>
-    <mergeCell ref="BG11:BG12"/>
-    <mergeCell ref="BH11:BH12"/>
-    <mergeCell ref="BI11:BI12"/>
-    <mergeCell ref="BJ11:BJ12"/>
-    <mergeCell ref="BK11:BK12"/>
-    <mergeCell ref="BL11:BL12"/>
-    <mergeCell ref="AU11:AU12"/>
-    <mergeCell ref="AV11:AV12"/>
-    <mergeCell ref="AW11:AW12"/>
-    <mergeCell ref="AX11:AX12"/>
-    <mergeCell ref="AY11:AY12"/>
-    <mergeCell ref="AZ11:AZ12"/>
-    <mergeCell ref="BA11:BA12"/>
-    <mergeCell ref="BB11:BB12"/>
-    <mergeCell ref="BC11:BC12"/>
-    <mergeCell ref="AL11:AL12"/>
-    <mergeCell ref="AM11:AM12"/>
-    <mergeCell ref="AN11:AN12"/>
-    <mergeCell ref="AO11:AO12"/>
-    <mergeCell ref="AP11:AP12"/>
-    <mergeCell ref="AQ11:AQ12"/>
-    <mergeCell ref="AR11:AR12"/>
-    <mergeCell ref="AS11:AS12"/>
-    <mergeCell ref="AT11:AT12"/>
-    <mergeCell ref="AC11:AC12"/>
-    <mergeCell ref="AD11:AD12"/>
-    <mergeCell ref="AE11:AE12"/>
-    <mergeCell ref="AF11:AF12"/>
-    <mergeCell ref="AG11:AG12"/>
-    <mergeCell ref="AH11:AH12"/>
-    <mergeCell ref="AI11:AI12"/>
-    <mergeCell ref="AJ11:AJ12"/>
-    <mergeCell ref="AK11:AK12"/>
+    <mergeCell ref="AC11:AD12"/>
     <mergeCell ref="BL7:BL8"/>
     <mergeCell ref="BM7:BM8"/>
     <mergeCell ref="BN7:BN8"/>
@@ -8202,7 +8827,6 @@
     <mergeCell ref="BP7:BP8"/>
     <mergeCell ref="BQ7:BQ8"/>
     <mergeCell ref="BR7:BR8"/>
-    <mergeCell ref="BS7:BS8"/>
     <mergeCell ref="BT7:BT8"/>
     <mergeCell ref="BC7:BC8"/>
     <mergeCell ref="BD7:BD8"/>
@@ -8222,15 +8846,8 @@
     <mergeCell ref="AZ7:AZ8"/>
     <mergeCell ref="BA7:BA8"/>
     <mergeCell ref="BB7:BB8"/>
-    <mergeCell ref="BN5:BN6"/>
-    <mergeCell ref="BO5:BO6"/>
-    <mergeCell ref="BP5:BP6"/>
-    <mergeCell ref="BQ5:BQ6"/>
-    <mergeCell ref="BR5:BR6"/>
-    <mergeCell ref="BS5:BS6"/>
+    <mergeCell ref="BS7:BS8"/>
     <mergeCell ref="BT5:BT6"/>
-    <mergeCell ref="AC7:AC8"/>
-    <mergeCell ref="AD7:AD8"/>
     <mergeCell ref="AE7:AE8"/>
     <mergeCell ref="AF7:AF8"/>
     <mergeCell ref="AG7:AG8"/>
@@ -8246,90 +8863,10 @@
     <mergeCell ref="AQ7:AQ8"/>
     <mergeCell ref="AR7:AR8"/>
     <mergeCell ref="AS7:AS8"/>
-    <mergeCell ref="BE5:BE6"/>
-    <mergeCell ref="BF5:BF6"/>
-    <mergeCell ref="BG5:BG6"/>
-    <mergeCell ref="BH5:BH6"/>
-    <mergeCell ref="BI5:BI6"/>
-    <mergeCell ref="BJ5:BJ6"/>
-    <mergeCell ref="BK5:BK6"/>
-    <mergeCell ref="BL5:BL6"/>
-    <mergeCell ref="BM5:BM6"/>
-    <mergeCell ref="AV5:AV6"/>
-    <mergeCell ref="AW5:AW6"/>
-    <mergeCell ref="AX5:AX6"/>
-    <mergeCell ref="AY5:AY6"/>
-    <mergeCell ref="AZ5:AZ6"/>
-    <mergeCell ref="BA5:BA6"/>
-    <mergeCell ref="BB5:BB6"/>
-    <mergeCell ref="BC5:BC6"/>
-    <mergeCell ref="BD5:BD6"/>
-    <mergeCell ref="BP3:BP4"/>
-    <mergeCell ref="BQ3:BQ4"/>
-    <mergeCell ref="BR3:BR4"/>
-    <mergeCell ref="BS3:BS4"/>
     <mergeCell ref="BT3:BT4"/>
-    <mergeCell ref="AC5:AC6"/>
-    <mergeCell ref="AD5:AD6"/>
-    <mergeCell ref="AE5:AE6"/>
-    <mergeCell ref="AF5:AF6"/>
-    <mergeCell ref="AG5:AG6"/>
-    <mergeCell ref="AH5:AH6"/>
-    <mergeCell ref="AI5:AI6"/>
-    <mergeCell ref="AJ5:AJ6"/>
-    <mergeCell ref="AK5:AK6"/>
-    <mergeCell ref="AL5:AL6"/>
-    <mergeCell ref="AM5:AM6"/>
-    <mergeCell ref="AN5:AN6"/>
-    <mergeCell ref="AO5:AO6"/>
-    <mergeCell ref="AP5:AP6"/>
-    <mergeCell ref="AQ5:AQ6"/>
-    <mergeCell ref="AR5:AR6"/>
-    <mergeCell ref="AS5:AS6"/>
-    <mergeCell ref="AT5:AT6"/>
-    <mergeCell ref="AU5:AU6"/>
-    <mergeCell ref="BG3:BG4"/>
-    <mergeCell ref="BH3:BH4"/>
-    <mergeCell ref="BI3:BI4"/>
-    <mergeCell ref="BJ3:BJ4"/>
-    <mergeCell ref="BK3:BK4"/>
-    <mergeCell ref="BL3:BL4"/>
-    <mergeCell ref="BM3:BM4"/>
-    <mergeCell ref="BN3:BN4"/>
-    <mergeCell ref="BO3:BO4"/>
-    <mergeCell ref="AX3:AX4"/>
-    <mergeCell ref="AY3:AY4"/>
-    <mergeCell ref="AZ3:AZ4"/>
-    <mergeCell ref="BA3:BA4"/>
-    <mergeCell ref="BB3:BB4"/>
-    <mergeCell ref="BC3:BC4"/>
-    <mergeCell ref="BD3:BD4"/>
-    <mergeCell ref="BE3:BE4"/>
-    <mergeCell ref="BF3:BF4"/>
     <mergeCell ref="BR9:BR10"/>
     <mergeCell ref="BS9:BS10"/>
     <mergeCell ref="BT9:BT10"/>
-    <mergeCell ref="AC3:AC4"/>
-    <mergeCell ref="AD3:AD4"/>
-    <mergeCell ref="AE3:AE4"/>
-    <mergeCell ref="AF3:AF4"/>
-    <mergeCell ref="AG3:AG4"/>
-    <mergeCell ref="AH3:AH4"/>
-    <mergeCell ref="AI3:AI4"/>
-    <mergeCell ref="AJ3:AJ4"/>
-    <mergeCell ref="AK3:AK4"/>
-    <mergeCell ref="AL3:AL4"/>
-    <mergeCell ref="AM3:AM4"/>
-    <mergeCell ref="AN3:AN4"/>
-    <mergeCell ref="AO3:AO4"/>
-    <mergeCell ref="AP3:AP4"/>
-    <mergeCell ref="AQ3:AQ4"/>
-    <mergeCell ref="AR3:AR4"/>
-    <mergeCell ref="AS3:AS4"/>
-    <mergeCell ref="AT3:AT4"/>
-    <mergeCell ref="AU3:AU4"/>
-    <mergeCell ref="AV3:AV4"/>
-    <mergeCell ref="AW3:AW4"/>
     <mergeCell ref="BI9:BI10"/>
     <mergeCell ref="BJ9:BJ10"/>
     <mergeCell ref="BK9:BK10"/>
@@ -8532,24 +9069,41 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="C25:AB25 C26:P26 R26:AB26 C27:AB37 C38:P38 R38:AB38 C39:AB43 C44:E44 G44:AB44 C45:AB45">
-    <cfRule type="containsText" dxfId="4" priority="4" operator="containsText" text="Jujitsu">
+    <cfRule type="containsText" dxfId="9" priority="9" operator="containsText" text="Jujitsu">
       <formula>NOT(ISERROR(SEARCH("Jujitsu",C25)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="5" operator="containsText" text="Travail">
+    <cfRule type="containsText" dxfId="8" priority="10" operator="containsText" text="Travail">
       <formula>NOT(ISERROR(SEARCH("Travail",C25)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C25:AB25 C26:P26 R26:AB26 C27:AB37 C38:P38 R38:AB38 C39:AB45">
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="Renfo">
+    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="Renfo">
       <formula>NOT(ISERROR(SEARCH("Renfo",C25)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="Séance">
+    <cfRule type="containsText" dxfId="6" priority="8" operator="containsText" text="Séance">
       <formula>NOT(ISERROR(SEARCH("Séance",C25)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C25:AB45">
-    <cfRule type="containsBlanks" dxfId="0" priority="6">
+    <cfRule type="containsBlanks" dxfId="5" priority="11">
       <formula>LEN(TRIM(C25))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AQ30:BT30">
+    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="Renfo">
+      <formula>NOT(ISERROR(SEARCH("Renfo",AQ30)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="Séance">
+      <formula>NOT(ISERROR(SEARCH("Séance",AQ30)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Jujitsu">
+      <formula>NOT(ISERROR(SEARCH("Jujitsu",AQ30)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="4" operator="containsText" text="Travail">
+      <formula>NOT(ISERROR(SEARCH("Travail",AQ30)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="5">
+      <formula>LEN(TRIM(AQ30))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
